--- a/api/templates/device_and_site_summary_report/fr.xlsx
+++ b/api/templates/device_and_site_summary_report/fr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harshthakkar/Desktop/Projects/aspect/api/templates/device_and_site_summary_report/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/device_and_site_summary_report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{030C1038-52F7-754A-8D7E-E5155DA53C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C265B29A-C9AC-3B4C-B6A0-9E95C2C0A067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Device and Site Summary Report" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="149">
   <si>
     <t>Dates: &lt;Dates&gt;</t>
   </si>
@@ -490,6 +490,9 @@
   <si>
     <t>Langue / Région</t>
   </si>
+  <si>
+    <t>#SUM_DYNAMIC</t>
+  </si>
 </sst>
 </file>
 
@@ -499,7 +502,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d&quot;, &quot;yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -511,38 +514,45 @@
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -564,8 +574,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -584,8 +601,14 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABEBEF"/>
+        <bgColor theme="4" tint="0.79995117038483843"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -697,11 +720,108 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -755,11 +875,60 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -785,14 +954,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1052,7 +1213,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="23" t="s">
         <v>134</v>
       </c>
       <c r="B1" s="1"/>
@@ -1073,11 +1234,11 @@
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
       <c r="H2" s="5"/>
       <c r="J2" s="2"/>
       <c r="K2" s="3"/>
@@ -1093,11 +1254,11 @@
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
       <c r="H3" s="5"/>
       <c r="J3" s="2"/>
       <c r="K3" s="3"/>
@@ -1113,9 +1274,9 @@
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
       <c r="H4" s="5"/>
       <c r="J4" s="2"/>
       <c r="K4" s="3"/>
@@ -1131,9 +1292,9 @@
       <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
       <c r="H5" s="5"/>
       <c r="J5" s="2"/>
       <c r="K5" s="3"/>
@@ -1149,9 +1310,9 @@
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
       <c r="J6" s="2"/>
       <c r="K6" s="3"/>
       <c r="L6" s="2"/>
@@ -1179,46 +1340,46 @@
       <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:26" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="F8" s="38" t="s">
+      <c r="F8" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="H8" s="38" t="s">
+      <c r="H8" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="I8" s="38" t="s">
+      <c r="I8" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="J8" s="38" t="s">
+      <c r="J8" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="K8" s="39" t="s">
+      <c r="K8" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="L8" s="39" t="s">
+      <c r="L8" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="M8" s="39" t="s">
+      <c r="M8" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="N8" s="39" t="s">
+      <c r="N8" s="25" t="s">
         <v>147</v>
       </c>
       <c r="O8" s="9" t="s">
@@ -1246,7 +1407,7 @@
       <c r="Y8" s="10"/>
       <c r="Z8" s="10"/>
     </row>
-    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>14</v>
       </c>
@@ -1308,16 +1469,36 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J10" s="2"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="3"/>
+    <row r="10" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="26"/>
+      <c r="S10" s="26">
+        <f>SUM(S$9:S9)</f>
+        <v>0</v>
+      </c>
+      <c r="T10" s="26">
+        <f>SUM(T$9:T9)</f>
+        <v>0</v>
+      </c>
+      <c r="U10" s="27" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="18"/>
@@ -4455,13 +4636,13 @@
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
@@ -5823,108 +6004,108 @@
       <c r="AF7" s="2"/>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="F8" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="G8" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="30" t="s">
+      <c r="H8" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="I8" s="30" t="s">
+      <c r="I8" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="30" t="s">
+      <c r="J8" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="K8" s="30" t="s">
+      <c r="K8" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="L8" s="30" t="s">
+      <c r="L8" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="M8" s="30" t="s">
+      <c r="M8" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="N8" s="30" t="s">
+      <c r="N8" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="O8" s="30" t="s">
+      <c r="O8" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="P8" s="30" t="s">
+      <c r="P8" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="Q8" s="30" t="s">
+      <c r="Q8" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="R8" s="30" t="s">
+      <c r="R8" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="S8" s="30" t="s">
+      <c r="S8" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="T8" s="30" t="s">
+      <c r="T8" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="U8" s="31" t="s">
+      <c r="U8" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="V8" s="32"/>
-      <c r="W8" s="32"/>
-      <c r="X8" s="32"/>
-      <c r="Y8" s="32"/>
-      <c r="Z8" s="32"/>
-      <c r="AA8" s="32"/>
-      <c r="AB8" s="32"/>
-      <c r="AC8" s="33"/>
-      <c r="AD8" s="28" t="s">
+      <c r="V8" s="51"/>
+      <c r="W8" s="51"/>
+      <c r="X8" s="51"/>
+      <c r="Y8" s="51"/>
+      <c r="Z8" s="51"/>
+      <c r="AA8" s="51"/>
+      <c r="AB8" s="51"/>
+      <c r="AC8" s="52"/>
+      <c r="AD8" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="AE8" s="28" t="s">
+      <c r="AE8" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="AF8" s="28" t="s">
+      <c r="AF8" s="47" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="29"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
+      <c r="A9" s="48"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="48"/>
+      <c r="O9" s="48"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="48"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="48"/>
       <c r="U9" s="22">
         <v>5011</v>
       </c>
@@ -5952,113 +6133,113 @@
       <c r="AC9" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="AD9" s="29"/>
-      <c r="AE9" s="29"/>
-      <c r="AF9" s="29"/>
+      <c r="AD9" s="48"/>
+      <c r="AE9" s="48"/>
+      <c r="AF9" s="48"/>
     </row>
     <row r="10" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="17">
         <f>IFERROR(IF(A10="No data","",IF(C10=0,0,D10/C10)),0)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="29">
         <f>IFERROR(IF(A10="No data","",IF(B10&lt;&gt;0, G10/B10, 0)),0)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="17">
         <f>IFERROR(IF(A10="No data","",U10+V10+W10+X10+Y10+Z10+AA10+AB10+AC10+AD10),0)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="17">
         <f>IFERROR(IF(A10="No data","",IF(G10=0,0,I10/G10)),0)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="17">
         <f>IFERROR(IF(A10="No data","",IF(G10=0,0,J10/G10)),0)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="17">
         <f>IFERROR(IF(A10="No data","",IF(D10=0,0,I10/D10)),0)</f>
         <v>0</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O10" s="17">
         <f>IFERROR(IF(A10="No data","",IF(G10=0,0,K10/G10)),0)</f>
         <v>0</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="P10" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="Q10" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="R10" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="S10" s="2">
+      <c r="S10" s="17">
         <f>IFERROR(IF(A10="No data","",IF(I10=0,0,R10/I10)),0)</f>
         <v>0</v>
       </c>
-      <c r="T10" s="2" t="s">
+      <c r="T10" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="U10" s="2" t="s">
+      <c r="U10" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="V10" s="2" t="s">
+      <c r="V10" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="W10" s="2" t="s">
+      <c r="W10" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="X10" s="2" t="s">
+      <c r="X10" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="Y10" s="2" t="s">
+      <c r="Y10" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="Z10" s="2" t="s">
+      <c r="Z10" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="AA10" s="2" t="s">
+      <c r="AA10" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="AB10" s="2" t="s">
+      <c r="AB10" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="AC10" s="2" t="s">
+      <c r="AC10" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="AD10" s="2" t="s">
+      <c r="AD10" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="AE10" s="2" t="s">
+      <c r="AE10" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="AF10" s="2">
+      <c r="AF10" s="17">
         <f>IFERROR(IF(A10="No data","",U10+V10+W10+X10+Y10+Z10+AA10+AB10+AC10+AD10+AE10),0)</f>
         <v>0</v>
       </c>
@@ -13942,29 +14123,29 @@
       <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="35" t="s">
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="L8" s="35" t="s">
+      <c r="L8" s="54" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="29"/>
+      <c r="A9" s="48"/>
       <c r="B9" s="22">
         <v>5011</v>
       </c>
@@ -13992,44 +14173,44 @@
       <c r="J9" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="L10" s="2" t="e">
+      <c r="L10" s="17" t="e">
         <f>B10+C10+D10+E10+F10+G10+H10+I10+J10+K10</f>
         <v>#VALUE!</v>
       </c>
@@ -17563,317 +17744,317 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C1000"/>
+  <dimension ref="B2:D1001"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.1640625" customWidth="1"/>
-    <col min="2" max="2" width="39.1640625" customWidth="1"/>
-    <col min="3" max="3" width="100.6640625" customWidth="1"/>
-    <col min="4" max="6" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.5" customWidth="1"/>
+    <col min="2" max="2" width="7.5" customWidth="1"/>
+    <col min="3" max="3" width="39.1640625" customWidth="1"/>
+    <col min="4" max="4" width="74.1640625" customWidth="1"/>
+    <col min="5" max="7" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+    <row r="2" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="C2" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D2" s="30" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24">
+    <row r="3" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="31">
         <v>1001</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="C3" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="D3" s="33" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24">
+    <row r="4" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="34">
         <v>1002</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="C4" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="D4" s="36" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="24">
+    <row r="5" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="37">
         <v>1004</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="C5" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="D5" s="39" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="24">
+    <row r="6" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="34">
         <v>1005</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="C6" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="D6" s="36" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="24">
+    <row r="7" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="37">
         <v>1006</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="C7" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="D7" s="39" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="24">
+    <row r="8" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="34">
         <v>1007</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="C8" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="D8" s="36" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="24">
+    <row r="9" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="37">
         <v>1017</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="C9" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="D9" s="39" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="24">
+    <row r="10" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="34">
         <v>1018</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="C10" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="D10" s="36" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="24">
+    <row r="11" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="37">
         <v>2003</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="C11" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="D11" s="39" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="24">
+    <row r="12" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="34">
         <v>2005</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="C12" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="D12" s="36" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="24">
+    <row r="13" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="37">
         <v>2008</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="C13" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="D13" s="39" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="24">
+    <row r="14" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="34">
         <v>2009</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="C14" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="D14" s="36" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="24">
+    <row r="15" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="37">
         <v>2011</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="C15" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="D15" s="39" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="24">
+    <row r="16" spans="2:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B16" s="34">
         <v>2014</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="C16" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="D16" s="36" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="24">
+    <row r="17" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="37">
         <v>2016</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="C17" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="D17" s="39" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="24">
+    <row r="18" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="34">
         <v>2018</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="C18" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="D18" s="36" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="24">
+    <row r="19" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="37">
         <v>2022</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="C19" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="D19" s="39" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="24">
+    <row r="20" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="34">
         <v>2025</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="C20" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="D20" s="36" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="24">
+    <row r="21" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="37">
         <v>2032</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="C21" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="D21" s="39" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="24">
+    <row r="22" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="34">
         <v>2034</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="C22" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="D22" s="36" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="24">
+    <row r="23" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="37">
         <v>2037</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="C23" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="D23" s="39" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="24">
+    <row r="24" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="34">
         <v>4010</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="C24" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="C23" s="24" t="s">
+      <c r="D24" s="36" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="24">
+    <row r="25" spans="2:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="B25" s="37">
         <v>4017</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="C25" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="D25" s="39" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="24">
+    <row r="26" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="34">
         <v>5006</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="C26" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="D26" s="36" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="24">
+    <row r="27" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="37">
         <v>5007</v>
       </c>
-      <c r="B26" s="24" t="s">
+      <c r="C27" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="D27" s="39" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="24">
+    <row r="28" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="40">
         <v>5011</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="C28" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="D28" s="42" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -18842,6 +19023,7 @@
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>

--- a/api/templates/device_and_site_summary_report/fr.xlsx
+++ b/api/templates/device_and_site_summary_report/fr.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/device_and_site_summary_report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C265B29A-C9AC-3B4C-B6A0-9E95C2C0A067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFB1B3E-378D-CE4C-BAFE-8292B1F1CF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4340" yWindow="760" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Device and Site Summary Report" sheetId="1" r:id="rId1"/>
-    <sheet name="Device and Site Inventory" sheetId="2" r:id="rId2"/>
-    <sheet name="Devices TB Reach" sheetId="3" r:id="rId3"/>
-    <sheet name="Errors by Device" sheetId="4" r:id="rId4"/>
-    <sheet name="Error Codes" sheetId="5" r:id="rId5"/>
+    <sheet name="Rapport récapitulatif sur l’app" sheetId="1" r:id="rId1"/>
+    <sheet name="Inventaire des appareils et des" sheetId="2" r:id="rId2"/>
+    <sheet name="Appareils TB Portée" sheetId="3" r:id="rId3"/>
+    <sheet name="Erreurs par appareil" sheetId="4" r:id="rId4"/>
+    <sheet name="Codes d'erreur" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="153">
   <si>
     <t>Dates: &lt;Dates&gt;</t>
   </si>
@@ -141,34 +141,10 @@
     <t>&lt;totalOtherTests&gt;</t>
   </si>
   <si>
-    <t>Device and Site Inventory</t>
-  </si>
-  <si>
-    <t>Note: this report only includes the consumables that were sometime tracked on the sites</t>
-  </si>
-  <si>
     <t>Site</t>
   </si>
   <si>
     <t>Consumable</t>
-  </si>
-  <si>
-    <t>Daily Consumption Rate</t>
-  </si>
-  <si>
-    <t>Projected Annual Consumption</t>
-  </si>
-  <si>
-    <t>Quantity On Hand</t>
-  </si>
-  <si>
-    <t>Quantity On Hand but Expired</t>
-  </si>
-  <si>
-    <t>Days Stock Left</t>
-  </si>
-  <si>
-    <t>Projected Waste</t>
   </si>
   <si>
     <t>&lt;siteName&gt;</t>
@@ -195,9 +171,6 @@
     <t>&lt;projectedWaste&gt;</t>
   </si>
   <si>
-    <t>List of Devices for TB Reach</t>
-  </si>
-  <si>
     <t>BK Total</t>
   </si>
   <si>
@@ -213,20 +186,10 @@
     <t>%BK+</t>
   </si>
   <si>
-    <t>Xpert Tests</t>
-  </si>
-  <si>
-    <t>%Xpert Tests</t>
-  </si>
-  <si>
     <t>Xpert+</t>
   </si>
   <si>
     <t>Xpert-</t>
-  </si>
-  <si>
-    <t>Xpert 
-Error/Invalid</t>
   </si>
   <si>
     <t>%Xpert+</t>
@@ -235,43 +198,11 @@
     <t>%Xpert-</t>
   </si>
   <si>
-    <t>%Xpert
-Increase</t>
-  </si>
-  <si>
-    <t>%Xpert
- Error/Invalid</t>
-  </si>
-  <si>
     <t>Xpert RIF+</t>
   </si>
   <si>
     <t>Xpert 
 Rif IND</t>
-  </si>
-  <si>
-    <t>Xpert+
- Treated</t>
-  </si>
-  <si>
-    <t>%Xpert+
-Treated</t>
-  </si>
-  <si>
-    <t>Xpert 
-Per Day</t>
-  </si>
-  <si>
-    <t>Type of error</t>
-  </si>
-  <si>
-    <t>Invalid Results</t>
-  </si>
-  <si>
-    <t>No Results</t>
-  </si>
-  <si>
-    <t>Total errors, invalid results, no results</t>
   </si>
   <si>
     <t>Other Error</t>
@@ -343,109 +274,10 @@
     <t>&lt;noResults&gt;</t>
   </si>
   <si>
-    <t>Errors by Device</t>
-  </si>
-  <si>
-    <t>Invalid results, no results</t>
-  </si>
-  <si>
     <t>Code</t>
   </si>
   <si>
-    <t>Category</t>
-  </si>
-  <si>
     <t>Description</t>
-  </si>
-  <si>
-    <t>Run-time error</t>
-  </si>
-  <si>
-    <t>The actual temperature has drifted too far away from the setpoint</t>
-  </si>
-  <si>
-    <t>The temperature difference exceeds the limit</t>
-  </si>
-  <si>
-    <t>The internal instrument temperature was out of range</t>
-  </si>
-  <si>
-    <t>Optic signal of from detector exceeded the limit</t>
-  </si>
-  <si>
-    <t>Detector dark signal exceeded the limit</t>
-  </si>
-  <si>
-    <t>The power supply was detected to be out of range</t>
-  </si>
-  <si>
-    <t>The measured temperature of the optical system was not within the acceptable range</t>
-  </si>
-  <si>
-    <t>A valve positioning error was detected at the end of the run</t>
-  </si>
-  <si>
-    <t>Operation terminated error</t>
-  </si>
-  <si>
-    <t>Module is already running a test while performing command</t>
-  </si>
-  <si>
-    <t>Motion of the syringe drive was not detected</t>
-  </si>
-  <si>
-    <t>Syringe pressure reading exceeds the protocol limit</t>
-  </si>
-  <si>
-    <t>Syringe pressure reading is below the protocol limit</t>
-  </si>
-  <si>
-    <t>Cartridge loading error</t>
-  </si>
-  <si>
-    <t>Unable to initialize pressure sensor</t>
-  </si>
-  <si>
-    <t>The digital temperature reading for Thermistor A/Thermistor B/Ambient Thermistor/Optic Thermistor was not within the acceptable range</t>
-  </si>
-  <si>
-    <t>The system was unable to find the valve home position</t>
-  </si>
-  <si>
-    <t>Attempt to load a cartridge while the door is still closed</t>
-  </si>
-  <si>
-    <t>Failed to get to desired temperature</t>
-  </si>
-  <si>
-    <t>The system failed to find the plunger home position</t>
-  </si>
-  <si>
-    <t>The ultrasonic horn could not be tuned properly</t>
-  </si>
-  <si>
-    <t>The optical signal from Detector did not reach the expected value</t>
-  </si>
-  <si>
-    <t>The cartridge integrity test failed</t>
-  </si>
-  <si>
-    <t>Self-test error</t>
-  </si>
-  <si>
-    <t>Cooling fan operation was not verified. Measured temperature exceeded the limit</t>
-  </si>
-  <si>
-    <t>Post-run analysis error</t>
-  </si>
-  <si>
-    <t>Probe check failed. Probe check value was above the maximum</t>
-  </si>
-  <si>
-    <t>Probe check failed. Probe check value was below the minimum</t>
-  </si>
-  <si>
-    <t>Signal loss detected in the amplification curve</t>
   </si>
   <si>
     <t>Rapport récapitulatif sur l’appareil et le site</t>
@@ -492,6 +324,186 @@
   </si>
   <si>
     <t>#SUM_DYNAMIC</t>
+  </si>
+  <si>
+    <t>&lt;unreconciledResults&gt;</t>
+  </si>
+  <si>
+    <t>Taux de consommation journalier</t>
+  </si>
+  <si>
+    <t>Consommation annuelle prévue</t>
+  </si>
+  <si>
+    <t>Quantité disponible</t>
+  </si>
+  <si>
+    <t>Quantité disponible mais périmée</t>
+  </si>
+  <si>
+    <t>Jours de stock restant</t>
+  </si>
+  <si>
+    <t>Déchets prévus</t>
+  </si>
+  <si>
+    <t>Total des résultats non réconciliés</t>
+  </si>
+  <si>
+    <t>Note : ce rapport n'inclut que les produits consommables qui ont été parfois suivis sur les sites.</t>
+  </si>
+  <si>
+    <t>Inventaire des appareils et des sites</t>
+  </si>
+  <si>
+    <t>Liste des dispositifs pour la portée de la TB</t>
+  </si>
+  <si>
+    <t>Dispositif</t>
+  </si>
+  <si>
+    <t>Tests Xpert</t>
+  </si>
+  <si>
+    <t>%Tests Xpert</t>
+  </si>
+  <si>
+    <t>Xpert
+Erreur/Invalide</t>
+  </si>
+  <si>
+    <t>%Xpert
+Augmenter</t>
+  </si>
+  <si>
+    <t>%Xpert
+ Erreur/Invalide</t>
+  </si>
+  <si>
+    <t>Xpert+
+ Traité</t>
+  </si>
+  <si>
+    <t>Xpert+
+Traité</t>
+  </si>
+  <si>
+    <t>Xpert
+Par jour</t>
+  </si>
+  <si>
+    <t>Type d'erreur</t>
+  </si>
+  <si>
+    <t>Résultats non valides</t>
+  </si>
+  <si>
+    <t>Pas de résultats</t>
+  </si>
+  <si>
+    <t>Erreurs totales, résultats non valides, pas de résultats</t>
+  </si>
+  <si>
+    <t>Résultats invalides, pas de résultats</t>
+  </si>
+  <si>
+    <t>Totaux</t>
+  </si>
+  <si>
+    <t>Erreur d’exécution</t>
+  </si>
+  <si>
+    <t>La température réelle s’est trop éloignée du point de consigne</t>
+  </si>
+  <si>
+    <t>La différence de température dépasse la limite</t>
+  </si>
+  <si>
+    <t>La température interne de l’instrument était hors plage</t>
+  </si>
+  <si>
+    <t>Le signal optique du détecteur a dépassé la limite</t>
+  </si>
+  <si>
+    <t>Le signal obscur du détecteur a dépassé la limite</t>
+  </si>
+  <si>
+    <t>L’alimentation électrique a été détectée hors plage</t>
+  </si>
+  <si>
+    <t>La température mesurée du système optique n’était pas dans la plage acceptable</t>
+  </si>
+  <si>
+    <t>Une erreur de positionnement de vanne a été détectée à la fin du cycle</t>
+  </si>
+  <si>
+    <t>Erreur de fin d’opération</t>
+  </si>
+  <si>
+    <t>Le module exécute déjà un test lors de l’exécution de la commande</t>
+  </si>
+  <si>
+    <t>Le mouvement du moteur de la seringue n’a pas été détecté</t>
+  </si>
+  <si>
+    <t>La pression de la seringue dépasse la limite du protocole</t>
+  </si>
+  <si>
+    <t>La pression de la seringue est inférieure à la limite du protocole</t>
+  </si>
+  <si>
+    <t>Erreur de chargement de cartouche</t>
+  </si>
+  <si>
+    <t>Impossible d’initialiser le capteur de pression</t>
+  </si>
+  <si>
+    <t>La lecture de température des thermistances A/B/Ambiante/Optique est hors plage acceptable</t>
+  </si>
+  <si>
+    <t>Le système n’a pas pu trouver la position d’origine de la vanne</t>
+  </si>
+  <si>
+    <t>Tentative de chargement d’une cartouche alors que la porte est encore fermée</t>
+  </si>
+  <si>
+    <t>Échec pour atteindre la température souhaitée</t>
+  </si>
+  <si>
+    <t>Le système n’a pas pu trouver la position d’origine du piston</t>
+  </si>
+  <si>
+    <t>Le cornet ultrasonique n’a pas pu être correctement accordé</t>
+  </si>
+  <si>
+    <t>Le signal optique du détecteur n’a pas atteint la valeur attendue</t>
+  </si>
+  <si>
+    <t>Le test d’intégrité de la cartouche a échoué</t>
+  </si>
+  <si>
+    <t>Erreur d’auto-test</t>
+  </si>
+  <si>
+    <t>Le fonctionnement du ventilateur de refroidissement n’a pas été vérifié. La température mesurée dépasse la limite</t>
+  </si>
+  <si>
+    <t>Erreur d’analyse post-exécution</t>
+  </si>
+  <si>
+    <t>Échec de la vérification de la sonde. La valeur était supérieure au maximum autorisé</t>
+  </si>
+  <si>
+    <t>Échec de la vérification de la sonde. La valeur était inférieure au minimum autorisé</t>
+  </si>
+  <si>
+    <t>Pertes de signal détectées dans la courbe d’amplification</t>
+  </si>
+  <si>
+    <t>Catégorie</t>
+  </si>
+  <si>
+    <t>Erreurs par appareil</t>
   </si>
 </sst>
 </file>
@@ -568,13 +580,14 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -608,7 +621,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -641,17 +654,6 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -817,11 +819,74 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -844,24 +909,6 @@
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -876,28 +923,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -906,7 +946,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -915,7 +955,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -924,8 +964,51 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -937,22 +1020,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1195,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1000"/>
+  <dimension ref="A1:U1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="27" customWidth="1"/>
@@ -1212,9 +1295,9 @@
     <col min="20" max="26" width="11.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
-        <v>134</v>
+    <row r="1" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>80</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1230,15 +1313,15 @@
       <c r="Q1" s="2"/>
       <c r="R1" s="3"/>
     </row>
-    <row r="2" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
+      <c r="E2" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
       <c r="H2" s="5"/>
       <c r="J2" s="2"/>
       <c r="K2" s="3"/>
@@ -1250,15 +1333,15 @@
       <c r="Q2" s="2"/>
       <c r="R2" s="3"/>
     </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
       <c r="H3" s="5"/>
       <c r="J3" s="2"/>
       <c r="K3" s="3"/>
@@ -1270,13 +1353,13 @@
       <c r="Q3" s="2"/>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
       <c r="H4" s="5"/>
       <c r="J4" s="2"/>
       <c r="K4" s="3"/>
@@ -1288,13 +1371,13 @@
       <c r="Q4" s="2"/>
       <c r="R4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
       <c r="H5" s="5"/>
       <c r="J5" s="2"/>
       <c r="K5" s="3"/>
@@ -1306,13 +1389,13 @@
       <c r="Q5" s="2"/>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
       <c r="J6" s="2"/>
       <c r="K6" s="3"/>
       <c r="L6" s="2"/>
@@ -1323,7 +1406,7 @@
       <c r="Q6" s="2"/>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
@@ -1339,48 +1422,48 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" spans="1:26" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="24" t="s">
+    <row r="8" spans="1:21" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="C8" s="24" t="s">
+      <c r="B8" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="H8" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="J8" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="K8" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="L8" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="M8" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="N8" s="25" t="s">
-        <v>147</v>
+      <c r="D8" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>93</v>
       </c>
       <c r="O8" s="9" t="s">
         <v>8</v>
@@ -1400,112 +1483,108 @@
       <c r="T8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="U8" s="10"/>
-      <c r="V8" s="10"/>
-      <c r="W8" s="10"/>
-      <c r="X8" s="10"/>
-      <c r="Y8" s="10"/>
-      <c r="Z8" s="10"/>
-    </row>
-    <row r="9" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+    </row>
+    <row r="9" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K9" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="17" t="s">
+      <c r="L9" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="M9" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="N9" s="17" t="s">
+      <c r="N9" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="O9" s="17" t="s">
+      <c r="O9" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="P9" s="17" t="s">
+      <c r="P9" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="Q9" s="17" t="s">
+      <c r="Q9" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="R9" s="16" t="s">
+      <c r="R9" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="S9" s="11" t="s">
+      <c r="S9" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="T9" s="11" t="s">
+      <c r="T9" s="47" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="26">
+    <row r="10" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16">
         <f>SUM(S$9:S9)</f>
         <v>0</v>
       </c>
-      <c r="T10" s="26">
+      <c r="T10" s="16">
         <f>SUM(T$9:T9)</f>
         <v>0</v>
       </c>
-      <c r="U10" s="27" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
+      <c r="U10" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
       <c r="J11" s="2"/>
       <c r="K11" s="3"/>
       <c r="L11" s="2"/>
@@ -1516,7 +1595,7 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J12" s="2"/>
       <c r="K12" s="3"/>
       <c r="L12" s="2"/>
@@ -1527,7 +1606,7 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J13" s="2"/>
       <c r="K13" s="3"/>
       <c r="L13" s="2"/>
@@ -1538,7 +1617,7 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J14" s="2"/>
       <c r="K14" s="3"/>
       <c r="L14" s="2"/>
@@ -1549,7 +1628,7 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J15" s="2"/>
       <c r="K15" s="3"/>
       <c r="L15" s="2"/>
@@ -1560,7 +1639,7 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J16" s="2"/>
       <c r="K16" s="3"/>
       <c r="L16" s="2"/>
@@ -4611,127 +4690,167 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:I1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" customWidth="1"/>
     <col min="3" max="3" width="21.6640625" customWidth="1"/>
-    <col min="4" max="4" width="28.1640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="27.33203125" customWidth="1"/>
-    <col min="7" max="7" width="14.1640625" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="31.33203125" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" customWidth="1"/>
+    <col min="6" max="6" width="32" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="25.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
-        <v>34</v>
+    <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>104</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="46" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-    </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C2" s="56" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+    </row>
+    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="6"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B9" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C9" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D9" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E9" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F9" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G9" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H9" s="36" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="I9" s="36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="33"/>
+      <c r="C10" s="34" t="e">
+        <f>AVERAGE(C$9:C9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D10" s="33">
+        <f>SUM(D$9:D9)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="33">
+        <f>SUM(E$9:E9)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="33">
+        <f>SUM(F$9:F9)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="34" t="e">
+        <f>AVERAGE(G$9:G9)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H10" s="33">
+        <f>SUM(H$9:H9)</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="35">
+        <f>SUM(I$9:I9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5755,7 +5874,7 @@
   <sheetData>
     <row r="1" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5862,7 +5981,7 @@
       <c r="AF3" s="2"/>
     </row>
     <row r="4" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2"/>
@@ -5898,7 +6017,7 @@
       <c r="AF4" s="2"/>
     </row>
     <row r="5" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="20"/>
+      <c r="A5" s="12"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -5966,7 +6085,7 @@
       <c r="AF6" s="2"/>
     </row>
     <row r="7" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="13" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2">
@@ -6004,278 +6123,362 @@
       <c r="AF7" s="2"/>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="47" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="49" t="s">
+      <c r="A8" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="59" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="59" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="59" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="59" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="59" t="s">
+        <v>107</v>
+      </c>
+      <c r="H8" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="I8" s="59" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="59" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="59" t="s">
+        <v>109</v>
+      </c>
+      <c r="L8" s="59" t="s">
+        <v>51</v>
+      </c>
+      <c r="M8" s="59" t="s">
+        <v>52</v>
+      </c>
+      <c r="N8" s="59" t="s">
+        <v>110</v>
+      </c>
+      <c r="O8" s="59" t="s">
+        <v>111</v>
+      </c>
+      <c r="P8" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="Q8" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="49" t="s">
+      <c r="R8" s="59" t="s">
+        <v>112</v>
+      </c>
+      <c r="S8" s="59" t="s">
+        <v>113</v>
+      </c>
+      <c r="T8" s="59" t="s">
+        <v>114</v>
+      </c>
+      <c r="U8" s="60" t="s">
+        <v>115</v>
+      </c>
+      <c r="V8" s="61"/>
+      <c r="W8" s="61"/>
+      <c r="X8" s="61"/>
+      <c r="Y8" s="61"/>
+      <c r="Z8" s="61"/>
+      <c r="AA8" s="61"/>
+      <c r="AB8" s="61"/>
+      <c r="AC8" s="62"/>
+      <c r="AD8" s="57" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE8" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF8" s="57" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="58"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="58"/>
+      <c r="L9" s="58"/>
+      <c r="M9" s="58"/>
+      <c r="N9" s="58"/>
+      <c r="O9" s="58"/>
+      <c r="P9" s="58"/>
+      <c r="Q9" s="58"/>
+      <c r="R9" s="58"/>
+      <c r="S9" s="58"/>
+      <c r="T9" s="58"/>
+      <c r="U9" s="14">
+        <v>5011</v>
+      </c>
+      <c r="V9" s="14">
+        <v>5007</v>
+      </c>
+      <c r="W9" s="14">
+        <v>5006</v>
+      </c>
+      <c r="X9" s="14">
+        <v>2008</v>
+      </c>
+      <c r="Y9" s="14">
+        <v>2005</v>
+      </c>
+      <c r="Z9" s="14">
+        <v>2037</v>
+      </c>
+      <c r="AA9" s="14">
+        <v>2025</v>
+      </c>
+      <c r="AB9" s="14">
+        <v>2022</v>
+      </c>
+      <c r="AC9" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="49" t="s">
+      <c r="AD9" s="58"/>
+      <c r="AE9" s="58"/>
+      <c r="AF9" s="58"/>
+    </row>
+    <row r="10" spans="1:32" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="49" t="s">
+      <c r="B10" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="49" t="s">
+      <c r="C10" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="49" t="s">
+      <c r="D10" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="I8" s="49" t="s">
+      <c r="E10" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="K8" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="L8" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="M8" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="N8" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="O8" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="P8" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q8" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="R8" s="49" t="s">
-        <v>69</v>
-      </c>
-      <c r="S8" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="T8" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="U8" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="V8" s="51"/>
-      <c r="W8" s="51"/>
-      <c r="X8" s="51"/>
-      <c r="Y8" s="51"/>
-      <c r="Z8" s="51"/>
-      <c r="AA8" s="51"/>
-      <c r="AB8" s="51"/>
-      <c r="AC8" s="52"/>
-      <c r="AD8" s="47" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE8" s="47" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF8" s="47" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="48"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="48"/>
-      <c r="O9" s="48"/>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="48"/>
-      <c r="R9" s="48"/>
-      <c r="S9" s="48"/>
-      <c r="T9" s="48"/>
-      <c r="U9" s="22">
-        <v>5011</v>
-      </c>
-      <c r="V9" s="22">
-        <v>5007</v>
-      </c>
-      <c r="W9" s="22">
-        <v>5006</v>
-      </c>
-      <c r="X9" s="22">
-        <v>2008</v>
-      </c>
-      <c r="Y9" s="22">
-        <v>2005</v>
-      </c>
-      <c r="Z9" s="22">
-        <v>2037</v>
-      </c>
-      <c r="AA9" s="22">
-        <v>2025</v>
-      </c>
-      <c r="AB9" s="22">
-        <v>2022</v>
-      </c>
-      <c r="AC9" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="AD9" s="48"/>
-      <c r="AE9" s="48"/>
-      <c r="AF9" s="48"/>
-    </row>
-    <row r="10" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="F10" s="17">
+      <c r="F10" s="50">
         <f>IFERROR(IF(A10="No data","",IF(C10=0,0,D10/C10)),0)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="51">
         <f>IFERROR(IF(A10="No data","",IF(B10&lt;&gt;0, G10/B10, 0)),0)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="K10" s="17">
+      <c r="I10" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="K10" s="49">
         <f>IFERROR(IF(A10="No data","",U10+V10+W10+X10+Y10+Z10+AA10+AB10+AC10+AD10),0)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="17">
+      <c r="L10" s="50">
         <f>IFERROR(IF(A10="No data","",IF(G10=0,0,I10/G10)),0)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="17">
+      <c r="M10" s="50">
         <f>IFERROR(IF(A10="No data","",IF(G10=0,0,J10/G10)),0)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="17">
+      <c r="N10" s="50">
         <f>IFERROR(IF(A10="No data","",IF(D10=0,0,I10/D10)),0)</f>
         <v>0</v>
       </c>
-      <c r="O10" s="17">
+      <c r="O10" s="50">
         <f>IFERROR(IF(A10="No data","",IF(G10=0,0,K10/G10)),0)</f>
         <v>0</v>
       </c>
-      <c r="P10" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q10" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="R10" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="S10" s="17">
+      <c r="P10" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q10" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="R10" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="S10" s="50">
         <f>IFERROR(IF(A10="No data","",IF(I10=0,0,R10/I10)),0)</f>
         <v>0</v>
       </c>
-      <c r="T10" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="U10" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="V10" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="W10" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="X10" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y10" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z10" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="AA10" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB10" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="AC10" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="AD10" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="AE10" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF10" s="17">
+      <c r="T10" s="52" t="s">
+        <v>66</v>
+      </c>
+      <c r="U10" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="V10" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="W10" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="X10" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y10" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z10" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA10" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB10" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC10" s="49" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD10" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE10" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF10" s="49">
         <f>IFERROR(IF(A10="No data","",U10+V10+W10+X10+Y10+Z10+AA10+AB10+AC10+AD10+AE10),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="2"/>
-      <c r="AA11" s="2"/>
-      <c r="AB11" s="2"/>
-      <c r="AC11" s="2"/>
-      <c r="AD11" s="2"/>
-      <c r="AE11" s="2"/>
-      <c r="AF11" s="2"/>
+    <row r="11" spans="1:32" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="40">
+        <f>AVERAGE(F$10:F10)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="41">
+        <f>SUM(G$10:G10)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="40">
+        <f>AVERAGE(H$10:H10)</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="41">
+        <f>SUM(I$10:I10)</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="41">
+        <f>SUM(J$10:J10)</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="41">
+        <f>SUM(K$10:K10)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="40">
+        <f>AVERAGE(L$10:L10)</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="40">
+        <f>AVERAGE(M$10:M10)</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="40">
+        <f>AVERAGE(N$10:N10)</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="40">
+        <f>AVERAGE(O$10:O10)</f>
+        <v>0</v>
+      </c>
+      <c r="P11" s="41">
+        <f>SUM(P$10:P10)</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="41">
+        <f>SUM(Q$10:Q10)</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="41">
+        <f>SUM(R$10:R10)</f>
+        <v>0</v>
+      </c>
+      <c r="S11" s="40">
+        <f>AVERAGE(S$10:S10)</f>
+        <v>0</v>
+      </c>
+      <c r="T11" s="40" t="e">
+        <f>AVERAGE(T$10:T10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U11" s="41">
+        <f>SUM(U$10:U10)</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="41">
+        <f>SUM(V$10:V10)</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="41">
+        <f>SUM(W$10:W10)</f>
+        <v>0</v>
+      </c>
+      <c r="X11" s="41">
+        <f>SUM(X$10:X10)</f>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="41">
+        <f>SUM(Y$10:Y10)</f>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="41">
+        <f>SUM(Z$10:Z10)</f>
+        <v>0</v>
+      </c>
+      <c r="AA11" s="41">
+        <f>SUM(AA$10:AA10)</f>
+        <v>0</v>
+      </c>
+      <c r="AB11" s="41">
+        <f>SUM(AB$10:AB10)</f>
+        <v>0</v>
+      </c>
+      <c r="AC11" s="41">
+        <f>SUM(AC$10:AC10)</f>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="41">
+        <f>SUM(AD$10:AD10)</f>
+        <v>0</v>
+      </c>
+      <c r="AE11" s="41">
+        <f>SUM(AE$10:AE10)</f>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="41">
+        <f>SUM(AF$10:AF10)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="2"/>
@@ -14010,7 +14213,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>152</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -14057,7 +14260,7 @@
       <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2"/>
@@ -14073,7 +14276,7 @@
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2"/>
@@ -14105,7 +14308,7 @@
       <c r="L6" s="2"/>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="13" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2">
@@ -14123,110 +14326,146 @@
       <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="53" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="50" t="s">
+      <c r="A8" s="63" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="60" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="64" t="s">
+        <v>119</v>
+      </c>
+      <c r="L8" s="64" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="58"/>
+      <c r="B9" s="14">
+        <v>5011</v>
+      </c>
+      <c r="C9" s="14">
+        <v>5007</v>
+      </c>
+      <c r="D9" s="14">
+        <v>5006</v>
+      </c>
+      <c r="E9" s="14">
+        <v>2008</v>
+      </c>
+      <c r="F9" s="14">
+        <v>2005</v>
+      </c>
+      <c r="G9" s="14">
+        <v>2037</v>
+      </c>
+      <c r="H9" s="14">
+        <v>2025</v>
+      </c>
+      <c r="I9" s="14">
+        <v>2022</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="K9" s="58"/>
+      <c r="L9" s="58"/>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="L8" s="54" t="s">
+      <c r="H10" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="J10" s="49" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="48"/>
-      <c r="B9" s="22">
-        <v>5011</v>
-      </c>
-      <c r="C9" s="22">
-        <v>5007</v>
-      </c>
-      <c r="D9" s="22">
-        <v>5006</v>
-      </c>
-      <c r="E9" s="22">
-        <v>2008</v>
-      </c>
-      <c r="F9" s="22">
-        <v>2005</v>
-      </c>
-      <c r="G9" s="22">
-        <v>2037</v>
-      </c>
-      <c r="H9" s="22">
-        <v>2025</v>
-      </c>
-      <c r="I9" s="22">
-        <v>2022</v>
-      </c>
-      <c r="J9" s="22" t="s">
+      <c r="K10" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="L10" s="17" t="e">
+      <c r="L10" s="49" t="e">
         <f>B10+C10+D10+E10+F10+G10+H10+I10+J10+K10</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
+    <row r="11" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="39">
+        <f>SUM(B$10:B10)</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="39">
+        <f>SUM(C$10:C10)</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="39">
+        <f>SUM(D$10:D10)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="39">
+        <f>SUM(E$10:E10)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="39">
+        <f>SUM(F$10:F10)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="39">
+        <f>SUM(G$10:G10)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="39">
+        <f>SUM(H$10:H10)</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="39">
+        <f>SUM(I$10:I10)</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="39">
+        <f>SUM(J$10:J10)</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="39">
+        <f>SUM(K$10:K10)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="42" t="e">
+        <f>SUM(L$10:L10)</f>
+        <v>#VALUE!</v>
+      </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="2"/>
@@ -17755,300 +17994,300 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>103</v>
+      <c r="B2" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="31">
+      <c r="B3" s="19">
         <v>1001</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>105</v>
+      <c r="C3" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="34">
+      <c r="B4" s="22">
         <v>1002</v>
       </c>
-      <c r="C4" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>106</v>
+      <c r="C4" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="37">
+      <c r="B5" s="25">
         <v>1004</v>
       </c>
-      <c r="C5" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>107</v>
+      <c r="C5" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="34">
+      <c r="B6" s="22">
         <v>1005</v>
       </c>
-      <c r="C6" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" s="36" t="s">
-        <v>108</v>
+      <c r="C6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="37">
+      <c r="B7" s="25">
         <v>1006</v>
       </c>
-      <c r="C7" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>109</v>
+      <c r="C7" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="34">
+      <c r="B8" s="22">
         <v>1007</v>
       </c>
-      <c r="C8" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="D8" s="36" t="s">
-        <v>110</v>
+      <c r="C8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="37">
+      <c r="B9" s="25">
         <v>1017</v>
       </c>
-      <c r="C9" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="D9" s="39" t="s">
-        <v>111</v>
+      <c r="C9" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="34">
+      <c r="B10" s="22">
         <v>1018</v>
       </c>
-      <c r="C10" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" s="36" t="s">
-        <v>112</v>
+      <c r="C10" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="37">
+      <c r="B11" s="25">
         <v>2003</v>
       </c>
-      <c r="C11" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>114</v>
+      <c r="C11" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="34">
+      <c r="B12" s="22">
         <v>2005</v>
       </c>
-      <c r="C12" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" s="36" t="s">
-        <v>115</v>
+      <c r="C12" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="37">
+      <c r="B13" s="25">
         <v>2008</v>
       </c>
-      <c r="C13" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>116</v>
+      <c r="C13" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="34">
+      <c r="B14" s="22">
         <v>2009</v>
       </c>
-      <c r="C14" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" s="36" t="s">
-        <v>117</v>
+      <c r="C14" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="37">
+      <c r="B15" s="25">
         <v>2011</v>
       </c>
-      <c r="C15" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>119</v>
+      <c r="C15" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B16" s="34">
+      <c r="B16" s="22">
         <v>2014</v>
       </c>
-      <c r="C16" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D16" s="36" t="s">
-        <v>120</v>
+      <c r="C16" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="37">
+      <c r="B17" s="25">
         <v>2016</v>
       </c>
-      <c r="C17" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" s="39" t="s">
-        <v>121</v>
+      <c r="C17" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="34">
+      <c r="B18" s="22">
         <v>2018</v>
       </c>
-      <c r="C18" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="D18" s="36" t="s">
-        <v>122</v>
+      <c r="C18" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="37">
+      <c r="B19" s="25">
         <v>2022</v>
       </c>
-      <c r="C19" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="D19" s="39" t="s">
-        <v>123</v>
+      <c r="C19" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="34">
+      <c r="B20" s="22">
         <v>2025</v>
       </c>
-      <c r="C20" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>124</v>
+      <c r="C20" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="37">
+      <c r="B21" s="25">
         <v>2032</v>
       </c>
-      <c r="C21" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" s="39" t="s">
-        <v>125</v>
+      <c r="C21" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="34">
+      <c r="B22" s="22">
         <v>2034</v>
       </c>
-      <c r="C22" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>126</v>
+      <c r="C22" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="37">
+      <c r="B23" s="25">
         <v>2037</v>
       </c>
-      <c r="C23" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>127</v>
+      <c r="C23" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="34">
+      <c r="B24" s="22">
         <v>4010</v>
       </c>
-      <c r="C24" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="D24" s="36" t="s">
-        <v>129</v>
+      <c r="C24" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="34" x14ac:dyDescent="0.2">
-      <c r="B25" s="37">
+      <c r="B25" s="25">
         <v>4017</v>
       </c>
-      <c r="C25" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>120</v>
+      <c r="C25" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="34">
+      <c r="B26" s="22">
         <v>5006</v>
       </c>
-      <c r="C26" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="D26" s="36" t="s">
-        <v>131</v>
+      <c r="C26" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="37">
+      <c r="B27" s="25">
         <v>5007</v>
       </c>
-      <c r="C27" s="38" t="s">
-        <v>130</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>132</v>
+      <c r="C27" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="40">
+      <c r="B28" s="28">
         <v>5011</v>
       </c>
-      <c r="C28" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="D28" s="42" t="s">
-        <v>133</v>
+      <c r="C28" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/api/templates/device_and_site_summary_report/fr.xlsx
+++ b/api/templates/device_and_site_summary_report/fr.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/device_and_site_summary_report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFB1B3E-378D-CE4C-BAFE-8292B1F1CF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C39AA3-B30B-FC4A-84C4-C0E6D507737F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="760" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -621,7 +621,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -820,10 +820,53 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -833,8 +876,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -844,7 +891,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -860,7 +909,9 @@
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
@@ -870,7 +921,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
@@ -886,7 +939,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -964,27 +1017,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1037,6 +1072,29 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1317,11 +1375,11 @@
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
       <c r="H2" s="5"/>
       <c r="J2" s="2"/>
       <c r="K2" s="3"/>
@@ -1337,11 +1395,11 @@
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
       <c r="H3" s="5"/>
       <c r="J3" s="2"/>
       <c r="K3" s="3"/>
@@ -1357,9 +1415,9 @@
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
       <c r="H4" s="5"/>
       <c r="J4" s="2"/>
       <c r="K4" s="3"/>
@@ -1375,9 +1433,9 @@
       <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
       <c r="H5" s="5"/>
       <c r="J5" s="2"/>
       <c r="K5" s="3"/>
@@ -1393,9 +1451,9 @@
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
       <c r="J6" s="2"/>
       <c r="K6" s="3"/>
       <c r="L6" s="2"/>
@@ -1485,89 +1543,89 @@
       </c>
     </row>
     <row r="9" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="43" t="s">
+      <c r="D9" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="44" t="s">
+      <c r="F9" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="43" t="s">
+      <c r="G9" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="43" t="s">
+      <c r="H9" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="44" t="s">
+      <c r="I9" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="45" t="s">
+      <c r="J9" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="K9" s="45" t="s">
+      <c r="K9" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="46" t="s">
+      <c r="L9" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="M9" s="46" t="s">
+      <c r="M9" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="N9" s="46" t="s">
+      <c r="N9" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="O9" s="46" t="s">
+      <c r="O9" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="P9" s="46" t="s">
+      <c r="P9" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="Q9" s="46" t="s">
+      <c r="Q9" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="R9" s="45" t="s">
+      <c r="R9" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="S9" s="47" t="s">
+      <c r="S9" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="T9" s="47" t="s">
+      <c r="T9" s="37" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16">
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="56"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="56"/>
+      <c r="N10" s="56"/>
+      <c r="O10" s="56"/>
+      <c r="P10" s="56"/>
+      <c r="Q10" s="56"/>
+      <c r="R10" s="56"/>
+      <c r="S10" s="57">
         <f>SUM(S$9:S9)</f>
         <v>0</v>
       </c>
@@ -4716,13 +4774,13 @@
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="56" t="s">
+      <c r="C2" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
@@ -4783,64 +4841,64 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="36" t="s">
+      <c r="E9" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="36" t="s">
+      <c r="G9" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="36" t="s">
+      <c r="H9" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="I9" s="36" t="s">
+      <c r="I9" s="31" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="33"/>
-      <c r="C10" s="34" t="e">
+      <c r="B10" s="59"/>
+      <c r="C10" s="60" t="e">
         <f>AVERAGE(C$9:C9)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="59">
         <f>SUM(D$9:D9)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="59">
         <f>SUM(E$9:E9)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="59">
         <f>SUM(F$9:F9)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="34" t="e">
+      <c r="G10" s="60" t="e">
         <f>AVERAGE(G$9:G9)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10" s="59">
         <f>SUM(H$9:H9)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="35">
+      <c r="I10" s="61">
         <f>SUM(I$9:I9)</f>
         <v>0</v>
       </c>
@@ -6123,108 +6181,108 @@
       <c r="AF7" s="2"/>
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B8" s="59" t="s">
+      <c r="B8" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="59" t="s">
+      <c r="C8" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="59" t="s">
+      <c r="D8" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="59" t="s">
+      <c r="E8" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="59" t="s">
+      <c r="F8" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="59" t="s">
+      <c r="G8" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="H8" s="59" t="s">
+      <c r="H8" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="I8" s="59" t="s">
+      <c r="I8" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="59" t="s">
+      <c r="J8" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="K8" s="59" t="s">
+      <c r="K8" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="L8" s="59" t="s">
+      <c r="L8" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="59" t="s">
+      <c r="M8" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="N8" s="59" t="s">
+      <c r="N8" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="O8" s="59" t="s">
+      <c r="O8" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="P8" s="59" t="s">
+      <c r="P8" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="Q8" s="59" t="s">
+      <c r="Q8" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="R8" s="59" t="s">
+      <c r="R8" s="49" t="s">
         <v>112</v>
       </c>
-      <c r="S8" s="59" t="s">
+      <c r="S8" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="T8" s="59" t="s">
+      <c r="T8" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="U8" s="60" t="s">
+      <c r="U8" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="V8" s="61"/>
-      <c r="W8" s="61"/>
-      <c r="X8" s="61"/>
-      <c r="Y8" s="61"/>
-      <c r="Z8" s="61"/>
-      <c r="AA8" s="61"/>
-      <c r="AB8" s="61"/>
-      <c r="AC8" s="62"/>
-      <c r="AD8" s="57" t="s">
+      <c r="V8" s="51"/>
+      <c r="W8" s="51"/>
+      <c r="X8" s="51"/>
+      <c r="Y8" s="51"/>
+      <c r="Z8" s="51"/>
+      <c r="AA8" s="51"/>
+      <c r="AB8" s="51"/>
+      <c r="AC8" s="52"/>
+      <c r="AD8" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="AE8" s="57" t="s">
+      <c r="AE8" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="AF8" s="57" t="s">
+      <c r="AF8" s="47" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="58"/>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="58"/>
-      <c r="L9" s="58"/>
-      <c r="M9" s="58"/>
-      <c r="N9" s="58"/>
-      <c r="O9" s="58"/>
-      <c r="P9" s="58"/>
-      <c r="Q9" s="58"/>
-      <c r="R9" s="58"/>
-      <c r="S9" s="58"/>
-      <c r="T9" s="58"/>
+      <c r="A9" s="48"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="48"/>
+      <c r="O9" s="48"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="48"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="48"/>
       <c r="U9" s="14">
         <v>5011</v>
       </c>
@@ -6252,230 +6310,230 @@
       <c r="AC9" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="AD9" s="58"/>
-      <c r="AE9" s="58"/>
-      <c r="AF9" s="58"/>
+      <c r="AD9" s="48"/>
+      <c r="AE9" s="48"/>
+      <c r="AF9" s="48"/>
     </row>
     <row r="10" spans="1:32" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="49" t="s">
+      <c r="D10" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="49" t="s">
+      <c r="E10" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="50">
+      <c r="F10" s="40">
         <f>IFERROR(IF(A10="No data","",IF(C10=0,0,D10/C10)),0)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="49" t="s">
+      <c r="G10" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="51">
+      <c r="H10" s="41">
         <f>IFERROR(IF(A10="No data","",IF(B10&lt;&gt;0, G10/B10, 0)),0)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="49" t="s">
+      <c r="I10" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="J10" s="49" t="s">
+      <c r="J10" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="K10" s="49">
+      <c r="K10" s="39">
         <f>IFERROR(IF(A10="No data","",U10+V10+W10+X10+Y10+Z10+AA10+AB10+AC10+AD10),0)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="50">
+      <c r="L10" s="40">
         <f>IFERROR(IF(A10="No data","",IF(G10=0,0,I10/G10)),0)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="50">
+      <c r="M10" s="40">
         <f>IFERROR(IF(A10="No data","",IF(G10=0,0,J10/G10)),0)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="50">
+      <c r="N10" s="40">
         <f>IFERROR(IF(A10="No data","",IF(D10=0,0,I10/D10)),0)</f>
         <v>0</v>
       </c>
-      <c r="O10" s="50">
+      <c r="O10" s="40">
         <f>IFERROR(IF(A10="No data","",IF(G10=0,0,K10/G10)),0)</f>
         <v>0</v>
       </c>
-      <c r="P10" s="49" t="s">
+      <c r="P10" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="Q10" s="49" t="s">
+      <c r="Q10" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="R10" s="49" t="s">
+      <c r="R10" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="S10" s="50">
+      <c r="S10" s="40">
         <f>IFERROR(IF(A10="No data","",IF(I10=0,0,R10/I10)),0)</f>
         <v>0</v>
       </c>
-      <c r="T10" s="52" t="s">
+      <c r="T10" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="U10" s="49" t="s">
+      <c r="U10" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="V10" s="49" t="s">
+      <c r="V10" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="W10" s="49" t="s">
+      <c r="W10" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="X10" s="49" t="s">
+      <c r="X10" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="Y10" s="49" t="s">
+      <c r="Y10" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="Z10" s="49" t="s">
+      <c r="Z10" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="AA10" s="49" t="s">
+      <c r="AA10" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="AB10" s="49" t="s">
+      <c r="AB10" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="AC10" s="49" t="s">
+      <c r="AC10" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="AD10" s="49" t="s">
+      <c r="AD10" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="AE10" s="49" t="s">
+      <c r="AE10" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="AF10" s="49">
+      <c r="AF10" s="39">
         <f>IFERROR(IF(A10="No data","",U10+V10+W10+X10+Y10+Z10+AA10+AB10+AC10+AD10+AE10),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="62" t="s">
         <v>120</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="40">
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="64">
         <f>AVERAGE(F$10:F10)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="65">
         <f>SUM(G$10:G10)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="40">
+      <c r="H11" s="64">
         <f>AVERAGE(H$10:H10)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="41">
+      <c r="I11" s="65">
         <f>SUM(I$10:I10)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="41">
+      <c r="J11" s="65">
         <f>SUM(J$10:J10)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="41">
+      <c r="K11" s="65">
         <f>SUM(K$10:K10)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="40">
+      <c r="L11" s="64">
         <f>AVERAGE(L$10:L10)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="40">
+      <c r="M11" s="64">
         <f>AVERAGE(M$10:M10)</f>
         <v>0</v>
       </c>
-      <c r="N11" s="40">
+      <c r="N11" s="64">
         <f>AVERAGE(N$10:N10)</f>
         <v>0</v>
       </c>
-      <c r="O11" s="40">
+      <c r="O11" s="64">
         <f>AVERAGE(O$10:O10)</f>
         <v>0</v>
       </c>
-      <c r="P11" s="41">
+      <c r="P11" s="65">
         <f>SUM(P$10:P10)</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="41">
+      <c r="Q11" s="65">
         <f>SUM(Q$10:Q10)</f>
         <v>0</v>
       </c>
-      <c r="R11" s="41">
+      <c r="R11" s="65">
         <f>SUM(R$10:R10)</f>
         <v>0</v>
       </c>
-      <c r="S11" s="40">
+      <c r="S11" s="64">
         <f>AVERAGE(S$10:S10)</f>
         <v>0</v>
       </c>
-      <c r="T11" s="40" t="e">
+      <c r="T11" s="64" t="e">
         <f>AVERAGE(T$10:T10)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U11" s="41">
+      <c r="U11" s="65">
         <f>SUM(U$10:U10)</f>
         <v>0</v>
       </c>
-      <c r="V11" s="41">
+      <c r="V11" s="65">
         <f>SUM(V$10:V10)</f>
         <v>0</v>
       </c>
-      <c r="W11" s="41">
+      <c r="W11" s="65">
         <f>SUM(W$10:W10)</f>
         <v>0</v>
       </c>
-      <c r="X11" s="41">
+      <c r="X11" s="65">
         <f>SUM(X$10:X10)</f>
         <v>0</v>
       </c>
-      <c r="Y11" s="41">
+      <c r="Y11" s="65">
         <f>SUM(Y$10:Y10)</f>
         <v>0</v>
       </c>
-      <c r="Z11" s="41">
+      <c r="Z11" s="65">
         <f>SUM(Z$10:Z10)</f>
         <v>0</v>
       </c>
-      <c r="AA11" s="41">
+      <c r="AA11" s="65">
         <f>SUM(AA$10:AA10)</f>
         <v>0</v>
       </c>
-      <c r="AB11" s="41">
+      <c r="AB11" s="65">
         <f>SUM(AB$10:AB10)</f>
         <v>0</v>
       </c>
-      <c r="AC11" s="41">
+      <c r="AC11" s="65">
         <f>SUM(AC$10:AC10)</f>
         <v>0</v>
       </c>
-      <c r="AD11" s="41">
+      <c r="AD11" s="65">
         <f>SUM(AD$10:AD10)</f>
         <v>0</v>
       </c>
-      <c r="AE11" s="41">
+      <c r="AE11" s="65">
         <f>SUM(AE$10:AE10)</f>
         <v>0</v>
       </c>
-      <c r="AF11" s="41">
+      <c r="AF11" s="66">
         <f>SUM(AF$10:AF10)</f>
         <v>0</v>
       </c>
@@ -14159,6 +14217,21 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="AD8:AD9"/>
     <mergeCell ref="AE8:AE9"/>
     <mergeCell ref="AF8:AF9"/>
     <mergeCell ref="O8:O9"/>
@@ -14168,21 +14241,6 @@
     <mergeCell ref="S8:S9"/>
     <mergeCell ref="T8:T9"/>
     <mergeCell ref="U8:AC8"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
   </mergeCells>
   <conditionalFormatting sqref="H10">
     <cfRule type="notContainsBlanks" dxfId="2" priority="1">
@@ -14326,29 +14384,29 @@
       <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="63" t="s">
+      <c r="A8" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="B8" s="60" t="s">
+      <c r="B8" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="64" t="s">
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="L8" s="64" t="s">
+      <c r="L8" s="54" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="58"/>
+      <c r="A9" s="48"/>
       <c r="B9" s="14">
         <v>5011</v>
       </c>
@@ -14376,93 +14434,93 @@
       <c r="J9" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="K9" s="58"/>
-      <c r="L9" s="58"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="49" t="s">
+      <c r="D10" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="49" t="s">
+      <c r="E10" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="49" t="s">
+      <c r="F10" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="G10" s="49" t="s">
+      <c r="G10" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="H10" s="49" t="s">
+      <c r="H10" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="I10" s="49" t="s">
+      <c r="I10" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="J10" s="49" t="s">
+      <c r="J10" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="K10" s="49" t="s">
+      <c r="K10" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="L10" s="49" t="e">
+      <c r="L10" s="39" t="e">
         <f>B10+C10+D10+E10+F10+G10+H10+I10+J10+K10</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="62" t="s">
         <v>120</v>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="63">
         <f>SUM(B$10:B10)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="63">
         <f>SUM(C$10:C10)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="63">
         <f>SUM(D$10:D10)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="63">
         <f>SUM(E$10:E10)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="63">
         <f>SUM(F$10:F10)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="39">
+      <c r="G11" s="63">
         <f>SUM(G$10:G10)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="39">
+      <c r="H11" s="63">
         <f>SUM(H$10:H10)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="39">
+      <c r="I11" s="63">
         <f>SUM(I$10:I10)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="39">
+      <c r="J11" s="63">
         <f>SUM(J$10:J10)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="39">
+      <c r="K11" s="63">
         <f>SUM(K$10:K10)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="42" t="e">
+      <c r="L11" s="67" t="e">
         <f>SUM(L$10:L10)</f>
         <v>#VALUE!</v>
       </c>

--- a/api/templates/device_and_site_summary_report/fr.xlsx
+++ b/api/templates/device_and_site_summary_report/fr.xlsx
@@ -18,16 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="150">
   <si>
     <t>Rapport récapitulatif sur l’appareil et le site</t>
   </si>
   <si>
     <t>Dates: &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note:
-Les catégories de résultats sont représentées par toutes les combinaisons de résultats possibles que l’appareil envoie à Aspect. Par exemple, MTB Detected n’inclut pas les RIF détectés MTB Detected, car ils sont considérés comme des résultats différents</t>
   </si>
   <si>
     <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
@@ -58,9 +54,6 @@
   </si>
   <si>
     <t>Feuilleton</t>
-  </si>
-  <si>
-    <t>Série de l’instrument</t>
   </si>
   <si>
     <t>Dernière mise à jour des résultats</t>
@@ -121,9 +114,6 @@
   </si>
   <si>
     <t>&lt;serial&gt;</t>
-  </si>
-  <si>
-    <t>&lt;instrumentSerial&gt;</t>
   </si>
   <si>
     <t>&lt;lastUploadOn&gt;</t>
@@ -1314,16 +1304,15 @@
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="4" width="27" customWidth="1"/>
     <col min="5" max="5" width="15.1640625" customWidth="1"/>
-    <col min="6" max="6" width="31.1640625" customWidth="1"/>
-    <col min="7" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" customWidth="1"/>
-    <col min="12" max="15" width="14.33203125" customWidth="1"/>
-    <col min="16" max="16" width="13.1640625" customWidth="1"/>
-    <col min="17" max="17" width="10.5" customWidth="1"/>
-    <col min="18" max="18" width="18.1640625" customWidth="1"/>
-    <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="14" customWidth="1"/>
-    <col min="21" max="27" width="11.1640625" customWidth="1"/>
+    <col min="6" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="14" width="14.33203125" customWidth="1"/>
+    <col min="15" max="15" width="13.1640625" customWidth="1"/>
+    <col min="16" max="16" width="10.5" customWidth="1"/>
+    <col min="17" max="17" width="18.1640625" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
+    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="20" max="26" width="11.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -1333,259 +1322,246 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="3"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="3"/>
+      <c r="R1" s="3"/>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>2</v>
-      </c>
+      <c r="F2" s="5"/>
       <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="6"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="3"/>
+      <c r="H2" s="6"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="3"/>
+      <c r="R2" s="3"/>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="6"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="3"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="3"/>
+      <c r="R3" s="3"/>
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="6"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="3"/>
+      <c r="H4" s="6"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="3"/>
+      <c r="R4" s="3"/>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="6"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="3"/>
+      <c r="H5" s="6"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="3"/>
+      <c r="R5" s="3"/>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="3"/>
+      <c r="H6"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="3"/>
+      <c r="R6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="8"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="3"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="3"/>
+      <c r="R7" s="3"/>
     </row>
     <row r="8" ht="67.5" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="C8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="D8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="E8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="G8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="H8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="I8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="J8" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="K8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="L8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="M8" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="N8" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="11" t="s">
+      <c r="O8" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="P8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P8" s="11" t="s">
+      <c r="Q8" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="Q8" s="11" t="s">
+      <c r="R8" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="R8" s="11" t="s">
+      <c r="S8" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="S8" s="11" t="s">
+      <c r="T8" s="10" t="s">
         <v>26</v>
-      </c>
-      <c r="T8" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="U8" s="10" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="D9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="E9" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="F9" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="G9" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="H9" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="I9" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="J9" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="K9" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="L9" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="M9" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="N9" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="O9" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="N9" s="15" t="s">
+      <c r="P9" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="O9" s="15" t="s">
+      <c r="Q9" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="P9" s="15" t="s">
+      <c r="R9" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="Q9" s="15" t="s">
+      <c r="S9" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="R9" s="15" t="s">
+      <c r="T9" s="16" t="s">
         <v>46</v>
-      </c>
-      <c r="S9" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="T9" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="U9" s="16" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -1604,15 +1580,14 @@
       <c r="P10" s="18"/>
       <c r="Q10" s="18"/>
       <c r="R10" s="18"/>
-      <c r="S10" s="18"/>
-      <c r="T10" s="19">
+      <c r="S10" s="19">
         <f>SUM(T$9:T9)</f>
       </c>
-      <c r="U10" s="20">
+      <c r="T10" s="20">
         <f>SUM(U$9:U9)</f>
       </c>
-      <c r="V10" s="21" t="s">
-        <v>51</v>
+      <c r="U10" s="21" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
@@ -1620,2315 +1595,2314 @@
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="3"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="3"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K12" s="2"/>
-      <c r="L12" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J12" s="2"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="3"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K13" s="2"/>
-      <c r="L13" s="3"/>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J13" s="2"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="3"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K14" s="2"/>
-      <c r="L14" s="3"/>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J14" s="2"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="3"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K15" s="2"/>
-      <c r="L15" s="3"/>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J15" s="2"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="3"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K16" s="2"/>
-      <c r="L16" s="3"/>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J16" s="2"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="3"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K17" s="2"/>
-      <c r="L17" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J17" s="2"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="3"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K18" s="2"/>
-      <c r="L18" s="3"/>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J18" s="2"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="3"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K19" s="2"/>
-      <c r="L19" s="3"/>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J19" s="2"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="3"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K20" s="2"/>
-      <c r="L20" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J20" s="2"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="3"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K21" s="2"/>
-      <c r="L21" s="3"/>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J21" s="2"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="3"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K22" s="2"/>
-      <c r="L22" s="3"/>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J22" s="2"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="3"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K23" s="2"/>
-      <c r="L23" s="3"/>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J23" s="2"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
       <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="3"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K24" s="2"/>
-      <c r="L24" s="3"/>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J24" s="2"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="3"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K25" s="2"/>
-      <c r="L25" s="3"/>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J25" s="2"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="3"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K26" s="2"/>
-      <c r="L26" s="3"/>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J26" s="2"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="3"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K27" s="2"/>
-      <c r="L27" s="3"/>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J27" s="2"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="2"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="3"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K28" s="2"/>
-      <c r="L28" s="3"/>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J28" s="2"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="2"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" s="2"/>
       <c r="Q28" s="2"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="3"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K29" s="2"/>
-      <c r="L29" s="3"/>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J29" s="2"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="2"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="3"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K30" s="2"/>
-      <c r="L30" s="3"/>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J30" s="2"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="2"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="3"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K31" s="2"/>
-      <c r="L31" s="3"/>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J31" s="2"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
-      <c r="R31" s="2"/>
-      <c r="S31" s="3"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K32" s="2"/>
-      <c r="L32" s="3"/>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J32" s="2"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="2"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="3"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K33" s="2"/>
-      <c r="L33" s="3"/>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J33" s="2"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="2"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
       <c r="Q33" s="2"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="3"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K34" s="2"/>
-      <c r="L34" s="3"/>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J34" s="2"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="3"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K35" s="2"/>
-      <c r="L35" s="3"/>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J35" s="2"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="2"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
-      <c r="R35" s="2"/>
-      <c r="S35" s="3"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K36" s="2"/>
-      <c r="L36" s="3"/>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J36" s="2"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="2"/>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
-      <c r="R36" s="2"/>
-      <c r="S36" s="3"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K37" s="2"/>
-      <c r="L37" s="3"/>
+      <c r="R36" s="3"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J37" s="2"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
-      <c r="R37" s="2"/>
-      <c r="S37" s="3"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K38" s="2"/>
-      <c r="L38" s="3"/>
+      <c r="R37" s="3"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J38" s="2"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="2"/>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
       <c r="Q38" s="2"/>
-      <c r="R38" s="2"/>
-      <c r="S38" s="3"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K39" s="2"/>
-      <c r="L39" s="3"/>
+      <c r="R38" s="3"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J39" s="2"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="2"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
       <c r="Q39" s="2"/>
-      <c r="R39" s="2"/>
-      <c r="S39" s="3"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K40" s="2"/>
-      <c r="L40" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J40" s="2"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
-      <c r="R40" s="2"/>
-      <c r="S40" s="3"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K41" s="2"/>
-      <c r="L41" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J41" s="2"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="2"/>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" s="2"/>
       <c r="Q41" s="2"/>
-      <c r="R41" s="2"/>
-      <c r="S41" s="3"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K42" s="2"/>
-      <c r="L42" s="3"/>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J42" s="2"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="2"/>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
       <c r="Q42" s="2"/>
-      <c r="R42" s="2"/>
-      <c r="S42" s="3"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K43" s="2"/>
-      <c r="L43" s="3"/>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J43" s="2"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="2"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" s="2"/>
       <c r="Q43" s="2"/>
-      <c r="R43" s="2"/>
-      <c r="S43" s="3"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K44" s="2"/>
-      <c r="L44" s="3"/>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J44" s="2"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="2"/>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" s="2"/>
       <c r="Q44" s="2"/>
-      <c r="R44" s="2"/>
-      <c r="S44" s="3"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K45" s="2"/>
-      <c r="L45" s="3"/>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J45" s="2"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" s="2"/>
       <c r="Q45" s="2"/>
-      <c r="R45" s="2"/>
-      <c r="S45" s="3"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K46" s="2"/>
-      <c r="L46" s="3"/>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J46" s="2"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="2"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
       <c r="Q46" s="2"/>
-      <c r="R46" s="2"/>
-      <c r="S46" s="3"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K47" s="2"/>
-      <c r="L47" s="3"/>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J47" s="2"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="2"/>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
       <c r="Q47" s="2"/>
-      <c r="R47" s="2"/>
-      <c r="S47" s="3"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K48" s="2"/>
-      <c r="L48" s="3"/>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J48" s="2"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" s="2"/>
       <c r="Q48" s="2"/>
-      <c r="R48" s="2"/>
-      <c r="S48" s="3"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K49" s="2"/>
-      <c r="L49" s="3"/>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J49" s="2"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="2"/>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
       <c r="Q49" s="2"/>
-      <c r="R49" s="2"/>
-      <c r="S49" s="3"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K50" s="2"/>
-      <c r="L50" s="3"/>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J50" s="2"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="2"/>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" s="2"/>
       <c r="Q50" s="2"/>
-      <c r="R50" s="2"/>
-      <c r="S50" s="3"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K51" s="2"/>
-      <c r="L51" s="3"/>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J51" s="2"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
       <c r="Q51" s="2"/>
-      <c r="R51" s="2"/>
-      <c r="S51" s="3"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K52" s="2"/>
-      <c r="L52" s="3"/>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J52" s="2"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
       <c r="Q52" s="2"/>
-      <c r="R52" s="2"/>
-      <c r="S52" s="3"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K53" s="2"/>
-      <c r="L53" s="3"/>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J53" s="2"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="2"/>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" s="2"/>
       <c r="Q53" s="2"/>
-      <c r="R53" s="2"/>
-      <c r="S53" s="3"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K54" s="2"/>
-      <c r="L54" s="3"/>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J54" s="2"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" s="2"/>
       <c r="Q54" s="2"/>
-      <c r="R54" s="2"/>
-      <c r="S54" s="3"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K55" s="2"/>
-      <c r="L55" s="3"/>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J55" s="2"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="2"/>
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" s="2"/>
       <c r="Q55" s="2"/>
-      <c r="R55" s="2"/>
-      <c r="S55" s="3"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K56" s="2"/>
-      <c r="L56" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J56" s="2"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="2"/>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" s="2"/>
       <c r="Q56" s="2"/>
-      <c r="R56" s="2"/>
-      <c r="S56" s="3"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K57" s="2"/>
-      <c r="L57" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J57" s="2"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="2"/>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
       <c r="Q57" s="2"/>
-      <c r="R57" s="2"/>
-      <c r="S57" s="3"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K58" s="2"/>
-      <c r="L58" s="3"/>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J58" s="2"/>
+      <c r="K58" s="3"/>
+      <c r="L58" s="2"/>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" s="2"/>
       <c r="Q58" s="2"/>
-      <c r="R58" s="2"/>
-      <c r="S58" s="3"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K59" s="2"/>
-      <c r="L59" s="3"/>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J59" s="2"/>
+      <c r="K59" s="3"/>
+      <c r="L59" s="2"/>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" s="2"/>
       <c r="Q59" s="2"/>
-      <c r="R59" s="2"/>
-      <c r="S59" s="3"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K60" s="2"/>
-      <c r="L60" s="3"/>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J60" s="2"/>
+      <c r="K60" s="3"/>
+      <c r="L60" s="2"/>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
       <c r="Q60" s="2"/>
-      <c r="R60" s="2"/>
-      <c r="S60" s="3"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K61" s="2"/>
-      <c r="L61" s="3"/>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J61" s="2"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="2"/>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" s="2"/>
       <c r="Q61" s="2"/>
-      <c r="R61" s="2"/>
-      <c r="S61" s="3"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K62" s="2"/>
-      <c r="L62" s="3"/>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J62" s="2"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="2"/>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
       <c r="Q62" s="2"/>
-      <c r="R62" s="2"/>
-      <c r="S62" s="3"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K63" s="2"/>
-      <c r="L63" s="3"/>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J63" s="2"/>
+      <c r="K63" s="3"/>
+      <c r="L63" s="2"/>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" s="2"/>
       <c r="Q63" s="2"/>
-      <c r="R63" s="2"/>
-      <c r="S63" s="3"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K64" s="2"/>
-      <c r="L64" s="3"/>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J64" s="2"/>
+      <c r="K64" s="3"/>
+      <c r="L64" s="2"/>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
       <c r="Q64" s="2"/>
-      <c r="R64" s="2"/>
-      <c r="S64" s="3"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K65" s="2"/>
-      <c r="L65" s="3"/>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J65" s="2"/>
+      <c r="K65" s="3"/>
+      <c r="L65" s="2"/>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" s="2"/>
       <c r="Q65" s="2"/>
-      <c r="R65" s="2"/>
-      <c r="S65" s="3"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K66" s="2"/>
-      <c r="L66" s="3"/>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J66" s="2"/>
+      <c r="K66" s="3"/>
+      <c r="L66" s="2"/>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" s="2"/>
       <c r="Q66" s="2"/>
-      <c r="R66" s="2"/>
-      <c r="S66" s="3"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K67" s="2"/>
-      <c r="L67" s="3"/>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J67" s="2"/>
+      <c r="K67" s="3"/>
+      <c r="L67" s="2"/>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" s="2"/>
       <c r="Q67" s="2"/>
-      <c r="R67" s="2"/>
-      <c r="S67" s="3"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K68" s="2"/>
-      <c r="L68" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J68" s="2"/>
+      <c r="K68" s="3"/>
+      <c r="L68" s="2"/>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" s="2"/>
       <c r="Q68" s="2"/>
-      <c r="R68" s="2"/>
-      <c r="S68" s="3"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K69" s="2"/>
-      <c r="L69" s="3"/>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J69" s="2"/>
+      <c r="K69" s="3"/>
+      <c r="L69" s="2"/>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" s="2"/>
       <c r="Q69" s="2"/>
-      <c r="R69" s="2"/>
-      <c r="S69" s="3"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K70" s="2"/>
-      <c r="L70" s="3"/>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J70" s="2"/>
+      <c r="K70" s="3"/>
+      <c r="L70" s="2"/>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" s="2"/>
       <c r="Q70" s="2"/>
-      <c r="R70" s="2"/>
-      <c r="S70" s="3"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K71" s="2"/>
-      <c r="L71" s="3"/>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J71" s="2"/>
+      <c r="K71" s="3"/>
+      <c r="L71" s="2"/>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" s="2"/>
       <c r="Q71" s="2"/>
-      <c r="R71" s="2"/>
-      <c r="S71" s="3"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K72" s="2"/>
-      <c r="L72" s="3"/>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J72" s="2"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="2"/>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" s="2"/>
       <c r="Q72" s="2"/>
-      <c r="R72" s="2"/>
-      <c r="S72" s="3"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K73" s="2"/>
-      <c r="L73" s="3"/>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J73" s="2"/>
+      <c r="K73" s="3"/>
+      <c r="L73" s="2"/>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" s="2"/>
       <c r="Q73" s="2"/>
-      <c r="R73" s="2"/>
-      <c r="S73" s="3"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K74" s="2"/>
-      <c r="L74" s="3"/>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J74" s="2"/>
+      <c r="K74" s="3"/>
+      <c r="L74" s="2"/>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" s="2"/>
       <c r="Q74" s="2"/>
-      <c r="R74" s="2"/>
-      <c r="S74" s="3"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K75" s="2"/>
-      <c r="L75" s="3"/>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J75" s="2"/>
+      <c r="K75" s="3"/>
+      <c r="L75" s="2"/>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" s="2"/>
       <c r="Q75" s="2"/>
-      <c r="R75" s="2"/>
-      <c r="S75" s="3"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K76" s="2"/>
-      <c r="L76" s="3"/>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J76" s="2"/>
+      <c r="K76" s="3"/>
+      <c r="L76" s="2"/>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" s="2"/>
       <c r="Q76" s="2"/>
-      <c r="R76" s="2"/>
-      <c r="S76" s="3"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K77" s="2"/>
-      <c r="L77" s="3"/>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J77" s="2"/>
+      <c r="K77" s="3"/>
+      <c r="L77" s="2"/>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" s="2"/>
       <c r="Q77" s="2"/>
-      <c r="R77" s="2"/>
-      <c r="S77" s="3"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K78" s="2"/>
-      <c r="L78" s="3"/>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J78" s="2"/>
+      <c r="K78" s="3"/>
+      <c r="L78" s="2"/>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" s="2"/>
       <c r="Q78" s="2"/>
-      <c r="R78" s="2"/>
-      <c r="S78" s="3"/>
-    </row>
-    <row r="79" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K79" s="2"/>
-      <c r="L79" s="3"/>
+      <c r="R78" s="3"/>
+    </row>
+    <row r="79" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J79" s="2"/>
+      <c r="K79" s="3"/>
+      <c r="L79" s="2"/>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
       <c r="Q79" s="2"/>
-      <c r="R79" s="2"/>
-      <c r="S79" s="3"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K80" s="2"/>
-      <c r="L80" s="3"/>
+      <c r="R79" s="3"/>
+    </row>
+    <row r="80" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J80" s="2"/>
+      <c r="K80" s="3"/>
+      <c r="L80" s="2"/>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" s="2"/>
       <c r="Q80" s="2"/>
-      <c r="R80" s="2"/>
-      <c r="S80" s="3"/>
-    </row>
-    <row r="81" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K81" s="2"/>
-      <c r="L81" s="3"/>
+      <c r="R80" s="3"/>
+    </row>
+    <row r="81" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J81" s="2"/>
+      <c r="K81" s="3"/>
+      <c r="L81" s="2"/>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" s="2"/>
       <c r="Q81" s="2"/>
-      <c r="R81" s="2"/>
-      <c r="S81" s="3"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K82" s="2"/>
-      <c r="L82" s="3"/>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J82" s="2"/>
+      <c r="K82" s="3"/>
+      <c r="L82" s="2"/>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" s="2"/>
       <c r="Q82" s="2"/>
-      <c r="R82" s="2"/>
-      <c r="S82" s="3"/>
-    </row>
-    <row r="83" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K83" s="2"/>
-      <c r="L83" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J83" s="2"/>
+      <c r="K83" s="3"/>
+      <c r="L83" s="2"/>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" s="2"/>
       <c r="Q83" s="2"/>
-      <c r="R83" s="2"/>
-      <c r="S83" s="3"/>
-    </row>
-    <row r="84" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K84" s="2"/>
-      <c r="L84" s="3"/>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J84" s="2"/>
+      <c r="K84" s="3"/>
+      <c r="L84" s="2"/>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" s="2"/>
       <c r="Q84" s="2"/>
-      <c r="R84" s="2"/>
-      <c r="S84" s="3"/>
-    </row>
-    <row r="85" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K85" s="2"/>
-      <c r="L85" s="3"/>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J85" s="2"/>
+      <c r="K85" s="3"/>
+      <c r="L85" s="2"/>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" s="2"/>
       <c r="Q85" s="2"/>
-      <c r="R85" s="2"/>
-      <c r="S85" s="3"/>
-    </row>
-    <row r="86" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K86" s="2"/>
-      <c r="L86" s="3"/>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J86" s="2"/>
+      <c r="K86" s="3"/>
+      <c r="L86" s="2"/>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" s="2"/>
       <c r="Q86" s="2"/>
-      <c r="R86" s="2"/>
-      <c r="S86" s="3"/>
-    </row>
-    <row r="87" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K87" s="2"/>
-      <c r="L87" s="3"/>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J87" s="2"/>
+      <c r="K87" s="3"/>
+      <c r="L87" s="2"/>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" s="2"/>
       <c r="Q87" s="2"/>
-      <c r="R87" s="2"/>
-      <c r="S87" s="3"/>
-    </row>
-    <row r="88" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K88" s="2"/>
-      <c r="L88" s="3"/>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J88" s="2"/>
+      <c r="K88" s="3"/>
+      <c r="L88" s="2"/>
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" s="2"/>
       <c r="Q88" s="2"/>
-      <c r="R88" s="2"/>
-      <c r="S88" s="3"/>
-    </row>
-    <row r="89" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K89" s="2"/>
-      <c r="L89" s="3"/>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J89" s="2"/>
+      <c r="K89" s="3"/>
+      <c r="L89" s="2"/>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" s="2"/>
       <c r="Q89" s="2"/>
-      <c r="R89" s="2"/>
-      <c r="S89" s="3"/>
-    </row>
-    <row r="90" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K90" s="2"/>
-      <c r="L90" s="3"/>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J90" s="2"/>
+      <c r="K90" s="3"/>
+      <c r="L90" s="2"/>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
       <c r="Q90" s="2"/>
-      <c r="R90" s="2"/>
-      <c r="S90" s="3"/>
-    </row>
-    <row r="91" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K91" s="2"/>
-      <c r="L91" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J91" s="2"/>
+      <c r="K91" s="3"/>
+      <c r="L91" s="2"/>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
       <c r="Q91" s="2"/>
-      <c r="R91" s="2"/>
-      <c r="S91" s="3"/>
-    </row>
-    <row r="92" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K92" s="2"/>
-      <c r="L92" s="3"/>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J92" s="2"/>
+      <c r="K92" s="3"/>
+      <c r="L92" s="2"/>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
       <c r="Q92" s="2"/>
-      <c r="R92" s="2"/>
-      <c r="S92" s="3"/>
-    </row>
-    <row r="93" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K93" s="2"/>
-      <c r="L93" s="3"/>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J93" s="2"/>
+      <c r="K93" s="3"/>
+      <c r="L93" s="2"/>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" s="2"/>
       <c r="Q93" s="2"/>
-      <c r="R93" s="2"/>
-      <c r="S93" s="3"/>
-    </row>
-    <row r="94" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K94" s="2"/>
-      <c r="L94" s="3"/>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J94" s="2"/>
+      <c r="K94" s="3"/>
+      <c r="L94" s="2"/>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" s="2"/>
       <c r="Q94" s="2"/>
-      <c r="R94" s="2"/>
-      <c r="S94" s="3"/>
-    </row>
-    <row r="95" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K95" s="2"/>
-      <c r="L95" s="3"/>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J95" s="2"/>
+      <c r="K95" s="3"/>
+      <c r="L95" s="2"/>
       <c r="M95" s="2"/>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" s="2"/>
       <c r="Q95" s="2"/>
-      <c r="R95" s="2"/>
-      <c r="S95" s="3"/>
-    </row>
-    <row r="96" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K96" s="2"/>
-      <c r="L96" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J96" s="2"/>
+      <c r="K96" s="3"/>
+      <c r="L96" s="2"/>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" s="2"/>
       <c r="Q96" s="2"/>
-      <c r="R96" s="2"/>
-      <c r="S96" s="3"/>
-    </row>
-    <row r="97" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K97" s="2"/>
-      <c r="L97" s="3"/>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J97" s="2"/>
+      <c r="K97" s="3"/>
+      <c r="L97" s="2"/>
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" s="2"/>
       <c r="Q97" s="2"/>
-      <c r="R97" s="2"/>
-      <c r="S97" s="3"/>
-    </row>
-    <row r="98" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K98" s="2"/>
-      <c r="L98" s="3"/>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J98" s="2"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="2"/>
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" s="2"/>
       <c r="Q98" s="2"/>
-      <c r="R98" s="2"/>
-      <c r="S98" s="3"/>
-    </row>
-    <row r="99" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K99" s="2"/>
-      <c r="L99" s="3"/>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J99" s="2"/>
+      <c r="K99" s="3"/>
+      <c r="L99" s="2"/>
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
       <c r="Q99" s="2"/>
-      <c r="R99" s="2"/>
-      <c r="S99" s="3"/>
-    </row>
-    <row r="100" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K100" s="2"/>
-      <c r="L100" s="3"/>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J100" s="2"/>
+      <c r="K100" s="3"/>
+      <c r="L100" s="2"/>
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
       <c r="Q100" s="2"/>
-      <c r="R100" s="2"/>
-      <c r="S100" s="3"/>
-    </row>
-    <row r="101" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K101" s="2"/>
-      <c r="L101" s="3"/>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J101" s="2"/>
+      <c r="K101" s="3"/>
+      <c r="L101" s="2"/>
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" s="2"/>
       <c r="Q101" s="2"/>
-      <c r="R101" s="2"/>
-      <c r="S101" s="3"/>
-    </row>
-    <row r="102" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K102" s="2"/>
-      <c r="L102" s="3"/>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J102" s="2"/>
+      <c r="K102" s="3"/>
+      <c r="L102" s="2"/>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" s="2"/>
       <c r="Q102" s="2"/>
-      <c r="R102" s="2"/>
-      <c r="S102" s="3"/>
-    </row>
-    <row r="103" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K103" s="2"/>
-      <c r="L103" s="3"/>
+      <c r="R102" s="3"/>
+    </row>
+    <row r="103" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J103" s="2"/>
+      <c r="K103" s="3"/>
+      <c r="L103" s="2"/>
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" s="2"/>
       <c r="Q103" s="2"/>
-      <c r="R103" s="2"/>
-      <c r="S103" s="3"/>
-    </row>
-    <row r="104" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K104" s="2"/>
-      <c r="L104" s="3"/>
+      <c r="R103" s="3"/>
+    </row>
+    <row r="104" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J104" s="2"/>
+      <c r="K104" s="3"/>
+      <c r="L104" s="2"/>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" s="2"/>
       <c r="Q104" s="2"/>
-      <c r="R104" s="2"/>
-      <c r="S104" s="3"/>
-    </row>
-    <row r="105" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K105" s="2"/>
-      <c r="L105" s="3"/>
+      <c r="R104" s="3"/>
+    </row>
+    <row r="105" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J105" s="2"/>
+      <c r="K105" s="3"/>
+      <c r="L105" s="2"/>
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" s="2"/>
       <c r="Q105" s="2"/>
-      <c r="R105" s="2"/>
-      <c r="S105" s="3"/>
-    </row>
-    <row r="106" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K106" s="2"/>
-      <c r="L106" s="3"/>
+      <c r="R105" s="3"/>
+    </row>
+    <row r="106" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J106" s="2"/>
+      <c r="K106" s="3"/>
+      <c r="L106" s="2"/>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" s="2"/>
       <c r="Q106" s="2"/>
-      <c r="R106" s="2"/>
-      <c r="S106" s="3"/>
-    </row>
-    <row r="107" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K107" s="2"/>
-      <c r="L107" s="3"/>
+      <c r="R106" s="3"/>
+    </row>
+    <row r="107" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J107" s="2"/>
+      <c r="K107" s="3"/>
+      <c r="L107" s="2"/>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" s="2"/>
       <c r="Q107" s="2"/>
-      <c r="R107" s="2"/>
-      <c r="S107" s="3"/>
-    </row>
-    <row r="108" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K108" s="2"/>
-      <c r="L108" s="3"/>
+      <c r="R107" s="3"/>
+    </row>
+    <row r="108" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J108" s="2"/>
+      <c r="K108" s="3"/>
+      <c r="L108" s="2"/>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" s="2"/>
       <c r="Q108" s="2"/>
-      <c r="R108" s="2"/>
-      <c r="S108" s="3"/>
-    </row>
-    <row r="109" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K109" s="2"/>
-      <c r="L109" s="3"/>
+      <c r="R108" s="3"/>
+    </row>
+    <row r="109" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J109" s="2"/>
+      <c r="K109" s="3"/>
+      <c r="L109" s="2"/>
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" s="2"/>
       <c r="Q109" s="2"/>
-      <c r="R109" s="2"/>
-      <c r="S109" s="3"/>
-    </row>
-    <row r="110" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K110" s="2"/>
-      <c r="L110" s="3"/>
+      <c r="R109" s="3"/>
+    </row>
+    <row r="110" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J110" s="2"/>
+      <c r="K110" s="3"/>
+      <c r="L110" s="2"/>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" s="2"/>
       <c r="Q110" s="2"/>
-      <c r="R110" s="2"/>
-      <c r="S110" s="3"/>
-    </row>
-    <row r="111" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K111" s="2"/>
-      <c r="L111" s="3"/>
+      <c r="R110" s="3"/>
+    </row>
+    <row r="111" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J111" s="2"/>
+      <c r="K111" s="3"/>
+      <c r="L111" s="2"/>
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" s="2"/>
       <c r="Q111" s="2"/>
-      <c r="R111" s="2"/>
-      <c r="S111" s="3"/>
-    </row>
-    <row r="112" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K112" s="2"/>
-      <c r="L112" s="3"/>
+      <c r="R111" s="3"/>
+    </row>
+    <row r="112" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J112" s="2"/>
+      <c r="K112" s="3"/>
+      <c r="L112" s="2"/>
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" s="2"/>
       <c r="Q112" s="2"/>
-      <c r="R112" s="2"/>
-      <c r="S112" s="3"/>
-    </row>
-    <row r="113" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K113" s="2"/>
-      <c r="L113" s="3"/>
+      <c r="R112" s="3"/>
+    </row>
+    <row r="113" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J113" s="2"/>
+      <c r="K113" s="3"/>
+      <c r="L113" s="2"/>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" s="2"/>
       <c r="Q113" s="2"/>
-      <c r="R113" s="2"/>
-      <c r="S113" s="3"/>
-    </row>
-    <row r="114" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K114" s="2"/>
-      <c r="L114" s="3"/>
+      <c r="R113" s="3"/>
+    </row>
+    <row r="114" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J114" s="2"/>
+      <c r="K114" s="3"/>
+      <c r="L114" s="2"/>
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" s="2"/>
       <c r="Q114" s="2"/>
-      <c r="R114" s="2"/>
-      <c r="S114" s="3"/>
-    </row>
-    <row r="115" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K115" s="2"/>
-      <c r="L115" s="3"/>
+      <c r="R114" s="3"/>
+    </row>
+    <row r="115" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J115" s="2"/>
+      <c r="K115" s="3"/>
+      <c r="L115" s="2"/>
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" s="2"/>
       <c r="Q115" s="2"/>
-      <c r="R115" s="2"/>
-      <c r="S115" s="3"/>
-    </row>
-    <row r="116" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K116" s="2"/>
-      <c r="L116" s="3"/>
+      <c r="R115" s="3"/>
+    </row>
+    <row r="116" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J116" s="2"/>
+      <c r="K116" s="3"/>
+      <c r="L116" s="2"/>
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" s="2"/>
       <c r="Q116" s="2"/>
-      <c r="R116" s="2"/>
-      <c r="S116" s="3"/>
-    </row>
-    <row r="117" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K117" s="2"/>
-      <c r="L117" s="3"/>
+      <c r="R116" s="3"/>
+    </row>
+    <row r="117" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J117" s="2"/>
+      <c r="K117" s="3"/>
+      <c r="L117" s="2"/>
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" s="2"/>
       <c r="Q117" s="2"/>
-      <c r="R117" s="2"/>
-      <c r="S117" s="3"/>
-    </row>
-    <row r="118" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K118" s="2"/>
-      <c r="L118" s="3"/>
+      <c r="R117" s="3"/>
+    </row>
+    <row r="118" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J118" s="2"/>
+      <c r="K118" s="3"/>
+      <c r="L118" s="2"/>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" s="2"/>
       <c r="Q118" s="2"/>
-      <c r="R118" s="2"/>
-      <c r="S118" s="3"/>
-    </row>
-    <row r="119" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K119" s="2"/>
-      <c r="L119" s="3"/>
+      <c r="R118" s="3"/>
+    </row>
+    <row r="119" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J119" s="2"/>
+      <c r="K119" s="3"/>
+      <c r="L119" s="2"/>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" s="2"/>
       <c r="Q119" s="2"/>
-      <c r="R119" s="2"/>
-      <c r="S119" s="3"/>
-    </row>
-    <row r="120" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K120" s="2"/>
-      <c r="L120" s="3"/>
+      <c r="R119" s="3"/>
+    </row>
+    <row r="120" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J120" s="2"/>
+      <c r="K120" s="3"/>
+      <c r="L120" s="2"/>
       <c r="M120" s="2"/>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
       <c r="P120" s="2"/>
       <c r="Q120" s="2"/>
-      <c r="R120" s="2"/>
-      <c r="S120" s="3"/>
-    </row>
-    <row r="121" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K121" s="2"/>
-      <c r="L121" s="3"/>
+      <c r="R120" s="3"/>
+    </row>
+    <row r="121" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J121" s="2"/>
+      <c r="K121" s="3"/>
+      <c r="L121" s="2"/>
       <c r="M121" s="2"/>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" s="2"/>
       <c r="Q121" s="2"/>
-      <c r="R121" s="2"/>
-      <c r="S121" s="3"/>
-    </row>
-    <row r="122" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K122" s="2"/>
-      <c r="L122" s="3"/>
+      <c r="R121" s="3"/>
+    </row>
+    <row r="122" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J122" s="2"/>
+      <c r="K122" s="3"/>
+      <c r="L122" s="2"/>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" s="2"/>
       <c r="Q122" s="2"/>
-      <c r="R122" s="2"/>
-      <c r="S122" s="3"/>
-    </row>
-    <row r="123" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K123" s="2"/>
-      <c r="L123" s="3"/>
+      <c r="R122" s="3"/>
+    </row>
+    <row r="123" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J123" s="2"/>
+      <c r="K123" s="3"/>
+      <c r="L123" s="2"/>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" s="2"/>
       <c r="Q123" s="2"/>
-      <c r="R123" s="2"/>
-      <c r="S123" s="3"/>
-    </row>
-    <row r="124" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K124" s="2"/>
-      <c r="L124" s="3"/>
+      <c r="R123" s="3"/>
+    </row>
+    <row r="124" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J124" s="2"/>
+      <c r="K124" s="3"/>
+      <c r="L124" s="2"/>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" s="2"/>
       <c r="Q124" s="2"/>
-      <c r="R124" s="2"/>
-      <c r="S124" s="3"/>
-    </row>
-    <row r="125" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K125" s="2"/>
-      <c r="L125" s="3"/>
+      <c r="R124" s="3"/>
+    </row>
+    <row r="125" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J125" s="2"/>
+      <c r="K125" s="3"/>
+      <c r="L125" s="2"/>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" s="2"/>
       <c r="Q125" s="2"/>
-      <c r="R125" s="2"/>
-      <c r="S125" s="3"/>
-    </row>
-    <row r="126" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K126" s="2"/>
-      <c r="L126" s="3"/>
+      <c r="R125" s="3"/>
+    </row>
+    <row r="126" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J126" s="2"/>
+      <c r="K126" s="3"/>
+      <c r="L126" s="2"/>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
       <c r="P126" s="2"/>
       <c r="Q126" s="2"/>
-      <c r="R126" s="2"/>
-      <c r="S126" s="3"/>
-    </row>
-    <row r="127" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K127" s="2"/>
-      <c r="L127" s="3"/>
+      <c r="R126" s="3"/>
+    </row>
+    <row r="127" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J127" s="2"/>
+      <c r="K127" s="3"/>
+      <c r="L127" s="2"/>
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" s="2"/>
       <c r="Q127" s="2"/>
-      <c r="R127" s="2"/>
-      <c r="S127" s="3"/>
-    </row>
-    <row r="128" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K128" s="2"/>
-      <c r="L128" s="3"/>
+      <c r="R127" s="3"/>
+    </row>
+    <row r="128" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J128" s="2"/>
+      <c r="K128" s="3"/>
+      <c r="L128" s="2"/>
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" s="2"/>
       <c r="Q128" s="2"/>
-      <c r="R128" s="2"/>
-      <c r="S128" s="3"/>
-    </row>
-    <row r="129" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K129" s="2"/>
-      <c r="L129" s="3"/>
+      <c r="R128" s="3"/>
+    </row>
+    <row r="129" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J129" s="2"/>
+      <c r="K129" s="3"/>
+      <c r="L129" s="2"/>
       <c r="M129" s="2"/>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
       <c r="P129" s="2"/>
       <c r="Q129" s="2"/>
-      <c r="R129" s="2"/>
-      <c r="S129" s="3"/>
-    </row>
-    <row r="130" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K130" s="2"/>
-      <c r="L130" s="3"/>
+      <c r="R129" s="3"/>
+    </row>
+    <row r="130" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J130" s="2"/>
+      <c r="K130" s="3"/>
+      <c r="L130" s="2"/>
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" s="2"/>
       <c r="Q130" s="2"/>
-      <c r="R130" s="2"/>
-      <c r="S130" s="3"/>
-    </row>
-    <row r="131" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K131" s="2"/>
-      <c r="L131" s="3"/>
+      <c r="R130" s="3"/>
+    </row>
+    <row r="131" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J131" s="2"/>
+      <c r="K131" s="3"/>
+      <c r="L131" s="2"/>
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" s="2"/>
       <c r="Q131" s="2"/>
-      <c r="R131" s="2"/>
-      <c r="S131" s="3"/>
-    </row>
-    <row r="132" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K132" s="2"/>
-      <c r="L132" s="3"/>
+      <c r="R131" s="3"/>
+    </row>
+    <row r="132" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J132" s="2"/>
+      <c r="K132" s="3"/>
+      <c r="L132" s="2"/>
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" s="2"/>
       <c r="Q132" s="2"/>
-      <c r="R132" s="2"/>
-      <c r="S132" s="3"/>
-    </row>
-    <row r="133" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K133" s="2"/>
-      <c r="L133" s="3"/>
+      <c r="R132" s="3"/>
+    </row>
+    <row r="133" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J133" s="2"/>
+      <c r="K133" s="3"/>
+      <c r="L133" s="2"/>
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" s="2"/>
       <c r="Q133" s="2"/>
-      <c r="R133" s="2"/>
-      <c r="S133" s="3"/>
-    </row>
-    <row r="134" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K134" s="2"/>
-      <c r="L134" s="3"/>
+      <c r="R133" s="3"/>
+    </row>
+    <row r="134" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J134" s="2"/>
+      <c r="K134" s="3"/>
+      <c r="L134" s="2"/>
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" s="2"/>
       <c r="Q134" s="2"/>
-      <c r="R134" s="2"/>
-      <c r="S134" s="3"/>
-    </row>
-    <row r="135" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K135" s="2"/>
-      <c r="L135" s="3"/>
+      <c r="R134" s="3"/>
+    </row>
+    <row r="135" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J135" s="2"/>
+      <c r="K135" s="3"/>
+      <c r="L135" s="2"/>
       <c r="M135" s="2"/>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
       <c r="P135" s="2"/>
       <c r="Q135" s="2"/>
-      <c r="R135" s="2"/>
-      <c r="S135" s="3"/>
-    </row>
-    <row r="136" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K136" s="2"/>
-      <c r="L136" s="3"/>
+      <c r="R135" s="3"/>
+    </row>
+    <row r="136" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J136" s="2"/>
+      <c r="K136" s="3"/>
+      <c r="L136" s="2"/>
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
       <c r="P136" s="2"/>
       <c r="Q136" s="2"/>
-      <c r="R136" s="2"/>
-      <c r="S136" s="3"/>
-    </row>
-    <row r="137" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K137" s="2"/>
-      <c r="L137" s="3"/>
+      <c r="R136" s="3"/>
+    </row>
+    <row r="137" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J137" s="2"/>
+      <c r="K137" s="3"/>
+      <c r="L137" s="2"/>
       <c r="M137" s="2"/>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" s="2"/>
       <c r="Q137" s="2"/>
-      <c r="R137" s="2"/>
-      <c r="S137" s="3"/>
-    </row>
-    <row r="138" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K138" s="2"/>
-      <c r="L138" s="3"/>
+      <c r="R137" s="3"/>
+    </row>
+    <row r="138" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J138" s="2"/>
+      <c r="K138" s="3"/>
+      <c r="L138" s="2"/>
       <c r="M138" s="2"/>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" s="2"/>
       <c r="Q138" s="2"/>
-      <c r="R138" s="2"/>
-      <c r="S138" s="3"/>
-    </row>
-    <row r="139" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K139" s="2"/>
-      <c r="L139" s="3"/>
+      <c r="R138" s="3"/>
+    </row>
+    <row r="139" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J139" s="2"/>
+      <c r="K139" s="3"/>
+      <c r="L139" s="2"/>
       <c r="M139" s="2"/>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" s="2"/>
       <c r="Q139" s="2"/>
-      <c r="R139" s="2"/>
-      <c r="S139" s="3"/>
-    </row>
-    <row r="140" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K140" s="2"/>
-      <c r="L140" s="3"/>
+      <c r="R139" s="3"/>
+    </row>
+    <row r="140" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J140" s="2"/>
+      <c r="K140" s="3"/>
+      <c r="L140" s="2"/>
       <c r="M140" s="2"/>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
       <c r="P140" s="2"/>
       <c r="Q140" s="2"/>
-      <c r="R140" s="2"/>
-      <c r="S140" s="3"/>
-    </row>
-    <row r="141" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K141" s="2"/>
-      <c r="L141" s="3"/>
+      <c r="R140" s="3"/>
+    </row>
+    <row r="141" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J141" s="2"/>
+      <c r="K141" s="3"/>
+      <c r="L141" s="2"/>
       <c r="M141" s="2"/>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" s="2"/>
       <c r="Q141" s="2"/>
-      <c r="R141" s="2"/>
-      <c r="S141" s="3"/>
-    </row>
-    <row r="142" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K142" s="2"/>
-      <c r="L142" s="3"/>
+      <c r="R141" s="3"/>
+    </row>
+    <row r="142" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J142" s="2"/>
+      <c r="K142" s="3"/>
+      <c r="L142" s="2"/>
       <c r="M142" s="2"/>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
       <c r="P142" s="2"/>
       <c r="Q142" s="2"/>
-      <c r="R142" s="2"/>
-      <c r="S142" s="3"/>
-    </row>
-    <row r="143" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K143" s="2"/>
-      <c r="L143" s="3"/>
+      <c r="R142" s="3"/>
+    </row>
+    <row r="143" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J143" s="2"/>
+      <c r="K143" s="3"/>
+      <c r="L143" s="2"/>
       <c r="M143" s="2"/>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
       <c r="P143" s="2"/>
       <c r="Q143" s="2"/>
-      <c r="R143" s="2"/>
-      <c r="S143" s="3"/>
-    </row>
-    <row r="144" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K144" s="2"/>
-      <c r="L144" s="3"/>
+      <c r="R143" s="3"/>
+    </row>
+    <row r="144" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J144" s="2"/>
+      <c r="K144" s="3"/>
+      <c r="L144" s="2"/>
       <c r="M144" s="2"/>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" s="2"/>
       <c r="Q144" s="2"/>
-      <c r="R144" s="2"/>
-      <c r="S144" s="3"/>
-    </row>
-    <row r="145" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K145" s="2"/>
-      <c r="L145" s="3"/>
+      <c r="R144" s="3"/>
+    </row>
+    <row r="145" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J145" s="2"/>
+      <c r="K145" s="3"/>
+      <c r="L145" s="2"/>
       <c r="M145" s="2"/>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
       <c r="P145" s="2"/>
       <c r="Q145" s="2"/>
-      <c r="R145" s="2"/>
-      <c r="S145" s="3"/>
-    </row>
-    <row r="146" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K146" s="2"/>
-      <c r="L146" s="3"/>
+      <c r="R145" s="3"/>
+    </row>
+    <row r="146" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J146" s="2"/>
+      <c r="K146" s="3"/>
+      <c r="L146" s="2"/>
       <c r="M146" s="2"/>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
       <c r="P146" s="2"/>
       <c r="Q146" s="2"/>
-      <c r="R146" s="2"/>
-      <c r="S146" s="3"/>
-    </row>
-    <row r="147" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K147" s="2"/>
-      <c r="L147" s="3"/>
+      <c r="R146" s="3"/>
+    </row>
+    <row r="147" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J147" s="2"/>
+      <c r="K147" s="3"/>
+      <c r="L147" s="2"/>
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
       <c r="P147" s="2"/>
       <c r="Q147" s="2"/>
-      <c r="R147" s="2"/>
-      <c r="S147" s="3"/>
-    </row>
-    <row r="148" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K148" s="2"/>
-      <c r="L148" s="3"/>
+      <c r="R147" s="3"/>
+    </row>
+    <row r="148" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J148" s="2"/>
+      <c r="K148" s="3"/>
+      <c r="L148" s="2"/>
       <c r="M148" s="2"/>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" s="2"/>
       <c r="Q148" s="2"/>
-      <c r="R148" s="2"/>
-      <c r="S148" s="3"/>
-    </row>
-    <row r="149" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K149" s="2"/>
-      <c r="L149" s="3"/>
+      <c r="R148" s="3"/>
+    </row>
+    <row r="149" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J149" s="2"/>
+      <c r="K149" s="3"/>
+      <c r="L149" s="2"/>
       <c r="M149" s="2"/>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
       <c r="P149" s="2"/>
       <c r="Q149" s="2"/>
-      <c r="R149" s="2"/>
-      <c r="S149" s="3"/>
-    </row>
-    <row r="150" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K150" s="2"/>
-      <c r="L150" s="3"/>
+      <c r="R149" s="3"/>
+    </row>
+    <row r="150" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J150" s="2"/>
+      <c r="K150" s="3"/>
+      <c r="L150" s="2"/>
       <c r="M150" s="2"/>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" s="2"/>
       <c r="Q150" s="2"/>
-      <c r="R150" s="2"/>
-      <c r="S150" s="3"/>
-    </row>
-    <row r="151" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K151" s="2"/>
-      <c r="L151" s="3"/>
+      <c r="R150" s="3"/>
+    </row>
+    <row r="151" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J151" s="2"/>
+      <c r="K151" s="3"/>
+      <c r="L151" s="2"/>
       <c r="M151" s="2"/>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" s="2"/>
       <c r="Q151" s="2"/>
-      <c r="R151" s="2"/>
-      <c r="S151" s="3"/>
-    </row>
-    <row r="152" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K152" s="2"/>
-      <c r="L152" s="3"/>
+      <c r="R151" s="3"/>
+    </row>
+    <row r="152" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J152" s="2"/>
+      <c r="K152" s="3"/>
+      <c r="L152" s="2"/>
       <c r="M152" s="2"/>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
       <c r="P152" s="2"/>
       <c r="Q152" s="2"/>
-      <c r="R152" s="2"/>
-      <c r="S152" s="3"/>
-    </row>
-    <row r="153" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K153" s="2"/>
-      <c r="L153" s="3"/>
+      <c r="R152" s="3"/>
+    </row>
+    <row r="153" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J153" s="2"/>
+      <c r="K153" s="3"/>
+      <c r="L153" s="2"/>
       <c r="M153" s="2"/>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" s="2"/>
       <c r="Q153" s="2"/>
-      <c r="R153" s="2"/>
-      <c r="S153" s="3"/>
-    </row>
-    <row r="154" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K154" s="2"/>
-      <c r="L154" s="3"/>
+      <c r="R153" s="3"/>
+    </row>
+    <row r="154" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J154" s="2"/>
+      <c r="K154" s="3"/>
+      <c r="L154" s="2"/>
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
       <c r="P154" s="2"/>
       <c r="Q154" s="2"/>
-      <c r="R154" s="2"/>
-      <c r="S154" s="3"/>
-    </row>
-    <row r="155" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K155" s="2"/>
-      <c r="L155" s="3"/>
+      <c r="R154" s="3"/>
+    </row>
+    <row r="155" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J155" s="2"/>
+      <c r="K155" s="3"/>
+      <c r="L155" s="2"/>
       <c r="M155" s="2"/>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
       <c r="P155" s="2"/>
       <c r="Q155" s="2"/>
-      <c r="R155" s="2"/>
-      <c r="S155" s="3"/>
-    </row>
-    <row r="156" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K156" s="2"/>
-      <c r="L156" s="3"/>
+      <c r="R155" s="3"/>
+    </row>
+    <row r="156" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J156" s="2"/>
+      <c r="K156" s="3"/>
+      <c r="L156" s="2"/>
       <c r="M156" s="2"/>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
       <c r="P156" s="2"/>
       <c r="Q156" s="2"/>
-      <c r="R156" s="2"/>
-      <c r="S156" s="3"/>
-    </row>
-    <row r="157" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K157" s="2"/>
-      <c r="L157" s="3"/>
+      <c r="R156" s="3"/>
+    </row>
+    <row r="157" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J157" s="2"/>
+      <c r="K157" s="3"/>
+      <c r="L157" s="2"/>
       <c r="M157" s="2"/>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
       <c r="P157" s="2"/>
       <c r="Q157" s="2"/>
-      <c r="R157" s="2"/>
-      <c r="S157" s="3"/>
-    </row>
-    <row r="158" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K158" s="2"/>
-      <c r="L158" s="3"/>
+      <c r="R157" s="3"/>
+    </row>
+    <row r="158" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J158" s="2"/>
+      <c r="K158" s="3"/>
+      <c r="L158" s="2"/>
       <c r="M158" s="2"/>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" s="2"/>
       <c r="Q158" s="2"/>
-      <c r="R158" s="2"/>
-      <c r="S158" s="3"/>
-    </row>
-    <row r="159" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K159" s="2"/>
-      <c r="L159" s="3"/>
+      <c r="R158" s="3"/>
+    </row>
+    <row r="159" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J159" s="2"/>
+      <c r="K159" s="3"/>
+      <c r="L159" s="2"/>
       <c r="M159" s="2"/>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
       <c r="P159" s="2"/>
       <c r="Q159" s="2"/>
-      <c r="R159" s="2"/>
-      <c r="S159" s="3"/>
-    </row>
-    <row r="160" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K160" s="2"/>
-      <c r="L160" s="3"/>
+      <c r="R159" s="3"/>
+    </row>
+    <row r="160" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J160" s="2"/>
+      <c r="K160" s="3"/>
+      <c r="L160" s="2"/>
       <c r="M160" s="2"/>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
       <c r="P160" s="2"/>
       <c r="Q160" s="2"/>
-      <c r="R160" s="2"/>
-      <c r="S160" s="3"/>
-    </row>
-    <row r="161" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K161" s="2"/>
-      <c r="L161" s="3"/>
+      <c r="R160" s="3"/>
+    </row>
+    <row r="161" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J161" s="2"/>
+      <c r="K161" s="3"/>
+      <c r="L161" s="2"/>
       <c r="M161" s="2"/>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
       <c r="P161" s="2"/>
       <c r="Q161" s="2"/>
-      <c r="R161" s="2"/>
-      <c r="S161" s="3"/>
-    </row>
-    <row r="162" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K162" s="2"/>
-      <c r="L162" s="3"/>
+      <c r="R161" s="3"/>
+    </row>
+    <row r="162" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J162" s="2"/>
+      <c r="K162" s="3"/>
+      <c r="L162" s="2"/>
       <c r="M162" s="2"/>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
       <c r="P162" s="2"/>
       <c r="Q162" s="2"/>
-      <c r="R162" s="2"/>
-      <c r="S162" s="3"/>
-    </row>
-    <row r="163" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K163" s="2"/>
-      <c r="L163" s="3"/>
+      <c r="R162" s="3"/>
+    </row>
+    <row r="163" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J163" s="2"/>
+      <c r="K163" s="3"/>
+      <c r="L163" s="2"/>
       <c r="M163" s="2"/>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
       <c r="P163" s="2"/>
       <c r="Q163" s="2"/>
-      <c r="R163" s="2"/>
-      <c r="S163" s="3"/>
-    </row>
-    <row r="164" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K164" s="2"/>
-      <c r="L164" s="3"/>
+      <c r="R163" s="3"/>
+    </row>
+    <row r="164" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J164" s="2"/>
+      <c r="K164" s="3"/>
+      <c r="L164" s="2"/>
       <c r="M164" s="2"/>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
       <c r="P164" s="2"/>
       <c r="Q164" s="2"/>
-      <c r="R164" s="2"/>
-      <c r="S164" s="3"/>
-    </row>
-    <row r="165" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K165" s="2"/>
-      <c r="L165" s="3"/>
+      <c r="R164" s="3"/>
+    </row>
+    <row r="165" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J165" s="2"/>
+      <c r="K165" s="3"/>
+      <c r="L165" s="2"/>
       <c r="M165" s="2"/>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
       <c r="P165" s="2"/>
       <c r="Q165" s="2"/>
-      <c r="R165" s="2"/>
-      <c r="S165" s="3"/>
-    </row>
-    <row r="166" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K166" s="2"/>
-      <c r="L166" s="3"/>
+      <c r="R165" s="3"/>
+    </row>
+    <row r="166" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J166" s="2"/>
+      <c r="K166" s="3"/>
+      <c r="L166" s="2"/>
       <c r="M166" s="2"/>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
       <c r="P166" s="2"/>
       <c r="Q166" s="2"/>
-      <c r="R166" s="2"/>
-      <c r="S166" s="3"/>
-    </row>
-    <row r="167" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K167" s="2"/>
-      <c r="L167" s="3"/>
+      <c r="R166" s="3"/>
+    </row>
+    <row r="167" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J167" s="2"/>
+      <c r="K167" s="3"/>
+      <c r="L167" s="2"/>
       <c r="M167" s="2"/>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
       <c r="P167" s="2"/>
       <c r="Q167" s="2"/>
-      <c r="R167" s="2"/>
-      <c r="S167" s="3"/>
-    </row>
-    <row r="168" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K168" s="2"/>
-      <c r="L168" s="3"/>
+      <c r="R167" s="3"/>
+    </row>
+    <row r="168" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J168" s="2"/>
+      <c r="K168" s="3"/>
+      <c r="L168" s="2"/>
       <c r="M168" s="2"/>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
       <c r="P168" s="2"/>
       <c r="Q168" s="2"/>
-      <c r="R168" s="2"/>
-      <c r="S168" s="3"/>
-    </row>
-    <row r="169" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K169" s="2"/>
-      <c r="L169" s="3"/>
+      <c r="R168" s="3"/>
+    </row>
+    <row r="169" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J169" s="2"/>
+      <c r="K169" s="3"/>
+      <c r="L169" s="2"/>
       <c r="M169" s="2"/>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
       <c r="P169" s="2"/>
       <c r="Q169" s="2"/>
-      <c r="R169" s="2"/>
-      <c r="S169" s="3"/>
-    </row>
-    <row r="170" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K170" s="2"/>
-      <c r="L170" s="3"/>
+      <c r="R169" s="3"/>
+    </row>
+    <row r="170" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J170" s="2"/>
+      <c r="K170" s="3"/>
+      <c r="L170" s="2"/>
       <c r="M170" s="2"/>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
       <c r="P170" s="2"/>
       <c r="Q170" s="2"/>
-      <c r="R170" s="2"/>
-      <c r="S170" s="3"/>
-    </row>
-    <row r="171" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K171" s="2"/>
-      <c r="L171" s="3"/>
+      <c r="R170" s="3"/>
+    </row>
+    <row r="171" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J171" s="2"/>
+      <c r="K171" s="3"/>
+      <c r="L171" s="2"/>
       <c r="M171" s="2"/>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
       <c r="P171" s="2"/>
       <c r="Q171" s="2"/>
-      <c r="R171" s="2"/>
-      <c r="S171" s="3"/>
-    </row>
-    <row r="172" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K172" s="2"/>
-      <c r="L172" s="3"/>
+      <c r="R171" s="3"/>
+    </row>
+    <row r="172" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J172" s="2"/>
+      <c r="K172" s="3"/>
+      <c r="L172" s="2"/>
       <c r="M172" s="2"/>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
       <c r="P172" s="2"/>
       <c r="Q172" s="2"/>
-      <c r="R172" s="2"/>
-      <c r="S172" s="3"/>
-    </row>
-    <row r="173" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K173" s="2"/>
-      <c r="L173" s="3"/>
+      <c r="R172" s="3"/>
+    </row>
+    <row r="173" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J173" s="2"/>
+      <c r="K173" s="3"/>
+      <c r="L173" s="2"/>
       <c r="M173" s="2"/>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
       <c r="P173" s="2"/>
       <c r="Q173" s="2"/>
-      <c r="R173" s="2"/>
-      <c r="S173" s="3"/>
-    </row>
-    <row r="174" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K174" s="2"/>
-      <c r="L174" s="3"/>
+      <c r="R173" s="3"/>
+    </row>
+    <row r="174" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J174" s="2"/>
+      <c r="K174" s="3"/>
+      <c r="L174" s="2"/>
       <c r="M174" s="2"/>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
       <c r="P174" s="2"/>
       <c r="Q174" s="2"/>
-      <c r="R174" s="2"/>
-      <c r="S174" s="3"/>
-    </row>
-    <row r="175" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K175" s="2"/>
-      <c r="L175" s="3"/>
+      <c r="R174" s="3"/>
+    </row>
+    <row r="175" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J175" s="2"/>
+      <c r="K175" s="3"/>
+      <c r="L175" s="2"/>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" s="2"/>
       <c r="Q175" s="2"/>
-      <c r="R175" s="2"/>
-      <c r="S175" s="3"/>
-    </row>
-    <row r="176" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K176" s="2"/>
-      <c r="L176" s="3"/>
+      <c r="R175" s="3"/>
+    </row>
+    <row r="176" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J176" s="2"/>
+      <c r="K176" s="3"/>
+      <c r="L176" s="2"/>
       <c r="M176" s="2"/>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
       <c r="P176" s="2"/>
       <c r="Q176" s="2"/>
-      <c r="R176" s="2"/>
-      <c r="S176" s="3"/>
-    </row>
-    <row r="177" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K177" s="2"/>
-      <c r="L177" s="3"/>
+      <c r="R176" s="3"/>
+    </row>
+    <row r="177" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J177" s="2"/>
+      <c r="K177" s="3"/>
+      <c r="L177" s="2"/>
       <c r="M177" s="2"/>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
       <c r="P177" s="2"/>
       <c r="Q177" s="2"/>
-      <c r="R177" s="2"/>
-      <c r="S177" s="3"/>
-    </row>
-    <row r="178" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K178" s="2"/>
-      <c r="L178" s="3"/>
+      <c r="R177" s="3"/>
+    </row>
+    <row r="178" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J178" s="2"/>
+      <c r="K178" s="3"/>
+      <c r="L178" s="2"/>
       <c r="M178" s="2"/>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
       <c r="P178" s="2"/>
       <c r="Q178" s="2"/>
-      <c r="R178" s="2"/>
-      <c r="S178" s="3"/>
-    </row>
-    <row r="179" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K179" s="2"/>
-      <c r="L179" s="3"/>
+      <c r="R178" s="3"/>
+    </row>
+    <row r="179" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J179" s="2"/>
+      <c r="K179" s="3"/>
+      <c r="L179" s="2"/>
       <c r="M179" s="2"/>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
       <c r="P179" s="2"/>
       <c r="Q179" s="2"/>
-      <c r="R179" s="2"/>
-      <c r="S179" s="3"/>
-    </row>
-    <row r="180" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K180" s="2"/>
-      <c r="L180" s="3"/>
+      <c r="R179" s="3"/>
+    </row>
+    <row r="180" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J180" s="2"/>
+      <c r="K180" s="3"/>
+      <c r="L180" s="2"/>
       <c r="M180" s="2"/>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
       <c r="P180" s="2"/>
       <c r="Q180" s="2"/>
-      <c r="R180" s="2"/>
-      <c r="S180" s="3"/>
-    </row>
-    <row r="181" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K181" s="2"/>
-      <c r="L181" s="3"/>
+      <c r="R180" s="3"/>
+    </row>
+    <row r="181" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J181" s="2"/>
+      <c r="K181" s="3"/>
+      <c r="L181" s="2"/>
       <c r="M181" s="2"/>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
       <c r="P181" s="2"/>
       <c r="Q181" s="2"/>
-      <c r="R181" s="2"/>
-      <c r="S181" s="3"/>
-    </row>
-    <row r="182" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K182" s="2"/>
-      <c r="L182" s="3"/>
+      <c r="R181" s="3"/>
+    </row>
+    <row r="182" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J182" s="2"/>
+      <c r="K182" s="3"/>
+      <c r="L182" s="2"/>
       <c r="M182" s="2"/>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
       <c r="P182" s="2"/>
       <c r="Q182" s="2"/>
-      <c r="R182" s="2"/>
-      <c r="S182" s="3"/>
-    </row>
-    <row r="183" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K183" s="2"/>
-      <c r="L183" s="3"/>
+      <c r="R182" s="3"/>
+    </row>
+    <row r="183" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J183" s="2"/>
+      <c r="K183" s="3"/>
+      <c r="L183" s="2"/>
       <c r="M183" s="2"/>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
       <c r="P183" s="2"/>
       <c r="Q183" s="2"/>
-      <c r="R183" s="2"/>
-      <c r="S183" s="3"/>
-    </row>
-    <row r="184" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K184" s="2"/>
-      <c r="L184" s="3"/>
+      <c r="R183" s="3"/>
+    </row>
+    <row r="184" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J184" s="2"/>
+      <c r="K184" s="3"/>
+      <c r="L184" s="2"/>
       <c r="M184" s="2"/>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
       <c r="P184" s="2"/>
       <c r="Q184" s="2"/>
-      <c r="R184" s="2"/>
-      <c r="S184" s="3"/>
-    </row>
-    <row r="185" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K185" s="2"/>
-      <c r="L185" s="3"/>
+      <c r="R184" s="3"/>
+    </row>
+    <row r="185" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J185" s="2"/>
+      <c r="K185" s="3"/>
+      <c r="L185" s="2"/>
       <c r="M185" s="2"/>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
       <c r="P185" s="2"/>
       <c r="Q185" s="2"/>
-      <c r="R185" s="2"/>
-      <c r="S185" s="3"/>
-    </row>
-    <row r="186" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K186" s="2"/>
-      <c r="L186" s="3"/>
+      <c r="R185" s="3"/>
+    </row>
+    <row r="186" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J186" s="2"/>
+      <c r="K186" s="3"/>
+      <c r="L186" s="2"/>
       <c r="M186" s="2"/>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
       <c r="P186" s="2"/>
       <c r="Q186" s="2"/>
-      <c r="R186" s="2"/>
-      <c r="S186" s="3"/>
-    </row>
-    <row r="187" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K187" s="2"/>
-      <c r="L187" s="3"/>
+      <c r="R186" s="3"/>
+    </row>
+    <row r="187" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J187" s="2"/>
+      <c r="K187" s="3"/>
+      <c r="L187" s="2"/>
       <c r="M187" s="2"/>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
       <c r="P187" s="2"/>
       <c r="Q187" s="2"/>
-      <c r="R187" s="2"/>
-      <c r="S187" s="3"/>
-    </row>
-    <row r="188" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K188" s="2"/>
-      <c r="L188" s="3"/>
+      <c r="R187" s="3"/>
+    </row>
+    <row r="188" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J188" s="2"/>
+      <c r="K188" s="3"/>
+      <c r="L188" s="2"/>
       <c r="M188" s="2"/>
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
       <c r="P188" s="2"/>
       <c r="Q188" s="2"/>
-      <c r="R188" s="2"/>
-      <c r="S188" s="3"/>
-    </row>
-    <row r="189" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K189" s="2"/>
-      <c r="L189" s="3"/>
+      <c r="R188" s="3"/>
+    </row>
+    <row r="189" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J189" s="2"/>
+      <c r="K189" s="3"/>
+      <c r="L189" s="2"/>
       <c r="M189" s="2"/>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
       <c r="P189" s="2"/>
       <c r="Q189" s="2"/>
-      <c r="R189" s="2"/>
-      <c r="S189" s="3"/>
-    </row>
-    <row r="190" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K190" s="2"/>
-      <c r="L190" s="3"/>
+      <c r="R189" s="3"/>
+    </row>
+    <row r="190" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J190" s="2"/>
+      <c r="K190" s="3"/>
+      <c r="L190" s="2"/>
       <c r="M190" s="2"/>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
       <c r="P190" s="2"/>
       <c r="Q190" s="2"/>
-      <c r="R190" s="2"/>
-      <c r="S190" s="3"/>
-    </row>
-    <row r="191" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K191" s="2"/>
-      <c r="L191" s="3"/>
+      <c r="R190" s="3"/>
+    </row>
+    <row r="191" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J191" s="2"/>
+      <c r="K191" s="3"/>
+      <c r="L191" s="2"/>
       <c r="M191" s="2"/>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
       <c r="P191" s="2"/>
       <c r="Q191" s="2"/>
-      <c r="R191" s="2"/>
-      <c r="S191" s="3"/>
-    </row>
-    <row r="192" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K192" s="2"/>
-      <c r="L192" s="3"/>
+      <c r="R191" s="3"/>
+    </row>
+    <row r="192" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J192" s="2"/>
+      <c r="K192" s="3"/>
+      <c r="L192" s="2"/>
       <c r="M192" s="2"/>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
       <c r="P192" s="2"/>
       <c r="Q192" s="2"/>
-      <c r="R192" s="2"/>
-      <c r="S192" s="3"/>
-    </row>
-    <row r="193" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K193" s="2"/>
-      <c r="L193" s="3"/>
+      <c r="R192" s="3"/>
+    </row>
+    <row r="193" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J193" s="2"/>
+      <c r="K193" s="3"/>
+      <c r="L193" s="2"/>
       <c r="M193" s="2"/>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
       <c r="P193" s="2"/>
       <c r="Q193" s="2"/>
-      <c r="R193" s="2"/>
-      <c r="S193" s="3"/>
-    </row>
-    <row r="194" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K194" s="2"/>
-      <c r="L194" s="3"/>
+      <c r="R193" s="3"/>
+    </row>
+    <row r="194" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J194" s="2"/>
+      <c r="K194" s="3"/>
+      <c r="L194" s="2"/>
       <c r="M194" s="2"/>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
       <c r="P194" s="2"/>
       <c r="Q194" s="2"/>
-      <c r="R194" s="2"/>
-      <c r="S194" s="3"/>
-    </row>
-    <row r="195" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K195" s="2"/>
-      <c r="L195" s="3"/>
+      <c r="R194" s="3"/>
+    </row>
+    <row r="195" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J195" s="2"/>
+      <c r="K195" s="3"/>
+      <c r="L195" s="2"/>
       <c r="M195" s="2"/>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
       <c r="P195" s="2"/>
       <c r="Q195" s="2"/>
-      <c r="R195" s="2"/>
-      <c r="S195" s="3"/>
-    </row>
-    <row r="196" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K196" s="2"/>
-      <c r="L196" s="3"/>
+      <c r="R195" s="3"/>
+    </row>
+    <row r="196" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J196" s="2"/>
+      <c r="K196" s="3"/>
+      <c r="L196" s="2"/>
       <c r="M196" s="2"/>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
       <c r="P196" s="2"/>
       <c r="Q196" s="2"/>
-      <c r="R196" s="2"/>
-      <c r="S196" s="3"/>
-    </row>
-    <row r="197" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K197" s="2"/>
-      <c r="L197" s="3"/>
+      <c r="R196" s="3"/>
+    </row>
+    <row r="197" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J197" s="2"/>
+      <c r="K197" s="3"/>
+      <c r="L197" s="2"/>
       <c r="M197" s="2"/>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
       <c r="P197" s="2"/>
       <c r="Q197" s="2"/>
-      <c r="R197" s="2"/>
-      <c r="S197" s="3"/>
-    </row>
-    <row r="198" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K198" s="2"/>
-      <c r="L198" s="3"/>
+      <c r="R197" s="3"/>
+    </row>
+    <row r="198" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J198" s="2"/>
+      <c r="K198" s="3"/>
+      <c r="L198" s="2"/>
       <c r="M198" s="2"/>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
       <c r="P198" s="2"/>
       <c r="Q198" s="2"/>
-      <c r="R198" s="2"/>
-      <c r="S198" s="3"/>
-    </row>
-    <row r="199" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K199" s="2"/>
-      <c r="L199" s="3"/>
+      <c r="R198" s="3"/>
+    </row>
+    <row r="199" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J199" s="2"/>
+      <c r="K199" s="3"/>
+      <c r="L199" s="2"/>
       <c r="M199" s="2"/>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
       <c r="P199" s="2"/>
       <c r="Q199" s="2"/>
-      <c r="R199" s="2"/>
-      <c r="S199" s="3"/>
-    </row>
-    <row r="200" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K200" s="2"/>
-      <c r="L200" s="3"/>
+      <c r="R199" s="3"/>
+    </row>
+    <row r="200" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J200" s="2"/>
+      <c r="K200" s="3"/>
+      <c r="L200" s="2"/>
       <c r="M200" s="2"/>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
       <c r="P200" s="2"/>
       <c r="Q200" s="2"/>
-      <c r="R200" s="2"/>
-      <c r="S200" s="3"/>
-    </row>
-    <row r="201" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K201" s="2"/>
-      <c r="L201" s="3"/>
+      <c r="R200" s="3"/>
+    </row>
+    <row r="201" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J201" s="2"/>
+      <c r="K201" s="3"/>
+      <c r="L201" s="2"/>
       <c r="M201" s="2"/>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
       <c r="P201" s="2"/>
       <c r="Q201" s="2"/>
-      <c r="R201" s="2"/>
-      <c r="S201" s="3"/>
-    </row>
-    <row r="202" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K202" s="2"/>
-      <c r="L202" s="3"/>
+      <c r="R201" s="3"/>
+    </row>
+    <row r="202" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J202" s="2"/>
+      <c r="K202" s="3"/>
+      <c r="L202" s="2"/>
       <c r="M202" s="2"/>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
       <c r="P202" s="2"/>
       <c r="Q202" s="2"/>
-      <c r="R202" s="2"/>
-      <c r="S202" s="3"/>
-    </row>
-    <row r="203" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K203" s="2"/>
-      <c r="L203" s="3"/>
+      <c r="R202" s="3"/>
+    </row>
+    <row r="203" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J203" s="2"/>
+      <c r="K203" s="3"/>
+      <c r="L203" s="2"/>
       <c r="M203" s="2"/>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
       <c r="P203" s="2"/>
       <c r="Q203" s="2"/>
-      <c r="R203" s="2"/>
-      <c r="S203" s="3"/>
-    </row>
-    <row r="204" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K204" s="2"/>
-      <c r="L204" s="3"/>
+      <c r="R203" s="3"/>
+    </row>
+    <row r="204" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J204" s="2"/>
+      <c r="K204" s="3"/>
+      <c r="L204" s="2"/>
       <c r="M204" s="2"/>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
       <c r="P204" s="2"/>
       <c r="Q204" s="2"/>
-      <c r="R204" s="2"/>
-      <c r="S204" s="3"/>
-    </row>
-    <row r="205" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K205" s="2"/>
-      <c r="L205" s="3"/>
+      <c r="R204" s="3"/>
+    </row>
+    <row r="205" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J205" s="2"/>
+      <c r="K205" s="3"/>
+      <c r="L205" s="2"/>
       <c r="M205" s="2"/>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
       <c r="P205" s="2"/>
       <c r="Q205" s="2"/>
-      <c r="R205" s="2"/>
-      <c r="S205" s="3"/>
-    </row>
-    <row r="206" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K206" s="2"/>
-      <c r="L206" s="3"/>
+      <c r="R205" s="3"/>
+    </row>
+    <row r="206" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J206" s="2"/>
+      <c r="K206" s="3"/>
+      <c r="L206" s="2"/>
       <c r="M206" s="2"/>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
       <c r="P206" s="2"/>
       <c r="Q206" s="2"/>
-      <c r="R206" s="2"/>
-      <c r="S206" s="3"/>
-    </row>
-    <row r="207" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K207" s="2"/>
-      <c r="L207" s="3"/>
+      <c r="R206" s="3"/>
+    </row>
+    <row r="207" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J207" s="2"/>
+      <c r="K207" s="3"/>
+      <c r="L207" s="2"/>
       <c r="M207" s="2"/>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
       <c r="P207" s="2"/>
       <c r="Q207" s="2"/>
-      <c r="R207" s="2"/>
-      <c r="S207" s="3"/>
-    </row>
-    <row r="208" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K208" s="2"/>
-      <c r="L208" s="3"/>
+      <c r="R207" s="3"/>
+    </row>
+    <row r="208" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J208" s="2"/>
+      <c r="K208" s="3"/>
+      <c r="L208" s="2"/>
       <c r="M208" s="2"/>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
       <c r="P208" s="2"/>
       <c r="Q208" s="2"/>
-      <c r="R208" s="2"/>
-      <c r="S208" s="3"/>
-    </row>
-    <row r="209" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K209" s="2"/>
-      <c r="L209" s="3"/>
+      <c r="R208" s="3"/>
+    </row>
+    <row r="209" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J209" s="2"/>
+      <c r="K209" s="3"/>
+      <c r="L209" s="2"/>
       <c r="M209" s="2"/>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
       <c r="P209" s="2"/>
       <c r="Q209" s="2"/>
-      <c r="R209" s="2"/>
-      <c r="S209" s="3"/>
-    </row>
-    <row r="210" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K210" s="2"/>
-      <c r="L210" s="3"/>
+      <c r="R209" s="3"/>
+    </row>
+    <row r="210" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J210" s="2"/>
+      <c r="K210" s="3"/>
+      <c r="L210" s="2"/>
       <c r="M210" s="2"/>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
       <c r="P210" s="2"/>
       <c r="Q210" s="2"/>
-      <c r="R210" s="2"/>
-      <c r="S210" s="3"/>
-    </row>
-    <row r="211" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K211" s="2"/>
-      <c r="L211" s="3"/>
+      <c r="R210" s="3"/>
+    </row>
+    <row r="211" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J211" s="2"/>
+      <c r="K211" s="3"/>
+      <c r="L211" s="2"/>
       <c r="M211" s="2"/>
       <c r="N211" s="2"/>
       <c r="O211" s="2"/>
       <c r="P211" s="2"/>
       <c r="Q211" s="2"/>
-      <c r="R211" s="2"/>
-      <c r="S211" s="3"/>
-    </row>
-    <row r="212" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K212" s="2"/>
-      <c r="L212" s="3"/>
+      <c r="R211" s="3"/>
+    </row>
+    <row r="212" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J212" s="2"/>
+      <c r="K212" s="3"/>
+      <c r="L212" s="2"/>
       <c r="M212" s="2"/>
       <c r="N212" s="2"/>
       <c r="O212" s="2"/>
       <c r="P212" s="2"/>
       <c r="Q212" s="2"/>
-      <c r="R212" s="2"/>
-      <c r="S212" s="3"/>
-    </row>
-    <row r="213" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K213" s="2"/>
-      <c r="L213" s="3"/>
+      <c r="R212" s="3"/>
+    </row>
+    <row r="213" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J213" s="2"/>
+      <c r="K213" s="3"/>
+      <c r="L213" s="2"/>
       <c r="M213" s="2"/>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
       <c r="P213" s="2"/>
       <c r="Q213" s="2"/>
-      <c r="R213" s="2"/>
-      <c r="S213" s="3"/>
-    </row>
-    <row r="214" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K214" s="2"/>
-      <c r="L214" s="3"/>
+      <c r="R213" s="3"/>
+    </row>
+    <row r="214" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J214" s="2"/>
+      <c r="K214" s="3"/>
+      <c r="L214" s="2"/>
       <c r="M214" s="2"/>
       <c r="N214" s="2"/>
       <c r="O214" s="2"/>
       <c r="P214" s="2"/>
       <c r="Q214" s="2"/>
-      <c r="R214" s="2"/>
-      <c r="S214" s="3"/>
-    </row>
-    <row r="215" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K215" s="2"/>
-      <c r="L215" s="3"/>
+      <c r="R214" s="3"/>
+    </row>
+    <row r="215" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J215" s="2"/>
+      <c r="K215" s="3"/>
+      <c r="L215" s="2"/>
       <c r="M215" s="2"/>
       <c r="N215" s="2"/>
       <c r="O215" s="2"/>
       <c r="P215" s="2"/>
       <c r="Q215" s="2"/>
-      <c r="R215" s="2"/>
-      <c r="S215" s="3"/>
-    </row>
-    <row r="216" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K216" s="2"/>
-      <c r="L216" s="3"/>
+      <c r="R215" s="3"/>
+    </row>
+    <row r="216" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J216" s="2"/>
+      <c r="K216" s="3"/>
+      <c r="L216" s="2"/>
       <c r="M216" s="2"/>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
       <c r="P216" s="2"/>
       <c r="Q216" s="2"/>
-      <c r="R216" s="2"/>
-      <c r="S216" s="3"/>
-    </row>
-    <row r="217" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K217" s="2"/>
-      <c r="L217" s="3"/>
+      <c r="R216" s="3"/>
+    </row>
+    <row r="217" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J217" s="2"/>
+      <c r="K217" s="3"/>
+      <c r="L217" s="2"/>
       <c r="M217" s="2"/>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
       <c r="P217" s="2"/>
       <c r="Q217" s="2"/>
-      <c r="R217" s="2"/>
-      <c r="S217" s="3"/>
-    </row>
-    <row r="218" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K218" s="2"/>
-      <c r="L218" s="3"/>
+      <c r="R217" s="3"/>
+    </row>
+    <row r="218" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J218" s="2"/>
+      <c r="K218" s="3"/>
+      <c r="L218" s="2"/>
       <c r="M218" s="2"/>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
       <c r="P218" s="2"/>
       <c r="Q218" s="2"/>
-      <c r="R218" s="2"/>
-      <c r="S218" s="3"/>
-    </row>
-    <row r="219" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K219" s="2"/>
-      <c r="L219" s="3"/>
+      <c r="R218" s="3"/>
+    </row>
+    <row r="219" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J219" s="2"/>
+      <c r="K219" s="3"/>
+      <c r="L219" s="2"/>
       <c r="M219" s="2"/>
       <c r="N219" s="2"/>
       <c r="O219" s="2"/>
       <c r="P219" s="2"/>
       <c r="Q219" s="2"/>
-      <c r="R219" s="2"/>
-      <c r="S219" s="3"/>
-    </row>
-    <row r="220" ht="15.75" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
-      <c r="K220" s="2"/>
-      <c r="L220" s="3"/>
+      <c r="R219" s="3"/>
+    </row>
+    <row r="220" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="J220" s="2"/>
+      <c r="K220" s="3"/>
+      <c r="L220" s="2"/>
       <c r="M220" s="2"/>
       <c r="N220" s="2"/>
       <c r="O220" s="2"/>
       <c r="P220" s="2"/>
       <c r="Q220" s="2"/>
-      <c r="R220" s="2"/>
-      <c r="S220" s="3"/>
+      <c r="R220" s="3"/>
     </row>
     <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4742,7 +4716,7 @@
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4753,7 +4727,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D2" s="25"/>
       <c r="E2" s="25"/>
@@ -4762,94 +4736,94 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="8"/>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="8"/>
     </row>
     <row r="8" ht="54" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="G8" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="H8" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="I8" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B9" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="F9" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="G9" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="H9" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="I9" s="26" t="s">
         <v>66</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="H9" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="I9" s="26" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B10" s="29"/>
       <c r="C10" s="30" t="e">
@@ -5910,7 +5884,7 @@
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5982,7 +5956,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -6018,7 +5992,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -6122,7 +6096,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2">
         <v>2</v>
@@ -6160,67 +6134,67 @@
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="E8" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="F8" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="G8" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="H8" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="34" t="s">
+      <c r="I8" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="G8" s="34" t="s">
+      <c r="J8" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="34" t="s">
+      <c r="K8" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="L8" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="J8" s="34" t="s">
+      <c r="M8" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="K8" s="34" t="s">
+      <c r="N8" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="L8" s="34" t="s">
+      <c r="O8" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="M8" s="34" t="s">
+      <c r="P8" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="N8" s="34" t="s">
+      <c r="Q8" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="O8" s="34" t="s">
+      <c r="R8" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="P8" s="34" t="s">
+      <c r="S8" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="Q8" s="34" t="s">
+      <c r="T8" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="R8" s="34" t="s">
+      <c r="U8" s="35" t="s">
         <v>88</v>
-      </c>
-      <c r="S8" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="T8" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="U8" s="35" t="s">
-        <v>91</v>
       </c>
       <c r="V8" s="36"/>
       <c r="W8" s="36"/>
@@ -6231,13 +6205,13 @@
       <c r="AB8" s="36"/>
       <c r="AC8" s="37"/>
       <c r="AD8" s="33" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="AE8" s="33" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="AF8" s="33" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" ht="31.5" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
@@ -6286,7 +6260,7 @@
         <v>2022</v>
       </c>
       <c r="AC9" s="39" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="AD9" s="38"/>
       <c r="AE9" s="38"/>
@@ -6294,36 +6268,36 @@
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="E10" s="41" t="s">
         <v>97</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" s="41" t="s">
-        <v>100</v>
       </c>
       <c r="F10" s="42">
         <f>IFERROR(IF(A10="No data","",IF(C10=0,0,D10/C10)),0)</f>
         <v>0</v>
       </c>
       <c r="G10" s="41" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H10" s="43">
         <f>IFERROR(IF(A10="No data","",IF(B10&lt;&gt;0, G10/B10, 0)),0)</f>
         <v>0</v>
       </c>
       <c r="I10" s="41" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J10" s="41" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K10" s="41">
         <f>IFERROR(IF(A10="No data","",U10+V10+W10+X10+Y10+Z10+AA10+AB10+AC10+AD10),0)</f>
@@ -6346,53 +6320,53 @@
         <v>0</v>
       </c>
       <c r="P10" s="41" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="Q10" s="41" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="R10" s="41" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="S10" s="42">
         <f>IFERROR(IF(A10="No data","",IF(I10=0,0,R10/I10)),0)</f>
         <v>0</v>
       </c>
       <c r="T10" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="U10" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="V10" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="W10" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="U10" s="41" t="s">
+      <c r="X10" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="V10" s="41" t="s">
+      <c r="Y10" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="W10" s="41" t="s">
+      <c r="Z10" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="X10" s="41" t="s">
+      <c r="AA10" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="Y10" s="41" t="s">
+      <c r="AB10" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="Z10" s="41" t="s">
+      <c r="AC10" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="AA10" s="41" t="s">
+      <c r="AD10" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="AB10" s="41" t="s">
+      <c r="AE10" s="41" t="s">
         <v>114</v>
-      </c>
-      <c r="AC10" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="AD10" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE10" s="41" t="s">
-        <v>117</v>
       </c>
       <c r="AF10" s="41">
         <f>IFERROR(IF(A10="No data","",U10+V10+W10+X10+Y10+Z10+AA10+AB10+AC10+AD10+AE10),0)</f>
@@ -6401,7 +6375,7 @@
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="45" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B11" s="46"/>
       <c r="C11" s="46"/>
@@ -14249,7 +14223,7 @@
   <sheetData>
     <row r="1" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -14281,7 +14255,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -14297,7 +14271,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -14313,7 +14287,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -14329,7 +14303,7 @@
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -14345,7 +14319,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2">
         <v>2</v>
@@ -14363,10 +14337,10 @@
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="50" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C8" s="36"/>
       <c r="D8" s="36"/>
@@ -14377,10 +14351,10 @@
       <c r="I8" s="36"/>
       <c r="J8" s="37"/>
       <c r="K8" s="51" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L8" s="51" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -14410,44 +14384,44 @@
         <v>2022</v>
       </c>
       <c r="J9" s="39" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K9" s="38"/>
       <c r="L9" s="38"/>
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="40" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B10" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="F10" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="G10" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="H10" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="I10" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="G10" s="41" t="s">
+      <c r="J10" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="H10" s="41" t="s">
+      <c r="K10" s="41" t="s">
         <v>113</v>
-      </c>
-      <c r="I10" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="J10" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="K10" s="41" t="s">
-        <v>116</v>
       </c>
       <c r="L10" s="41" t="e">
         <f>B10+C10+D10+E10+F10+G10+H10+I10+J10+K10</f>
@@ -14456,7 +14430,7 @@
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="45" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B11" s="46">
         <f>SUM(B$10:B10)</f>
@@ -18031,13 +18005,13 @@
   <sheetData>
     <row r="2" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" s="53" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C2" s="53" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D2" s="53" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18045,10 +18019,10 @@
         <v>1001</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18056,10 +18030,10 @@
         <v>1002</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D4" s="59" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18067,10 +18041,10 @@
         <v>1004</v>
       </c>
       <c r="C5" s="61" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="62" t="s">
         <v>123</v>
-      </c>
-      <c r="D5" s="62" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="6" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18078,10 +18052,10 @@
         <v>1005</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18089,10 +18063,10 @@
         <v>1006</v>
       </c>
       <c r="C7" s="61" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D7" s="62" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18100,10 +18074,10 @@
         <v>1007</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18111,10 +18085,10 @@
         <v>1017</v>
       </c>
       <c r="C9" s="61" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D9" s="62" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18122,10 +18096,10 @@
         <v>1018</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18133,10 +18107,10 @@
         <v>2003</v>
       </c>
       <c r="C11" s="61" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D11" s="62" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18144,10 +18118,10 @@
         <v>2005</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18155,10 +18129,10 @@
         <v>2008</v>
       </c>
       <c r="C13" s="61" t="s">
+        <v>129</v>
+      </c>
+      <c r="D13" s="62" t="s">
         <v>132</v>
-      </c>
-      <c r="D13" s="62" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="14" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18166,10 +18140,10 @@
         <v>2009</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18177,10 +18151,10 @@
         <v>2011</v>
       </c>
       <c r="C15" s="61" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D15" s="62" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18188,10 +18162,10 @@
         <v>2014</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18199,10 +18173,10 @@
         <v>2016</v>
       </c>
       <c r="C17" s="61" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D17" s="62" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18210,10 +18184,10 @@
         <v>2018</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18221,10 +18195,10 @@
         <v>2022</v>
       </c>
       <c r="C19" s="61" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D19" s="62" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18232,10 +18206,10 @@
         <v>2025</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D20" s="59" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18243,10 +18217,10 @@
         <v>2032</v>
       </c>
       <c r="C21" s="61" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D21" s="62" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18254,10 +18228,10 @@
         <v>2034</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D22" s="59" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18265,10 +18239,10 @@
         <v>2037</v>
       </c>
       <c r="C23" s="61" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D23" s="62" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18276,10 +18250,10 @@
         <v>4010</v>
       </c>
       <c r="C24" s="58" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D24" s="59" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18287,10 +18261,10 @@
         <v>4017</v>
       </c>
       <c r="C25" s="61" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D25" s="62" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18298,10 +18272,10 @@
         <v>5006</v>
       </c>
       <c r="C26" s="58" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D26" s="59" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18309,10 +18283,10 @@
         <v>5007</v>
       </c>
       <c r="C27" s="61" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D27" s="62" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18320,10 +18294,10 @@
         <v>5011</v>
       </c>
       <c r="C28" s="64" t="s">
+        <v>146</v>
+      </c>
+      <c r="D28" s="65" t="s">
         <v>149</v>
-      </c>
-      <c r="D28" s="65" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/api/templates/device_and_site_summary_report/fr.xlsx
+++ b/api/templates/device_and_site_summary_report/fr.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="151">
   <si>
     <t>Rapport récapitulatif sur l’appareil et le site</t>
   </si>
@@ -36,6 +36,9 @@
   </si>
   <si>
     <t>&lt;AssaysLabel&gt;: &lt;Assays&gt;</t>
+  </si>
+  <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -1297,7 +1300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V1000"/>
+  <dimension ref="A1:U1001"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11.1640625"/>
   <cols>
     <col min="1" max="1" width="34.5" customWidth="1"/>
@@ -1315,7 +1318,7 @@
     <col min="20" max="26" width="11.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" ht="27.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1332,7 +1335,7 @@
       <c r="Q1" s="2"/>
       <c r="R1" s="3"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1349,7 +1352,7 @@
       <c r="Q2" s="2"/>
       <c r="R2" s="3"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -1368,7 +1371,7 @@
       <c r="Q3" s="2"/>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -1385,7 +1388,7 @@
       <c r="Q4" s="2"/>
       <c r="R4" s="3"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>4</v>
       </c>
@@ -1402,7 +1405,7 @@
       <c r="Q5" s="2"/>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
@@ -1419,193 +1422,187 @@
       <c r="Q6" s="2"/>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="8"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="3"/>
-    </row>
-    <row r="8" ht="67.5" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+    </row>
+    <row r="8" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="D8" s="9"/>
+      <c r="E8" s="8"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" ht="67.5" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="B9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="C9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="D9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="E9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="F9" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="G9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="H9" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="I9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="J9" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="K9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="L9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="N8" s="11" t="s">
+      <c r="M9" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="N9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="P8" s="11" t="s">
+      <c r="O9" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Q8" s="11" t="s">
+      <c r="P9" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="R8" s="11" t="s">
+      <c r="Q9" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="S8" s="10" t="s">
+      <c r="R9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="T8" s="10" t="s">
+      <c r="S9" s="10" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="T9" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="12" t="s">
+    </row>
+    <row r="10" ht="15.75" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="B10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="C10" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="D10" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="E10" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="F10" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="G10" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="H10" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="I10" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="J10" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="K10" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="L10" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="N9" s="15" t="s">
+      <c r="M10" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="O9" s="15" t="s">
+      <c r="N10" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="P9" s="15" t="s">
+      <c r="O10" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="Q9" s="15" t="s">
+      <c r="P10" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="R9" s="14" t="s">
+      <c r="Q10" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="S9" s="16" t="s">
+      <c r="R10" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="T9" s="16" t="s">
+      <c r="S10" s="16" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="T10" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="18"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="18"/>
-      <c r="R10" s="18"/>
-      <c r="S10" s="19">
+    </row>
+    <row r="11" ht="15.75" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="19">
         <f>SUM(T$9:T9)</f>
       </c>
-      <c r="T10" s="20">
+      <c r="T11" s="20">
         <f>SUM(U$9:U9)</f>
       </c>
-      <c r="U10" s="21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="3"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+      <c r="U11" s="21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
       <c r="J12" s="2"/>
       <c r="K12" s="3"/>
       <c r="L12" s="2"/>
@@ -1616,7 +1613,7 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="13" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J13" s="2"/>
       <c r="K13" s="3"/>
       <c r="L13" s="2"/>
@@ -1627,7 +1624,7 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="14" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J14" s="2"/>
       <c r="K14" s="3"/>
       <c r="L14" s="2"/>
@@ -1638,7 +1635,7 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="15" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J15" s="2"/>
       <c r="K15" s="3"/>
       <c r="L15" s="2"/>
@@ -1649,7 +1646,7 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J16" s="2"/>
       <c r="K16" s="3"/>
       <c r="L16" s="2"/>
@@ -1660,7 +1657,7 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="3"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="17" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J17" s="2"/>
       <c r="K17" s="3"/>
       <c r="L17" s="2"/>
@@ -1671,7 +1668,7 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="3"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="18" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J18" s="2"/>
       <c r="K18" s="3"/>
       <c r="L18" s="2"/>
@@ -1682,7 +1679,7 @@
       <c r="Q18" s="2"/>
       <c r="R18" s="3"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="19" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J19" s="2"/>
       <c r="K19" s="3"/>
       <c r="L19" s="2"/>
@@ -1693,7 +1690,7 @@
       <c r="Q19" s="2"/>
       <c r="R19" s="3"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="20" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J20" s="2"/>
       <c r="K20" s="3"/>
       <c r="L20" s="2"/>
@@ -1704,7 +1701,7 @@
       <c r="Q20" s="2"/>
       <c r="R20" s="3"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="21" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J21" s="2"/>
       <c r="K21" s="3"/>
       <c r="L21" s="2"/>
@@ -1715,7 +1712,7 @@
       <c r="Q21" s="2"/>
       <c r="R21" s="3"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="22" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J22" s="2"/>
       <c r="K22" s="3"/>
       <c r="L22" s="2"/>
@@ -1726,7 +1723,7 @@
       <c r="Q22" s="2"/>
       <c r="R22" s="3"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="23" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J23" s="2"/>
       <c r="K23" s="3"/>
       <c r="L23" s="2"/>
@@ -1737,7 +1734,7 @@
       <c r="Q23" s="2"/>
       <c r="R23" s="3"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="24" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J24" s="2"/>
       <c r="K24" s="3"/>
       <c r="L24" s="2"/>
@@ -1748,7 +1745,7 @@
       <c r="Q24" s="2"/>
       <c r="R24" s="3"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="25" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J25" s="2"/>
       <c r="K25" s="3"/>
       <c r="L25" s="2"/>
@@ -1759,7 +1756,7 @@
       <c r="Q25" s="2"/>
       <c r="R25" s="3"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="26" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J26" s="2"/>
       <c r="K26" s="3"/>
       <c r="L26" s="2"/>
@@ -1770,7 +1767,7 @@
       <c r="Q26" s="2"/>
       <c r="R26" s="3"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="27" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J27" s="2"/>
       <c r="K27" s="3"/>
       <c r="L27" s="2"/>
@@ -1781,7 +1778,7 @@
       <c r="Q27" s="2"/>
       <c r="R27" s="3"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="28" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J28" s="2"/>
       <c r="K28" s="3"/>
       <c r="L28" s="2"/>
@@ -1792,7 +1789,7 @@
       <c r="Q28" s="2"/>
       <c r="R28" s="3"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="29" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J29" s="2"/>
       <c r="K29" s="3"/>
       <c r="L29" s="2"/>
@@ -1803,7 +1800,7 @@
       <c r="Q29" s="2"/>
       <c r="R29" s="3"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="30" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J30" s="2"/>
       <c r="K30" s="3"/>
       <c r="L30" s="2"/>
@@ -1814,7 +1811,7 @@
       <c r="Q30" s="2"/>
       <c r="R30" s="3"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="31" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J31" s="2"/>
       <c r="K31" s="3"/>
       <c r="L31" s="2"/>
@@ -1825,7 +1822,7 @@
       <c r="Q31" s="2"/>
       <c r="R31" s="3"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="32" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J32" s="2"/>
       <c r="K32" s="3"/>
       <c r="L32" s="2"/>
@@ -1836,7 +1833,7 @@
       <c r="Q32" s="2"/>
       <c r="R32" s="3"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="33" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J33" s="2"/>
       <c r="K33" s="3"/>
       <c r="L33" s="2"/>
@@ -1847,7 +1844,7 @@
       <c r="Q33" s="2"/>
       <c r="R33" s="3"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="34" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J34" s="2"/>
       <c r="K34" s="3"/>
       <c r="L34" s="2"/>
@@ -1858,7 +1855,7 @@
       <c r="Q34" s="2"/>
       <c r="R34" s="3"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="35" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J35" s="2"/>
       <c r="K35" s="3"/>
       <c r="L35" s="2"/>
@@ -1869,7 +1866,7 @@
       <c r="Q35" s="2"/>
       <c r="R35" s="3"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="36" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J36" s="2"/>
       <c r="K36" s="3"/>
       <c r="L36" s="2"/>
@@ -1880,7 +1877,7 @@
       <c r="Q36" s="2"/>
       <c r="R36" s="3"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="37" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J37" s="2"/>
       <c r="K37" s="3"/>
       <c r="L37" s="2"/>
@@ -1891,7 +1888,7 @@
       <c r="Q37" s="2"/>
       <c r="R37" s="3"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="38" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J38" s="2"/>
       <c r="K38" s="3"/>
       <c r="L38" s="2"/>
@@ -1902,7 +1899,7 @@
       <c r="Q38" s="2"/>
       <c r="R38" s="3"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="39" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J39" s="2"/>
       <c r="K39" s="3"/>
       <c r="L39" s="2"/>
@@ -1913,7 +1910,7 @@
       <c r="Q39" s="2"/>
       <c r="R39" s="3"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="40" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J40" s="2"/>
       <c r="K40" s="3"/>
       <c r="L40" s="2"/>
@@ -1924,7 +1921,7 @@
       <c r="Q40" s="2"/>
       <c r="R40" s="3"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="41" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J41" s="2"/>
       <c r="K41" s="3"/>
       <c r="L41" s="2"/>
@@ -1935,7 +1932,7 @@
       <c r="Q41" s="2"/>
       <c r="R41" s="3"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="42" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J42" s="2"/>
       <c r="K42" s="3"/>
       <c r="L42" s="2"/>
@@ -1946,7 +1943,7 @@
       <c r="Q42" s="2"/>
       <c r="R42" s="3"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="43" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J43" s="2"/>
       <c r="K43" s="3"/>
       <c r="L43" s="2"/>
@@ -1957,7 +1954,7 @@
       <c r="Q43" s="2"/>
       <c r="R43" s="3"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="44" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J44" s="2"/>
       <c r="K44" s="3"/>
       <c r="L44" s="2"/>
@@ -1968,7 +1965,7 @@
       <c r="Q44" s="2"/>
       <c r="R44" s="3"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="45" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J45" s="2"/>
       <c r="K45" s="3"/>
       <c r="L45" s="2"/>
@@ -1979,7 +1976,7 @@
       <c r="Q45" s="2"/>
       <c r="R45" s="3"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J46" s="2"/>
       <c r="K46" s="3"/>
       <c r="L46" s="2"/>
@@ -1990,7 +1987,7 @@
       <c r="Q46" s="2"/>
       <c r="R46" s="3"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="47" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J47" s="2"/>
       <c r="K47" s="3"/>
       <c r="L47" s="2"/>
@@ -2001,7 +1998,7 @@
       <c r="Q47" s="2"/>
       <c r="R47" s="3"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J48" s="2"/>
       <c r="K48" s="3"/>
       <c r="L48" s="2"/>
@@ -2012,7 +2009,7 @@
       <c r="Q48" s="2"/>
       <c r="R48" s="3"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="49" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J49" s="2"/>
       <c r="K49" s="3"/>
       <c r="L49" s="2"/>
@@ -2023,7 +2020,7 @@
       <c r="Q49" s="2"/>
       <c r="R49" s="3"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J50" s="2"/>
       <c r="K50" s="3"/>
       <c r="L50" s="2"/>
@@ -2034,7 +2031,7 @@
       <c r="Q50" s="2"/>
       <c r="R50" s="3"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="51" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J51" s="2"/>
       <c r="K51" s="3"/>
       <c r="L51" s="2"/>
@@ -2045,7 +2042,7 @@
       <c r="Q51" s="2"/>
       <c r="R51" s="3"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J52" s="2"/>
       <c r="K52" s="3"/>
       <c r="L52" s="2"/>
@@ -2056,7 +2053,7 @@
       <c r="Q52" s="2"/>
       <c r="R52" s="3"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="53" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J53" s="2"/>
       <c r="K53" s="3"/>
       <c r="L53" s="2"/>
@@ -2067,7 +2064,7 @@
       <c r="Q53" s="2"/>
       <c r="R53" s="3"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J54" s="2"/>
       <c r="K54" s="3"/>
       <c r="L54" s="2"/>
@@ -2078,7 +2075,7 @@
       <c r="Q54" s="2"/>
       <c r="R54" s="3"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="55" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J55" s="2"/>
       <c r="K55" s="3"/>
       <c r="L55" s="2"/>
@@ -2089,7 +2086,7 @@
       <c r="Q55" s="2"/>
       <c r="R55" s="3"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J56" s="2"/>
       <c r="K56" s="3"/>
       <c r="L56" s="2"/>
@@ -2100,7 +2097,7 @@
       <c r="Q56" s="2"/>
       <c r="R56" s="3"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="57" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J57" s="2"/>
       <c r="K57" s="3"/>
       <c r="L57" s="2"/>
@@ -2111,7 +2108,7 @@
       <c r="Q57" s="2"/>
       <c r="R57" s="3"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J58" s="2"/>
       <c r="K58" s="3"/>
       <c r="L58" s="2"/>
@@ -2122,7 +2119,7 @@
       <c r="Q58" s="2"/>
       <c r="R58" s="3"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="59" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J59" s="2"/>
       <c r="K59" s="3"/>
       <c r="L59" s="2"/>
@@ -2133,7 +2130,7 @@
       <c r="Q59" s="2"/>
       <c r="R59" s="3"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="60" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J60" s="2"/>
       <c r="K60" s="3"/>
       <c r="L60" s="2"/>
@@ -2144,7 +2141,7 @@
       <c r="Q60" s="2"/>
       <c r="R60" s="3"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="61" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J61" s="2"/>
       <c r="K61" s="3"/>
       <c r="L61" s="2"/>
@@ -2155,7 +2152,7 @@
       <c r="Q61" s="2"/>
       <c r="R61" s="3"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="62" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J62" s="2"/>
       <c r="K62" s="3"/>
       <c r="L62" s="2"/>
@@ -2166,7 +2163,7 @@
       <c r="Q62" s="2"/>
       <c r="R62" s="3"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="63" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J63" s="2"/>
       <c r="K63" s="3"/>
       <c r="L63" s="2"/>
@@ -2177,7 +2174,7 @@
       <c r="Q63" s="2"/>
       <c r="R63" s="3"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="64" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J64" s="2"/>
       <c r="K64" s="3"/>
       <c r="L64" s="2"/>
@@ -2188,7 +2185,7 @@
       <c r="Q64" s="2"/>
       <c r="R64" s="3"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="65" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J65" s="2"/>
       <c r="K65" s="3"/>
       <c r="L65" s="2"/>
@@ -2199,7 +2196,7 @@
       <c r="Q65" s="2"/>
       <c r="R65" s="3"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="66" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J66" s="2"/>
       <c r="K66" s="3"/>
       <c r="L66" s="2"/>
@@ -2210,7 +2207,7 @@
       <c r="Q66" s="2"/>
       <c r="R66" s="3"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="67" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J67" s="2"/>
       <c r="K67" s="3"/>
       <c r="L67" s="2"/>
@@ -2221,7 +2218,7 @@
       <c r="Q67" s="2"/>
       <c r="R67" s="3"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="68" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J68" s="2"/>
       <c r="K68" s="3"/>
       <c r="L68" s="2"/>
@@ -2232,7 +2229,7 @@
       <c r="Q68" s="2"/>
       <c r="R68" s="3"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J69" s="2"/>
       <c r="K69" s="3"/>
       <c r="L69" s="2"/>
@@ -2243,7 +2240,7 @@
       <c r="Q69" s="2"/>
       <c r="R69" s="3"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="70" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J70" s="2"/>
       <c r="K70" s="3"/>
       <c r="L70" s="2"/>
@@ -2254,7 +2251,7 @@
       <c r="Q70" s="2"/>
       <c r="R70" s="3"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="71" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J71" s="2"/>
       <c r="K71" s="3"/>
       <c r="L71" s="2"/>
@@ -2265,7 +2262,7 @@
       <c r="Q71" s="2"/>
       <c r="R71" s="3"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="72" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J72" s="2"/>
       <c r="K72" s="3"/>
       <c r="L72" s="2"/>
@@ -2276,7 +2273,7 @@
       <c r="Q72" s="2"/>
       <c r="R72" s="3"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="73" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J73" s="2"/>
       <c r="K73" s="3"/>
       <c r="L73" s="2"/>
@@ -2287,7 +2284,7 @@
       <c r="Q73" s="2"/>
       <c r="R73" s="3"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="74" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J74" s="2"/>
       <c r="K74" s="3"/>
       <c r="L74" s="2"/>
@@ -2298,7 +2295,7 @@
       <c r="Q74" s="2"/>
       <c r="R74" s="3"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="75" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J75" s="2"/>
       <c r="K75" s="3"/>
       <c r="L75" s="2"/>
@@ -2309,7 +2306,7 @@
       <c r="Q75" s="2"/>
       <c r="R75" s="3"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="76" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J76" s="2"/>
       <c r="K76" s="3"/>
       <c r="L76" s="2"/>
@@ -2320,7 +2317,7 @@
       <c r="Q76" s="2"/>
       <c r="R76" s="3"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="77" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J77" s="2"/>
       <c r="K77" s="3"/>
       <c r="L77" s="2"/>
@@ -2331,7 +2328,7 @@
       <c r="Q77" s="2"/>
       <c r="R77" s="3"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="78" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J78" s="2"/>
       <c r="K78" s="3"/>
       <c r="L78" s="2"/>
@@ -2342,7 +2339,7 @@
       <c r="Q78" s="2"/>
       <c r="R78" s="3"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="79" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J79" s="2"/>
       <c r="K79" s="3"/>
       <c r="L79" s="2"/>
@@ -2353,7 +2350,7 @@
       <c r="Q79" s="2"/>
       <c r="R79" s="3"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="80" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J80" s="2"/>
       <c r="K80" s="3"/>
       <c r="L80" s="2"/>
@@ -2364,7 +2361,7 @@
       <c r="Q80" s="2"/>
       <c r="R80" s="3"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="81" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J81" s="2"/>
       <c r="K81" s="3"/>
       <c r="L81" s="2"/>
@@ -2375,7 +2372,7 @@
       <c r="Q81" s="2"/>
       <c r="R81" s="3"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="82" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J82" s="2"/>
       <c r="K82" s="3"/>
       <c r="L82" s="2"/>
@@ -2386,7 +2383,7 @@
       <c r="Q82" s="2"/>
       <c r="R82" s="3"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="83" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J83" s="2"/>
       <c r="K83" s="3"/>
       <c r="L83" s="2"/>
@@ -2397,7 +2394,7 @@
       <c r="Q83" s="2"/>
       <c r="R83" s="3"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="84" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J84" s="2"/>
       <c r="K84" s="3"/>
       <c r="L84" s="2"/>
@@ -2408,7 +2405,7 @@
       <c r="Q84" s="2"/>
       <c r="R84" s="3"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="85" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J85" s="2"/>
       <c r="K85" s="3"/>
       <c r="L85" s="2"/>
@@ -2419,7 +2416,7 @@
       <c r="Q85" s="2"/>
       <c r="R85" s="3"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="86" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J86" s="2"/>
       <c r="K86" s="3"/>
       <c r="L86" s="2"/>
@@ -2430,7 +2427,7 @@
       <c r="Q86" s="2"/>
       <c r="R86" s="3"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="87" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J87" s="2"/>
       <c r="K87" s="3"/>
       <c r="L87" s="2"/>
@@ -2441,7 +2438,7 @@
       <c r="Q87" s="2"/>
       <c r="R87" s="3"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="88" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J88" s="2"/>
       <c r="K88" s="3"/>
       <c r="L88" s="2"/>
@@ -2452,7 +2449,7 @@
       <c r="Q88" s="2"/>
       <c r="R88" s="3"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="89" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J89" s="2"/>
       <c r="K89" s="3"/>
       <c r="L89" s="2"/>
@@ -2463,7 +2460,7 @@
       <c r="Q89" s="2"/>
       <c r="R89" s="3"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="90" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J90" s="2"/>
       <c r="K90" s="3"/>
       <c r="L90" s="2"/>
@@ -2474,7 +2471,7 @@
       <c r="Q90" s="2"/>
       <c r="R90" s="3"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="91" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J91" s="2"/>
       <c r="K91" s="3"/>
       <c r="L91" s="2"/>
@@ -2485,7 +2482,7 @@
       <c r="Q91" s="2"/>
       <c r="R91" s="3"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="92" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J92" s="2"/>
       <c r="K92" s="3"/>
       <c r="L92" s="2"/>
@@ -2496,7 +2493,7 @@
       <c r="Q92" s="2"/>
       <c r="R92" s="3"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="93" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J93" s="2"/>
       <c r="K93" s="3"/>
       <c r="L93" s="2"/>
@@ -2507,7 +2504,7 @@
       <c r="Q93" s="2"/>
       <c r="R93" s="3"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="94" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J94" s="2"/>
       <c r="K94" s="3"/>
       <c r="L94" s="2"/>
@@ -2518,7 +2515,7 @@
       <c r="Q94" s="2"/>
       <c r="R94" s="3"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="95" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J95" s="2"/>
       <c r="K95" s="3"/>
       <c r="L95" s="2"/>
@@ -2529,7 +2526,7 @@
       <c r="Q95" s="2"/>
       <c r="R95" s="3"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="96" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J96" s="2"/>
       <c r="K96" s="3"/>
       <c r="L96" s="2"/>
@@ -2540,7 +2537,7 @@
       <c r="Q96" s="2"/>
       <c r="R96" s="3"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="97" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J97" s="2"/>
       <c r="K97" s="3"/>
       <c r="L97" s="2"/>
@@ -2551,7 +2548,7 @@
       <c r="Q97" s="2"/>
       <c r="R97" s="3"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="98" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J98" s="2"/>
       <c r="K98" s="3"/>
       <c r="L98" s="2"/>
@@ -2562,7 +2559,7 @@
       <c r="Q98" s="2"/>
       <c r="R98" s="3"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="99" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J99" s="2"/>
       <c r="K99" s="3"/>
       <c r="L99" s="2"/>
@@ -2573,7 +2570,7 @@
       <c r="Q99" s="2"/>
       <c r="R99" s="3"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="100" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J100" s="2"/>
       <c r="K100" s="3"/>
       <c r="L100" s="2"/>
@@ -2584,7 +2581,7 @@
       <c r="Q100" s="2"/>
       <c r="R100" s="3"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="101" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J101" s="2"/>
       <c r="K101" s="3"/>
       <c r="L101" s="2"/>
@@ -2595,7 +2592,7 @@
       <c r="Q101" s="2"/>
       <c r="R101" s="3"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="102" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J102" s="2"/>
       <c r="K102" s="3"/>
       <c r="L102" s="2"/>
@@ -2606,7 +2603,7 @@
       <c r="Q102" s="2"/>
       <c r="R102" s="3"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="103" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J103" s="2"/>
       <c r="K103" s="3"/>
       <c r="L103" s="2"/>
@@ -2617,7 +2614,7 @@
       <c r="Q103" s="2"/>
       <c r="R103" s="3"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="104" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J104" s="2"/>
       <c r="K104" s="3"/>
       <c r="L104" s="2"/>
@@ -2628,7 +2625,7 @@
       <c r="Q104" s="2"/>
       <c r="R104" s="3"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="105" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J105" s="2"/>
       <c r="K105" s="3"/>
       <c r="L105" s="2"/>
@@ -2639,7 +2636,7 @@
       <c r="Q105" s="2"/>
       <c r="R105" s="3"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="106" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J106" s="2"/>
       <c r="K106" s="3"/>
       <c r="L106" s="2"/>
@@ -2650,7 +2647,7 @@
       <c r="Q106" s="2"/>
       <c r="R106" s="3"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="107" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J107" s="2"/>
       <c r="K107" s="3"/>
       <c r="L107" s="2"/>
@@ -2661,7 +2658,7 @@
       <c r="Q107" s="2"/>
       <c r="R107" s="3"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="108" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J108" s="2"/>
       <c r="K108" s="3"/>
       <c r="L108" s="2"/>
@@ -2672,7 +2669,7 @@
       <c r="Q108" s="2"/>
       <c r="R108" s="3"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="109" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J109" s="2"/>
       <c r="K109" s="3"/>
       <c r="L109" s="2"/>
@@ -2683,7 +2680,7 @@
       <c r="Q109" s="2"/>
       <c r="R109" s="3"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="110" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J110" s="2"/>
       <c r="K110" s="3"/>
       <c r="L110" s="2"/>
@@ -2694,7 +2691,7 @@
       <c r="Q110" s="2"/>
       <c r="R110" s="3"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="111" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J111" s="2"/>
       <c r="K111" s="3"/>
       <c r="L111" s="2"/>
@@ -2705,7 +2702,7 @@
       <c r="Q111" s="2"/>
       <c r="R111" s="3"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="112" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J112" s="2"/>
       <c r="K112" s="3"/>
       <c r="L112" s="2"/>
@@ -2716,7 +2713,7 @@
       <c r="Q112" s="2"/>
       <c r="R112" s="3"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="113" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J113" s="2"/>
       <c r="K113" s="3"/>
       <c r="L113" s="2"/>
@@ -2727,7 +2724,7 @@
       <c r="Q113" s="2"/>
       <c r="R113" s="3"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="114" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J114" s="2"/>
       <c r="K114" s="3"/>
       <c r="L114" s="2"/>
@@ -2738,7 +2735,7 @@
       <c r="Q114" s="2"/>
       <c r="R114" s="3"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="115" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J115" s="2"/>
       <c r="K115" s="3"/>
       <c r="L115" s="2"/>
@@ -2749,7 +2746,7 @@
       <c r="Q115" s="2"/>
       <c r="R115" s="3"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="116" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J116" s="2"/>
       <c r="K116" s="3"/>
       <c r="L116" s="2"/>
@@ -2760,7 +2757,7 @@
       <c r="Q116" s="2"/>
       <c r="R116" s="3"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="117" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J117" s="2"/>
       <c r="K117" s="3"/>
       <c r="L117" s="2"/>
@@ -2771,7 +2768,7 @@
       <c r="Q117" s="2"/>
       <c r="R117" s="3"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="118" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J118" s="2"/>
       <c r="K118" s="3"/>
       <c r="L118" s="2"/>
@@ -2782,7 +2779,7 @@
       <c r="Q118" s="2"/>
       <c r="R118" s="3"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="119" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J119" s="2"/>
       <c r="K119" s="3"/>
       <c r="L119" s="2"/>
@@ -2793,7 +2790,7 @@
       <c r="Q119" s="2"/>
       <c r="R119" s="3"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="120" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J120" s="2"/>
       <c r="K120" s="3"/>
       <c r="L120" s="2"/>
@@ -2804,7 +2801,7 @@
       <c r="Q120" s="2"/>
       <c r="R120" s="3"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="121" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J121" s="2"/>
       <c r="K121" s="3"/>
       <c r="L121" s="2"/>
@@ -2815,7 +2812,7 @@
       <c r="Q121" s="2"/>
       <c r="R121" s="3"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="122" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J122" s="2"/>
       <c r="K122" s="3"/>
       <c r="L122" s="2"/>
@@ -2826,7 +2823,7 @@
       <c r="Q122" s="2"/>
       <c r="R122" s="3"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="123" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J123" s="2"/>
       <c r="K123" s="3"/>
       <c r="L123" s="2"/>
@@ -2837,7 +2834,7 @@
       <c r="Q123" s="2"/>
       <c r="R123" s="3"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="124" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J124" s="2"/>
       <c r="K124" s="3"/>
       <c r="L124" s="2"/>
@@ -2848,7 +2845,7 @@
       <c r="Q124" s="2"/>
       <c r="R124" s="3"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="125" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J125" s="2"/>
       <c r="K125" s="3"/>
       <c r="L125" s="2"/>
@@ -2859,7 +2856,7 @@
       <c r="Q125" s="2"/>
       <c r="R125" s="3"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="126" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J126" s="2"/>
       <c r="K126" s="3"/>
       <c r="L126" s="2"/>
@@ -2870,7 +2867,7 @@
       <c r="Q126" s="2"/>
       <c r="R126" s="3"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="127" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J127" s="2"/>
       <c r="K127" s="3"/>
       <c r="L127" s="2"/>
@@ -2881,7 +2878,7 @@
       <c r="Q127" s="2"/>
       <c r="R127" s="3"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="128" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J128" s="2"/>
       <c r="K128" s="3"/>
       <c r="L128" s="2"/>
@@ -2892,7 +2889,7 @@
       <c r="Q128" s="2"/>
       <c r="R128" s="3"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="129" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J129" s="2"/>
       <c r="K129" s="3"/>
       <c r="L129" s="2"/>
@@ -2903,7 +2900,7 @@
       <c r="Q129" s="2"/>
       <c r="R129" s="3"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="130" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J130" s="2"/>
       <c r="K130" s="3"/>
       <c r="L130" s="2"/>
@@ -2914,7 +2911,7 @@
       <c r="Q130" s="2"/>
       <c r="R130" s="3"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="131" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J131" s="2"/>
       <c r="K131" s="3"/>
       <c r="L131" s="2"/>
@@ -2925,7 +2922,7 @@
       <c r="Q131" s="2"/>
       <c r="R131" s="3"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="132" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J132" s="2"/>
       <c r="K132" s="3"/>
       <c r="L132" s="2"/>
@@ -2936,7 +2933,7 @@
       <c r="Q132" s="2"/>
       <c r="R132" s="3"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="133" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J133" s="2"/>
       <c r="K133" s="3"/>
       <c r="L133" s="2"/>
@@ -2947,7 +2944,7 @@
       <c r="Q133" s="2"/>
       <c r="R133" s="3"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="134" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J134" s="2"/>
       <c r="K134" s="3"/>
       <c r="L134" s="2"/>
@@ -2958,7 +2955,7 @@
       <c r="Q134" s="2"/>
       <c r="R134" s="3"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="135" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J135" s="2"/>
       <c r="K135" s="3"/>
       <c r="L135" s="2"/>
@@ -2969,7 +2966,7 @@
       <c r="Q135" s="2"/>
       <c r="R135" s="3"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="136" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J136" s="2"/>
       <c r="K136" s="3"/>
       <c r="L136" s="2"/>
@@ -2980,7 +2977,7 @@
       <c r="Q136" s="2"/>
       <c r="R136" s="3"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="137" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J137" s="2"/>
       <c r="K137" s="3"/>
       <c r="L137" s="2"/>
@@ -2991,7 +2988,7 @@
       <c r="Q137" s="2"/>
       <c r="R137" s="3"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="138" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J138" s="2"/>
       <c r="K138" s="3"/>
       <c r="L138" s="2"/>
@@ -3002,7 +2999,7 @@
       <c r="Q138" s="2"/>
       <c r="R138" s="3"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="139" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J139" s="2"/>
       <c r="K139" s="3"/>
       <c r="L139" s="2"/>
@@ -3013,7 +3010,7 @@
       <c r="Q139" s="2"/>
       <c r="R139" s="3"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="140" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J140" s="2"/>
       <c r="K140" s="3"/>
       <c r="L140" s="2"/>
@@ -3024,7 +3021,7 @@
       <c r="Q140" s="2"/>
       <c r="R140" s="3"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="141" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J141" s="2"/>
       <c r="K141" s="3"/>
       <c r="L141" s="2"/>
@@ -3035,7 +3032,7 @@
       <c r="Q141" s="2"/>
       <c r="R141" s="3"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="142" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J142" s="2"/>
       <c r="K142" s="3"/>
       <c r="L142" s="2"/>
@@ -3046,7 +3043,7 @@
       <c r="Q142" s="2"/>
       <c r="R142" s="3"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="143" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J143" s="2"/>
       <c r="K143" s="3"/>
       <c r="L143" s="2"/>
@@ -3057,7 +3054,7 @@
       <c r="Q143" s="2"/>
       <c r="R143" s="3"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="144" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J144" s="2"/>
       <c r="K144" s="3"/>
       <c r="L144" s="2"/>
@@ -3068,7 +3065,7 @@
       <c r="Q144" s="2"/>
       <c r="R144" s="3"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="145" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J145" s="2"/>
       <c r="K145" s="3"/>
       <c r="L145" s="2"/>
@@ -3079,7 +3076,7 @@
       <c r="Q145" s="2"/>
       <c r="R145" s="3"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="146" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J146" s="2"/>
       <c r="K146" s="3"/>
       <c r="L146" s="2"/>
@@ -3090,7 +3087,7 @@
       <c r="Q146" s="2"/>
       <c r="R146" s="3"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="147" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J147" s="2"/>
       <c r="K147" s="3"/>
       <c r="L147" s="2"/>
@@ -3101,7 +3098,7 @@
       <c r="Q147" s="2"/>
       <c r="R147" s="3"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="148" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J148" s="2"/>
       <c r="K148" s="3"/>
       <c r="L148" s="2"/>
@@ -3112,7 +3109,7 @@
       <c r="Q148" s="2"/>
       <c r="R148" s="3"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="149" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J149" s="2"/>
       <c r="K149" s="3"/>
       <c r="L149" s="2"/>
@@ -3123,7 +3120,7 @@
       <c r="Q149" s="2"/>
       <c r="R149" s="3"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="150" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J150" s="2"/>
       <c r="K150" s="3"/>
       <c r="L150" s="2"/>
@@ -3134,7 +3131,7 @@
       <c r="Q150" s="2"/>
       <c r="R150" s="3"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="151" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J151" s="2"/>
       <c r="K151" s="3"/>
       <c r="L151" s="2"/>
@@ -3145,7 +3142,7 @@
       <c r="Q151" s="2"/>
       <c r="R151" s="3"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="152" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J152" s="2"/>
       <c r="K152" s="3"/>
       <c r="L152" s="2"/>
@@ -3156,7 +3153,7 @@
       <c r="Q152" s="2"/>
       <c r="R152" s="3"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="153" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J153" s="2"/>
       <c r="K153" s="3"/>
       <c r="L153" s="2"/>
@@ -3167,7 +3164,7 @@
       <c r="Q153" s="2"/>
       <c r="R153" s="3"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="154" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J154" s="2"/>
       <c r="K154" s="3"/>
       <c r="L154" s="2"/>
@@ -3178,7 +3175,7 @@
       <c r="Q154" s="2"/>
       <c r="R154" s="3"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="155" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J155" s="2"/>
       <c r="K155" s="3"/>
       <c r="L155" s="2"/>
@@ -3189,7 +3186,7 @@
       <c r="Q155" s="2"/>
       <c r="R155" s="3"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="156" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J156" s="2"/>
       <c r="K156" s="3"/>
       <c r="L156" s="2"/>
@@ -3200,7 +3197,7 @@
       <c r="Q156" s="2"/>
       <c r="R156" s="3"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="157" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J157" s="2"/>
       <c r="K157" s="3"/>
       <c r="L157" s="2"/>
@@ -3211,7 +3208,7 @@
       <c r="Q157" s="2"/>
       <c r="R157" s="3"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="158" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J158" s="2"/>
       <c r="K158" s="3"/>
       <c r="L158" s="2"/>
@@ -3222,7 +3219,7 @@
       <c r="Q158" s="2"/>
       <c r="R158" s="3"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="159" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J159" s="2"/>
       <c r="K159" s="3"/>
       <c r="L159" s="2"/>
@@ -3233,7 +3230,7 @@
       <c r="Q159" s="2"/>
       <c r="R159" s="3"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="160" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J160" s="2"/>
       <c r="K160" s="3"/>
       <c r="L160" s="2"/>
@@ -3244,7 +3241,7 @@
       <c r="Q160" s="2"/>
       <c r="R160" s="3"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="161" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J161" s="2"/>
       <c r="K161" s="3"/>
       <c r="L161" s="2"/>
@@ -3255,7 +3252,7 @@
       <c r="Q161" s="2"/>
       <c r="R161" s="3"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="162" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J162" s="2"/>
       <c r="K162" s="3"/>
       <c r="L162" s="2"/>
@@ -3266,7 +3263,7 @@
       <c r="Q162" s="2"/>
       <c r="R162" s="3"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="163" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J163" s="2"/>
       <c r="K163" s="3"/>
       <c r="L163" s="2"/>
@@ -3277,7 +3274,7 @@
       <c r="Q163" s="2"/>
       <c r="R163" s="3"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="164" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J164" s="2"/>
       <c r="K164" s="3"/>
       <c r="L164" s="2"/>
@@ -3288,7 +3285,7 @@
       <c r="Q164" s="2"/>
       <c r="R164" s="3"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="165" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J165" s="2"/>
       <c r="K165" s="3"/>
       <c r="L165" s="2"/>
@@ -3299,7 +3296,7 @@
       <c r="Q165" s="2"/>
       <c r="R165" s="3"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="166" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J166" s="2"/>
       <c r="K166" s="3"/>
       <c r="L166" s="2"/>
@@ -3310,7 +3307,7 @@
       <c r="Q166" s="2"/>
       <c r="R166" s="3"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="167" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J167" s="2"/>
       <c r="K167" s="3"/>
       <c r="L167" s="2"/>
@@ -3321,7 +3318,7 @@
       <c r="Q167" s="2"/>
       <c r="R167" s="3"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="168" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J168" s="2"/>
       <c r="K168" s="3"/>
       <c r="L168" s="2"/>
@@ -3332,7 +3329,7 @@
       <c r="Q168" s="2"/>
       <c r="R168" s="3"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="169" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J169" s="2"/>
       <c r="K169" s="3"/>
       <c r="L169" s="2"/>
@@ -3343,7 +3340,7 @@
       <c r="Q169" s="2"/>
       <c r="R169" s="3"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="170" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J170" s="2"/>
       <c r="K170" s="3"/>
       <c r="L170" s="2"/>
@@ -3354,7 +3351,7 @@
       <c r="Q170" s="2"/>
       <c r="R170" s="3"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="171" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J171" s="2"/>
       <c r="K171" s="3"/>
       <c r="L171" s="2"/>
@@ -3365,7 +3362,7 @@
       <c r="Q171" s="2"/>
       <c r="R171" s="3"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="172" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J172" s="2"/>
       <c r="K172" s="3"/>
       <c r="L172" s="2"/>
@@ -3376,7 +3373,7 @@
       <c r="Q172" s="2"/>
       <c r="R172" s="3"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="173" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J173" s="2"/>
       <c r="K173" s="3"/>
       <c r="L173" s="2"/>
@@ -3387,7 +3384,7 @@
       <c r="Q173" s="2"/>
       <c r="R173" s="3"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="174" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J174" s="2"/>
       <c r="K174" s="3"/>
       <c r="L174" s="2"/>
@@ -3398,7 +3395,7 @@
       <c r="Q174" s="2"/>
       <c r="R174" s="3"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="175" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J175" s="2"/>
       <c r="K175" s="3"/>
       <c r="L175" s="2"/>
@@ -3409,7 +3406,7 @@
       <c r="Q175" s="2"/>
       <c r="R175" s="3"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="176" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J176" s="2"/>
       <c r="K176" s="3"/>
       <c r="L176" s="2"/>
@@ -3420,7 +3417,7 @@
       <c r="Q176" s="2"/>
       <c r="R176" s="3"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="177" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J177" s="2"/>
       <c r="K177" s="3"/>
       <c r="L177" s="2"/>
@@ -3431,7 +3428,7 @@
       <c r="Q177" s="2"/>
       <c r="R177" s="3"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="178" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J178" s="2"/>
       <c r="K178" s="3"/>
       <c r="L178" s="2"/>
@@ -3442,7 +3439,7 @@
       <c r="Q178" s="2"/>
       <c r="R178" s="3"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="179" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J179" s="2"/>
       <c r="K179" s="3"/>
       <c r="L179" s="2"/>
@@ -3453,7 +3450,7 @@
       <c r="Q179" s="2"/>
       <c r="R179" s="3"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="180" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J180" s="2"/>
       <c r="K180" s="3"/>
       <c r="L180" s="2"/>
@@ -3464,7 +3461,7 @@
       <c r="Q180" s="2"/>
       <c r="R180" s="3"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="181" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J181" s="2"/>
       <c r="K181" s="3"/>
       <c r="L181" s="2"/>
@@ -3475,7 +3472,7 @@
       <c r="Q181" s="2"/>
       <c r="R181" s="3"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="182" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J182" s="2"/>
       <c r="K182" s="3"/>
       <c r="L182" s="2"/>
@@ -3486,7 +3483,7 @@
       <c r="Q182" s="2"/>
       <c r="R182" s="3"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="183" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J183" s="2"/>
       <c r="K183" s="3"/>
       <c r="L183" s="2"/>
@@ -3497,7 +3494,7 @@
       <c r="Q183" s="2"/>
       <c r="R183" s="3"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="184" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J184" s="2"/>
       <c r="K184" s="3"/>
       <c r="L184" s="2"/>
@@ -3508,7 +3505,7 @@
       <c r="Q184" s="2"/>
       <c r="R184" s="3"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="185" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J185" s="2"/>
       <c r="K185" s="3"/>
       <c r="L185" s="2"/>
@@ -3519,7 +3516,7 @@
       <c r="Q185" s="2"/>
       <c r="R185" s="3"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="186" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J186" s="2"/>
       <c r="K186" s="3"/>
       <c r="L186" s="2"/>
@@ -3530,7 +3527,7 @@
       <c r="Q186" s="2"/>
       <c r="R186" s="3"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="187" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J187" s="2"/>
       <c r="K187" s="3"/>
       <c r="L187" s="2"/>
@@ -3541,7 +3538,7 @@
       <c r="Q187" s="2"/>
       <c r="R187" s="3"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="188" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J188" s="2"/>
       <c r="K188" s="3"/>
       <c r="L188" s="2"/>
@@ -3552,7 +3549,7 @@
       <c r="Q188" s="2"/>
       <c r="R188" s="3"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="189" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J189" s="2"/>
       <c r="K189" s="3"/>
       <c r="L189" s="2"/>
@@ -3563,7 +3560,7 @@
       <c r="Q189" s="2"/>
       <c r="R189" s="3"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="190" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J190" s="2"/>
       <c r="K190" s="3"/>
       <c r="L190" s="2"/>
@@ -3574,7 +3571,7 @@
       <c r="Q190" s="2"/>
       <c r="R190" s="3"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="191" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J191" s="2"/>
       <c r="K191" s="3"/>
       <c r="L191" s="2"/>
@@ -3585,7 +3582,7 @@
       <c r="Q191" s="2"/>
       <c r="R191" s="3"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="192" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J192" s="2"/>
       <c r="K192" s="3"/>
       <c r="L192" s="2"/>
@@ -3596,7 +3593,7 @@
       <c r="Q192" s="2"/>
       <c r="R192" s="3"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="193" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J193" s="2"/>
       <c r="K193" s="3"/>
       <c r="L193" s="2"/>
@@ -3607,7 +3604,7 @@
       <c r="Q193" s="2"/>
       <c r="R193" s="3"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="194" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J194" s="2"/>
       <c r="K194" s="3"/>
       <c r="L194" s="2"/>
@@ -3618,7 +3615,7 @@
       <c r="Q194" s="2"/>
       <c r="R194" s="3"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="195" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J195" s="2"/>
       <c r="K195" s="3"/>
       <c r="L195" s="2"/>
@@ -3629,7 +3626,7 @@
       <c r="Q195" s="2"/>
       <c r="R195" s="3"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="196" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J196" s="2"/>
       <c r="K196" s="3"/>
       <c r="L196" s="2"/>
@@ -3640,7 +3637,7 @@
       <c r="Q196" s="2"/>
       <c r="R196" s="3"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="197" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J197" s="2"/>
       <c r="K197" s="3"/>
       <c r="L197" s="2"/>
@@ -3651,7 +3648,7 @@
       <c r="Q197" s="2"/>
       <c r="R197" s="3"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="198" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J198" s="2"/>
       <c r="K198" s="3"/>
       <c r="L198" s="2"/>
@@ -3662,7 +3659,7 @@
       <c r="Q198" s="2"/>
       <c r="R198" s="3"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="199" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J199" s="2"/>
       <c r="K199" s="3"/>
       <c r="L199" s="2"/>
@@ -3673,7 +3670,7 @@
       <c r="Q199" s="2"/>
       <c r="R199" s="3"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="200" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J200" s="2"/>
       <c r="K200" s="3"/>
       <c r="L200" s="2"/>
@@ -3684,7 +3681,7 @@
       <c r="Q200" s="2"/>
       <c r="R200" s="3"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="201" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J201" s="2"/>
       <c r="K201" s="3"/>
       <c r="L201" s="2"/>
@@ -3695,7 +3692,7 @@
       <c r="Q201" s="2"/>
       <c r="R201" s="3"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="202" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J202" s="2"/>
       <c r="K202" s="3"/>
       <c r="L202" s="2"/>
@@ -3706,7 +3703,7 @@
       <c r="Q202" s="2"/>
       <c r="R202" s="3"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="203" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J203" s="2"/>
       <c r="K203" s="3"/>
       <c r="L203" s="2"/>
@@ -3717,7 +3714,7 @@
       <c r="Q203" s="2"/>
       <c r="R203" s="3"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="204" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J204" s="2"/>
       <c r="K204" s="3"/>
       <c r="L204" s="2"/>
@@ -3728,7 +3725,7 @@
       <c r="Q204" s="2"/>
       <c r="R204" s="3"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="205" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J205" s="2"/>
       <c r="K205" s="3"/>
       <c r="L205" s="2"/>
@@ -3739,7 +3736,7 @@
       <c r="Q205" s="2"/>
       <c r="R205" s="3"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="206" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J206" s="2"/>
       <c r="K206" s="3"/>
       <c r="L206" s="2"/>
@@ -3750,7 +3747,7 @@
       <c r="Q206" s="2"/>
       <c r="R206" s="3"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="207" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J207" s="2"/>
       <c r="K207" s="3"/>
       <c r="L207" s="2"/>
@@ -3761,7 +3758,7 @@
       <c r="Q207" s="2"/>
       <c r="R207" s="3"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="208" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J208" s="2"/>
       <c r="K208" s="3"/>
       <c r="L208" s="2"/>
@@ -3772,7 +3769,7 @@
       <c r="Q208" s="2"/>
       <c r="R208" s="3"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="209" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J209" s="2"/>
       <c r="K209" s="3"/>
       <c r="L209" s="2"/>
@@ -3783,7 +3780,7 @@
       <c r="Q209" s="2"/>
       <c r="R209" s="3"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="210" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J210" s="2"/>
       <c r="K210" s="3"/>
       <c r="L210" s="2"/>
@@ -3794,7 +3791,7 @@
       <c r="Q210" s="2"/>
       <c r="R210" s="3"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="211" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J211" s="2"/>
       <c r="K211" s="3"/>
       <c r="L211" s="2"/>
@@ -3805,7 +3802,7 @@
       <c r="Q211" s="2"/>
       <c r="R211" s="3"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="212" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J212" s="2"/>
       <c r="K212" s="3"/>
       <c r="L212" s="2"/>
@@ -3816,7 +3813,7 @@
       <c r="Q212" s="2"/>
       <c r="R212" s="3"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="213" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J213" s="2"/>
       <c r="K213" s="3"/>
       <c r="L213" s="2"/>
@@ -3827,7 +3824,7 @@
       <c r="Q213" s="2"/>
       <c r="R213" s="3"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="214" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J214" s="2"/>
       <c r="K214" s="3"/>
       <c r="L214" s="2"/>
@@ -3838,7 +3835,7 @@
       <c r="Q214" s="2"/>
       <c r="R214" s="3"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="215" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J215" s="2"/>
       <c r="K215" s="3"/>
       <c r="L215" s="2"/>
@@ -3849,7 +3846,7 @@
       <c r="Q215" s="2"/>
       <c r="R215" s="3"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="216" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J216" s="2"/>
       <c r="K216" s="3"/>
       <c r="L216" s="2"/>
@@ -3860,7 +3857,7 @@
       <c r="Q216" s="2"/>
       <c r="R216" s="3"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="217" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J217" s="2"/>
       <c r="K217" s="3"/>
       <c r="L217" s="2"/>
@@ -3871,7 +3868,7 @@
       <c r="Q217" s="2"/>
       <c r="R217" s="3"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="218" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J218" s="2"/>
       <c r="K218" s="3"/>
       <c r="L218" s="2"/>
@@ -3882,7 +3879,7 @@
       <c r="Q218" s="2"/>
       <c r="R218" s="3"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="219" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J219" s="2"/>
       <c r="K219" s="3"/>
       <c r="L219" s="2"/>
@@ -3893,7 +3890,7 @@
       <c r="Q219" s="2"/>
       <c r="R219" s="3"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="220" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J220" s="2"/>
       <c r="K220" s="3"/>
       <c r="L220" s="2"/>
@@ -3904,7 +3901,17 @@
       <c r="Q220" s="2"/>
       <c r="R220" s="3"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J221" s="2"/>
+      <c r="K221" s="3"/>
+      <c r="L221" s="2"/>
+      <c r="M221" s="2"/>
+      <c r="N221" s="2"/>
+      <c r="O221" s="2"/>
+      <c r="P221" s="2"/>
+      <c r="Q221" s="2"/>
+      <c r="R221" s="3"/>
+    </row>
     <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4684,6 +4691,7 @@
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="F2:H6"/>
@@ -4700,7 +4708,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1000"/>
+  <dimension ref="A1:I1001"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11.1640625"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
@@ -4716,7 +4724,7 @@
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4727,7 +4735,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" s="25"/>
       <c r="E2" s="25"/>
@@ -4756,106 +4764,105 @@
       <c r="C6" s="9"/>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="8"/>
-    </row>
-    <row r="8" ht="54" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+    </row>
+    <row r="8" ht="15.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9"/>
+      <c r="D8" s="8"/>
+    </row>
+    <row r="9" ht="54" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="C9" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="D9" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="E9" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="F9" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="G9" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="H9" s="10" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="26" t="s">
+      <c r="I9" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="27" t="s">
+    </row>
+    <row r="10" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="C10" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="D10" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="E10" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="F10" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="H9" s="26" t="s">
+      <c r="G10" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="I9" s="26" t="s">
+      <c r="H10" s="26" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="30" t="e">
+      <c r="I10" s="26" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="29"/>
+      <c r="C11" s="30" t="e">
         <f>AVERAGE(C$9:C9)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D11" s="29">
         <f>SUM(D$9:D9)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="29">
+      </c>
+      <c r="E11" s="29">
         <f>SUM(E$9:E9)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="29">
+      </c>
+      <c r="F11" s="29">
         <f>SUM(F$9:F9)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="30" t="e">
+      </c>
+      <c r="G11" s="30" t="e">
         <f>AVERAGE(G$9:G9)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H11" s="29">
         <f>SUM(H$9:H9)</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="31">
+      </c>
+      <c r="I11" s="31">
         <f>SUM(I$9:I9)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      </c>
+    </row>
     <row r="12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5845,6 +5852,7 @@
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C2:G2"/>
@@ -5884,7 +5892,7 @@
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6027,7 +6035,9 @@
       <c r="AF4" s="2"/>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
+      <c r="A5" s="24" t="s">
+        <v>6</v>
+      </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -6096,7 +6106,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2">
         <v>2</v>
@@ -6134,67 +6144,67 @@
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K8" s="34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L8" s="34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O8" s="34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P8" s="34" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q8" s="34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="R8" s="34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="S8" s="34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T8" s="34" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U8" s="35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V8" s="36"/>
       <c r="W8" s="36"/>
@@ -6205,13 +6215,13 @@
       <c r="AB8" s="36"/>
       <c r="AC8" s="37"/>
       <c r="AD8" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AE8" s="33" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AF8" s="33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" ht="31.5" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
@@ -6260,7 +6270,7 @@
         <v>2022</v>
       </c>
       <c r="AC9" s="39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AD9" s="38"/>
       <c r="AE9" s="38"/>
@@ -6268,36 +6278,36 @@
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="40" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E10" s="41" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F10" s="42">
         <f>IFERROR(IF(A10="No data","",IF(C10=0,0,D10/C10)),0)</f>
         <v>0</v>
       </c>
       <c r="G10" s="41" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H10" s="43">
         <f>IFERROR(IF(A10="No data","",IF(B10&lt;&gt;0, G10/B10, 0)),0)</f>
         <v>0</v>
       </c>
       <c r="I10" s="41" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J10" s="41" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K10" s="41">
         <f>IFERROR(IF(A10="No data","",U10+V10+W10+X10+Y10+Z10+AA10+AB10+AC10+AD10),0)</f>
@@ -6320,53 +6330,53 @@
         <v>0</v>
       </c>
       <c r="P10" s="41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q10" s="41" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R10" s="41" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S10" s="42">
         <f>IFERROR(IF(A10="No data","",IF(I10=0,0,R10/I10)),0)</f>
         <v>0</v>
       </c>
       <c r="T10" s="44" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U10" s="41" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="V10" s="41" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="W10" s="41" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="X10" s="41" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Y10" s="41" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Z10" s="41" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AA10" s="41" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB10" s="41" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AC10" s="41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AD10" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AE10" s="41" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AF10" s="41">
         <f>IFERROR(IF(A10="No data","",U10+V10+W10+X10+Y10+Z10+AA10+AB10+AC10+AD10+AE10),0)</f>
@@ -6375,7 +6385,7 @@
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="46"/>
       <c r="C11" s="46"/>
@@ -14211,7 +14221,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1000"/>
+  <dimension ref="A1:L1001"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11.1640625"/>
   <cols>
     <col min="1" max="1" width="33.1640625" customWidth="1"/>
@@ -14223,7 +14233,7 @@
   <sheetData>
     <row r="1" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -14317,180 +14327,162 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+    <row r="7" ht="15.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
+    </row>
+    <row r="8" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
         <v>2</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="50" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="L8" s="51" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="38"/>
-      <c r="B9" s="39">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="L9" s="51" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="38"/>
+      <c r="B10" s="39">
         <v>5011</v>
       </c>
-      <c r="C9" s="39">
+      <c r="C10" s="39">
         <v>5007</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D10" s="39">
         <v>5006</v>
       </c>
-      <c r="E9" s="39">
+      <c r="E10" s="39">
         <v>2008</v>
       </c>
-      <c r="F9" s="39">
+      <c r="F10" s="39">
         <v>2005</v>
       </c>
-      <c r="G9" s="39">
+      <c r="G10" s="39">
         <v>2037</v>
       </c>
-      <c r="H9" s="39">
+      <c r="H10" s="39">
         <v>2025</v>
       </c>
-      <c r="I9" s="39">
+      <c r="I10" s="39">
         <v>2022</v>
       </c>
-      <c r="J9" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="40" t="s">
+      <c r="J10" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" s="41" t="s">
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="C11" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="D11" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="E11" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="G10" s="41" t="s">
+      <c r="F11" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="H10" s="41" t="s">
+      <c r="G11" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="I10" s="41" t="s">
+      <c r="H11" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="J10" s="41" t="s">
+      <c r="I11" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="K10" s="41" t="s">
+      <c r="J11" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="L10" s="41" t="e">
+      <c r="K11" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="L11" s="41" t="e">
         <f>B10+C10+D10+E10+F10+G10+H10+I10+J10+K10</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="45" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="46">
+    <row r="12" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="46">
         <f>SUM(B$10:B10)</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="46">
+      </c>
+      <c r="C12" s="46">
         <f>SUM(C$10:C10)</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="46">
+      </c>
+      <c r="D12" s="46">
         <f>SUM(D$10:D10)</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="46">
+      </c>
+      <c r="E12" s="46">
         <f>SUM(E$10:E10)</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="46">
+      </c>
+      <c r="F12" s="46">
         <f>SUM(F$10:F10)</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="46">
+      </c>
+      <c r="G12" s="46">
         <f>SUM(G$10:G10)</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="46">
+      </c>
+      <c r="H12" s="46">
         <f>SUM(H$10:H10)</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="46">
+      </c>
+      <c r="I12" s="46">
         <f>SUM(I$10:I10)</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="46">
+      </c>
+      <c r="J12" s="46">
         <f>SUM(J$10:J10)</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="46">
+      </c>
+      <c r="K12" s="46">
         <f>SUM(K$10:K10)</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="52" t="e">
+      </c>
+      <c r="L12" s="52" t="e">
         <f>SUM(L$10:L10)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -14503,7 +14495,7 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -14516,7 +14508,7 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -14529,7 +14521,7 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -14542,7 +14534,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -14555,7 +14547,7 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -14568,7 +14560,7 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -14581,7 +14573,7 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -14594,7 +14586,7 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -14607,7 +14599,7 @@
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -14620,7 +14612,7 @@
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -14633,7 +14625,7 @@
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -14646,7 +14638,7 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -14659,7 +14651,7 @@
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -14672,7 +14664,7 @@
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -14685,7 +14677,7 @@
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -14698,7 +14690,7 @@
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -14711,7 +14703,7 @@
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -14724,7 +14716,7 @@
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -14737,7 +14729,7 @@
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -14750,7 +14742,7 @@
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -14763,7 +14755,7 @@
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -14776,7 +14768,7 @@
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -14789,7 +14781,7 @@
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -14802,7 +14794,7 @@
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -14815,7 +14807,7 @@
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -14828,7 +14820,7 @@
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="39" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -14841,7 +14833,7 @@
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -14854,7 +14846,7 @@
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="41" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -14867,7 +14859,7 @@
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="42" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -14880,7 +14872,7 @@
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="43" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -14893,7 +14885,7 @@
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="44" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
@@ -14906,7 +14898,7 @@
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="45" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -14919,7 +14911,7 @@
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -14932,7 +14924,7 @@
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="47" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -14945,7 +14937,7 @@
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -14958,7 +14950,7 @@
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="49" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -14971,7 +14963,7 @@
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -14984,7 +14976,7 @@
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="51" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
@@ -14997,7 +14989,7 @@
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -15010,7 +15002,7 @@
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="53" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -15023,7 +15015,7 @@
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -15036,7 +15028,7 @@
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="55" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -15049,7 +15041,7 @@
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
@@ -15062,7 +15054,7 @@
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="57" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -15075,7 +15067,7 @@
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
@@ -15088,7 +15080,7 @@
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="59" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -15101,7 +15093,7 @@
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="60" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
@@ -15114,7 +15106,7 @@
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="61" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
@@ -15127,7 +15119,7 @@
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="62" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -15140,7 +15132,7 @@
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="63" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -15153,7 +15145,7 @@
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="64" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -15166,7 +15158,7 @@
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="65" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -15179,7 +15171,7 @@
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="66" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
@@ -15192,7 +15184,7 @@
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="67" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -15205,7 +15197,7 @@
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="68" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
@@ -15218,7 +15210,7 @@
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -15231,7 +15223,7 @@
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="70" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
@@ -15244,7 +15236,7 @@
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="71" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -15257,7 +15249,7 @@
       <c r="K71" s="2"/>
       <c r="L71" s="2"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="72" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
@@ -15270,7 +15262,7 @@
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="73" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
@@ -15283,7 +15275,7 @@
       <c r="K73" s="2"/>
       <c r="L73" s="2"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="74" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
@@ -15296,7 +15288,7 @@
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="75" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
@@ -15309,7 +15301,7 @@
       <c r="K75" s="2"/>
       <c r="L75" s="2"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="76" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
@@ -15322,7 +15314,7 @@
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="77" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
@@ -15335,7 +15327,7 @@
       <c r="K77" s="2"/>
       <c r="L77" s="2"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="78" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
@@ -15348,7 +15340,7 @@
       <c r="K78" s="2"/>
       <c r="L78" s="2"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="79" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
@@ -15361,7 +15353,7 @@
       <c r="K79" s="2"/>
       <c r="L79" s="2"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="80" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
@@ -15374,7 +15366,7 @@
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="81" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
@@ -15387,7 +15379,7 @@
       <c r="K81" s="2"/>
       <c r="L81" s="2"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="82" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
@@ -15400,7 +15392,7 @@
       <c r="K82" s="2"/>
       <c r="L82" s="2"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="83" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
@@ -15413,7 +15405,7 @@
       <c r="K83" s="2"/>
       <c r="L83" s="2"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="84" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
@@ -15426,7 +15418,7 @@
       <c r="K84" s="2"/>
       <c r="L84" s="2"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="85" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
@@ -15439,7 +15431,7 @@
       <c r="K85" s="2"/>
       <c r="L85" s="2"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="86" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
@@ -15452,7 +15444,7 @@
       <c r="K86" s="2"/>
       <c r="L86" s="2"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="87" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
@@ -15465,7 +15457,7 @@
       <c r="K87" s="2"/>
       <c r="L87" s="2"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="88" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
@@ -15478,7 +15470,7 @@
       <c r="K88" s="2"/>
       <c r="L88" s="2"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="89" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
@@ -15491,7 +15483,7 @@
       <c r="K89" s="2"/>
       <c r="L89" s="2"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="90" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
@@ -15504,7 +15496,7 @@
       <c r="K90" s="2"/>
       <c r="L90" s="2"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="91" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
@@ -15517,7 +15509,7 @@
       <c r="K91" s="2"/>
       <c r="L91" s="2"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="92" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
@@ -15530,7 +15522,7 @@
       <c r="K92" s="2"/>
       <c r="L92" s="2"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="93" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
@@ -15543,7 +15535,7 @@
       <c r="K93" s="2"/>
       <c r="L93" s="2"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="94" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
@@ -15556,7 +15548,7 @@
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="95" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
@@ -15569,7 +15561,7 @@
       <c r="K95" s="2"/>
       <c r="L95" s="2"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="96" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
@@ -15582,7 +15574,7 @@
       <c r="K96" s="2"/>
       <c r="L96" s="2"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="97" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
@@ -15595,7 +15587,7 @@
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="98" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
@@ -15608,7 +15600,7 @@
       <c r="K98" s="2"/>
       <c r="L98" s="2"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="99" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
@@ -15621,7 +15613,7 @@
       <c r="K99" s="2"/>
       <c r="L99" s="2"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="100" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
@@ -15634,7 +15626,7 @@
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="101" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
@@ -15647,7 +15639,7 @@
       <c r="K101" s="2"/>
       <c r="L101" s="2"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="102" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
@@ -15660,7 +15652,7 @@
       <c r="K102" s="2"/>
       <c r="L102" s="2"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="103" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
@@ -15673,7 +15665,7 @@
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="104" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
@@ -15686,7 +15678,7 @@
       <c r="K104" s="2"/>
       <c r="L104" s="2"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="105" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
@@ -15699,7 +15691,7 @@
       <c r="K105" s="2"/>
       <c r="L105" s="2"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="106" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
@@ -15712,7 +15704,7 @@
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="107" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
@@ -15725,7 +15717,7 @@
       <c r="K107" s="2"/>
       <c r="L107" s="2"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="108" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
@@ -15738,7 +15730,7 @@
       <c r="K108" s="2"/>
       <c r="L108" s="2"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="109" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
@@ -15751,7 +15743,7 @@
       <c r="K109" s="2"/>
       <c r="L109" s="2"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="110" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
@@ -15764,7 +15756,7 @@
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="111" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
@@ -15777,7 +15769,7 @@
       <c r="K111" s="2"/>
       <c r="L111" s="2"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="112" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
@@ -15790,7 +15782,7 @@
       <c r="K112" s="2"/>
       <c r="L112" s="2"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="113" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
@@ -15803,7 +15795,7 @@
       <c r="K113" s="2"/>
       <c r="L113" s="2"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="114" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
@@ -15816,7 +15808,7 @@
       <c r="K114" s="2"/>
       <c r="L114" s="2"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="115" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
@@ -15829,7 +15821,7 @@
       <c r="K115" s="2"/>
       <c r="L115" s="2"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="116" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
@@ -15842,7 +15834,7 @@
       <c r="K116" s="2"/>
       <c r="L116" s="2"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="117" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
@@ -15855,7 +15847,7 @@
       <c r="K117" s="2"/>
       <c r="L117" s="2"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="118" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
@@ -15868,7 +15860,7 @@
       <c r="K118" s="2"/>
       <c r="L118" s="2"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="119" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
@@ -15881,7 +15873,7 @@
       <c r="K119" s="2"/>
       <c r="L119" s="2"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="120" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
@@ -15894,7 +15886,7 @@
       <c r="K120" s="2"/>
       <c r="L120" s="2"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="121" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
@@ -15907,7 +15899,7 @@
       <c r="K121" s="2"/>
       <c r="L121" s="2"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="122" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
@@ -15920,7 +15912,7 @@
       <c r="K122" s="2"/>
       <c r="L122" s="2"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="123" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
@@ -15933,7 +15925,7 @@
       <c r="K123" s="2"/>
       <c r="L123" s="2"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="124" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
@@ -15946,7 +15938,7 @@
       <c r="K124" s="2"/>
       <c r="L124" s="2"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="125" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
@@ -15959,7 +15951,7 @@
       <c r="K125" s="2"/>
       <c r="L125" s="2"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="126" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
@@ -15972,7 +15964,7 @@
       <c r="K126" s="2"/>
       <c r="L126" s="2"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="127" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
@@ -15985,7 +15977,7 @@
       <c r="K127" s="2"/>
       <c r="L127" s="2"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="128" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
@@ -15998,7 +15990,7 @@
       <c r="K128" s="2"/>
       <c r="L128" s="2"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="129" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
@@ -16011,7 +16003,7 @@
       <c r="K129" s="2"/>
       <c r="L129" s="2"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="130" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
@@ -16024,7 +16016,7 @@
       <c r="K130" s="2"/>
       <c r="L130" s="2"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="131" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
@@ -16037,7 +16029,7 @@
       <c r="K131" s="2"/>
       <c r="L131" s="2"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="132" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
@@ -16050,7 +16042,7 @@
       <c r="K132" s="2"/>
       <c r="L132" s="2"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="133" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
@@ -16063,7 +16055,7 @@
       <c r="K133" s="2"/>
       <c r="L133" s="2"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="134" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
@@ -16076,7 +16068,7 @@
       <c r="K134" s="2"/>
       <c r="L134" s="2"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="135" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
@@ -16089,7 +16081,7 @@
       <c r="K135" s="2"/>
       <c r="L135" s="2"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="136" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
@@ -16102,7 +16094,7 @@
       <c r="K136" s="2"/>
       <c r="L136" s="2"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="137" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
       <c r="D137" s="2"/>
@@ -16115,7 +16107,7 @@
       <c r="K137" s="2"/>
       <c r="L137" s="2"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="138" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
@@ -16128,7 +16120,7 @@
       <c r="K138" s="2"/>
       <c r="L138" s="2"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="139" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
@@ -16141,7 +16133,7 @@
       <c r="K139" s="2"/>
       <c r="L139" s="2"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="140" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
@@ -16154,7 +16146,7 @@
       <c r="K140" s="2"/>
       <c r="L140" s="2"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="141" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
@@ -16167,7 +16159,7 @@
       <c r="K141" s="2"/>
       <c r="L141" s="2"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="142" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
@@ -16180,7 +16172,7 @@
       <c r="K142" s="2"/>
       <c r="L142" s="2"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="143" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
@@ -16193,7 +16185,7 @@
       <c r="K143" s="2"/>
       <c r="L143" s="2"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="144" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
@@ -16206,7 +16198,7 @@
       <c r="K144" s="2"/>
       <c r="L144" s="2"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="145" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
@@ -16219,7 +16211,7 @@
       <c r="K145" s="2"/>
       <c r="L145" s="2"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="146" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
@@ -16232,7 +16224,7 @@
       <c r="K146" s="2"/>
       <c r="L146" s="2"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="147" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
@@ -16245,7 +16237,7 @@
       <c r="K147" s="2"/>
       <c r="L147" s="2"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="148" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
@@ -16258,7 +16250,7 @@
       <c r="K148" s="2"/>
       <c r="L148" s="2"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="149" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
       <c r="D149" s="2"/>
@@ -16271,7 +16263,7 @@
       <c r="K149" s="2"/>
       <c r="L149" s="2"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="150" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
@@ -16284,7 +16276,7 @@
       <c r="K150" s="2"/>
       <c r="L150" s="2"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="151" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
@@ -16297,7 +16289,7 @@
       <c r="K151" s="2"/>
       <c r="L151" s="2"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="152" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
@@ -16310,7 +16302,7 @@
       <c r="K152" s="2"/>
       <c r="L152" s="2"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="153" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
       <c r="D153" s="2"/>
@@ -16323,7 +16315,7 @@
       <c r="K153" s="2"/>
       <c r="L153" s="2"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="154" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
       <c r="D154" s="2"/>
@@ -16336,7 +16328,7 @@
       <c r="K154" s="2"/>
       <c r="L154" s="2"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="155" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
       <c r="D155" s="2"/>
@@ -16349,7 +16341,7 @@
       <c r="K155" s="2"/>
       <c r="L155" s="2"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="156" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
@@ -16362,7 +16354,7 @@
       <c r="K156" s="2"/>
       <c r="L156" s="2"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="157" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
@@ -16375,7 +16367,7 @@
       <c r="K157" s="2"/>
       <c r="L157" s="2"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="158" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
       <c r="D158" s="2"/>
@@ -16388,7 +16380,7 @@
       <c r="K158" s="2"/>
       <c r="L158" s="2"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="159" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
       <c r="D159" s="2"/>
@@ -16401,7 +16393,7 @@
       <c r="K159" s="2"/>
       <c r="L159" s="2"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="160" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
       <c r="D160" s="2"/>
@@ -16414,7 +16406,7 @@
       <c r="K160" s="2"/>
       <c r="L160" s="2"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="161" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
@@ -16427,7 +16419,7 @@
       <c r="K161" s="2"/>
       <c r="L161" s="2"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="162" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
       <c r="D162" s="2"/>
@@ -16440,7 +16432,7 @@
       <c r="K162" s="2"/>
       <c r="L162" s="2"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="163" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
       <c r="D163" s="2"/>
@@ -16453,7 +16445,7 @@
       <c r="K163" s="2"/>
       <c r="L163" s="2"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="164" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
@@ -16466,7 +16458,7 @@
       <c r="K164" s="2"/>
       <c r="L164" s="2"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="165" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
@@ -16479,7 +16471,7 @@
       <c r="K165" s="2"/>
       <c r="L165" s="2"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="166" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
       <c r="D166" s="2"/>
@@ -16492,7 +16484,7 @@
       <c r="K166" s="2"/>
       <c r="L166" s="2"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="167" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
       <c r="D167" s="2"/>
@@ -16505,7 +16497,7 @@
       <c r="K167" s="2"/>
       <c r="L167" s="2"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="168" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
@@ -16518,7 +16510,7 @@
       <c r="K168" s="2"/>
       <c r="L168" s="2"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="169" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
       <c r="D169" s="2"/>
@@ -16531,7 +16523,7 @@
       <c r="K169" s="2"/>
       <c r="L169" s="2"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="170" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
       <c r="D170" s="2"/>
@@ -16544,7 +16536,7 @@
       <c r="K170" s="2"/>
       <c r="L170" s="2"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="171" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
@@ -16557,7 +16549,7 @@
       <c r="K171" s="2"/>
       <c r="L171" s="2"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="172" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
@@ -16570,7 +16562,7 @@
       <c r="K172" s="2"/>
       <c r="L172" s="2"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="173" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
@@ -16583,7 +16575,7 @@
       <c r="K173" s="2"/>
       <c r="L173" s="2"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="174" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
@@ -16596,7 +16588,7 @@
       <c r="K174" s="2"/>
       <c r="L174" s="2"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="175" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
@@ -16609,7 +16601,7 @@
       <c r="K175" s="2"/>
       <c r="L175" s="2"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="176" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
@@ -16622,7 +16614,7 @@
       <c r="K176" s="2"/>
       <c r="L176" s="2"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="177" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
@@ -16635,7 +16627,7 @@
       <c r="K177" s="2"/>
       <c r="L177" s="2"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="178" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
@@ -16648,7 +16640,7 @@
       <c r="K178" s="2"/>
       <c r="L178" s="2"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="179" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
@@ -16661,7 +16653,7 @@
       <c r="K179" s="2"/>
       <c r="L179" s="2"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="180" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
@@ -16674,7 +16666,7 @@
       <c r="K180" s="2"/>
       <c r="L180" s="2"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="181" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
@@ -16687,7 +16679,7 @@
       <c r="K181" s="2"/>
       <c r="L181" s="2"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="182" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
       <c r="D182" s="2"/>
@@ -16700,7 +16692,7 @@
       <c r="K182" s="2"/>
       <c r="L182" s="2"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="183" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
       <c r="D183" s="2"/>
@@ -16713,7 +16705,7 @@
       <c r="K183" s="2"/>
       <c r="L183" s="2"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="184" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
@@ -16726,7 +16718,7 @@
       <c r="K184" s="2"/>
       <c r="L184" s="2"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="185" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
@@ -16739,7 +16731,7 @@
       <c r="K185" s="2"/>
       <c r="L185" s="2"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="186" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
@@ -16752,7 +16744,7 @@
       <c r="K186" s="2"/>
       <c r="L186" s="2"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="187" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
@@ -16765,7 +16757,7 @@
       <c r="K187" s="2"/>
       <c r="L187" s="2"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="188" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
@@ -16778,7 +16770,7 @@
       <c r="K188" s="2"/>
       <c r="L188" s="2"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="189" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
@@ -16791,7 +16783,7 @@
       <c r="K189" s="2"/>
       <c r="L189" s="2"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="190" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
       <c r="D190" s="2"/>
@@ -16804,7 +16796,7 @@
       <c r="K190" s="2"/>
       <c r="L190" s="2"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="191" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
       <c r="D191" s="2"/>
@@ -16817,7 +16809,7 @@
       <c r="K191" s="2"/>
       <c r="L191" s="2"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="192" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
@@ -16830,7 +16822,7 @@
       <c r="K192" s="2"/>
       <c r="L192" s="2"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="193" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
@@ -16843,7 +16835,7 @@
       <c r="K193" s="2"/>
       <c r="L193" s="2"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="194" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
@@ -16856,7 +16848,7 @@
       <c r="K194" s="2"/>
       <c r="L194" s="2"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="195" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
       <c r="D195" s="2"/>
@@ -16869,7 +16861,7 @@
       <c r="K195" s="2"/>
       <c r="L195" s="2"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="196" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
@@ -16882,7 +16874,7 @@
       <c r="K196" s="2"/>
       <c r="L196" s="2"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="197" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
       <c r="D197" s="2"/>
@@ -16895,7 +16887,7 @@
       <c r="K197" s="2"/>
       <c r="L197" s="2"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="198" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
@@ -16908,7 +16900,7 @@
       <c r="K198" s="2"/>
       <c r="L198" s="2"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="199" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
@@ -16921,7 +16913,7 @@
       <c r="K199" s="2"/>
       <c r="L199" s="2"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="200" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
@@ -16934,7 +16926,7 @@
       <c r="K200" s="2"/>
       <c r="L200" s="2"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="201" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
@@ -16947,7 +16939,7 @@
       <c r="K201" s="2"/>
       <c r="L201" s="2"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="202" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
@@ -16960,7 +16952,7 @@
       <c r="K202" s="2"/>
       <c r="L202" s="2"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="203" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
@@ -16973,7 +16965,7 @@
       <c r="K203" s="2"/>
       <c r="L203" s="2"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="204" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
@@ -16986,7 +16978,7 @@
       <c r="K204" s="2"/>
       <c r="L204" s="2"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="205" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
@@ -16999,7 +16991,7 @@
       <c r="K205" s="2"/>
       <c r="L205" s="2"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="206" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
@@ -17012,7 +17004,7 @@
       <c r="K206" s="2"/>
       <c r="L206" s="2"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="207" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
       <c r="D207" s="2"/>
@@ -17025,7 +17017,7 @@
       <c r="K207" s="2"/>
       <c r="L207" s="2"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="208" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
       <c r="D208" s="2"/>
@@ -17038,7 +17030,7 @@
       <c r="K208" s="2"/>
       <c r="L208" s="2"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="209" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
@@ -17051,7 +17043,7 @@
       <c r="K209" s="2"/>
       <c r="L209" s="2"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="210" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
       <c r="D210" s="2"/>
@@ -17064,7 +17056,7 @@
       <c r="K210" s="2"/>
       <c r="L210" s="2"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="211" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
       <c r="D211" s="2"/>
@@ -17077,7 +17069,7 @@
       <c r="K211" s="2"/>
       <c r="L211" s="2"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="212" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
@@ -17090,7 +17082,7 @@
       <c r="K212" s="2"/>
       <c r="L212" s="2"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="213" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
       <c r="D213" s="2"/>
@@ -17103,7 +17095,7 @@
       <c r="K213" s="2"/>
       <c r="L213" s="2"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="214" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>
@@ -17116,7 +17108,7 @@
       <c r="K214" s="2"/>
       <c r="L214" s="2"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="215" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
       <c r="D215" s="2"/>
@@ -17129,7 +17121,7 @@
       <c r="K215" s="2"/>
       <c r="L215" s="2"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="216" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
       <c r="D216" s="2"/>
@@ -17142,7 +17134,7 @@
       <c r="K216" s="2"/>
       <c r="L216" s="2"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="217" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
       <c r="D217" s="2"/>
@@ -17155,7 +17147,7 @@
       <c r="K217" s="2"/>
       <c r="L217" s="2"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="218" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
       <c r="D218" s="2"/>
@@ -17168,7 +17160,7 @@
       <c r="K218" s="2"/>
       <c r="L218" s="2"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="219" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
       <c r="D219" s="2"/>
@@ -17181,7 +17173,7 @@
       <c r="K219" s="2"/>
       <c r="L219" s="2"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="220" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
       <c r="D220" s="2"/>
@@ -17194,7 +17186,19 @@
       <c r="K220" s="2"/>
       <c r="L220" s="2"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B221" s="2"/>
+      <c r="C221" s="2"/>
+      <c r="D221" s="2"/>
+      <c r="E221" s="2"/>
+      <c r="F221" s="2"/>
+      <c r="G221" s="2"/>
+      <c r="H221" s="2"/>
+      <c r="I221" s="2"/>
+      <c r="J221" s="2"/>
+      <c r="K221" s="2"/>
+      <c r="L221" s="2"/>
+    </row>
     <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -17974,12 +17978,13 @@
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B8:J8"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L9:L10"/>
   </mergeCells>
   <conditionalFormatting sqref="L10">
     <cfRule type="notContainsBlanks" dxfId="2" priority="1" operator="notContainsBlanks">
@@ -18005,13 +18010,13 @@
   <sheetData>
     <row r="2" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" s="53" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C2" s="53" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D2" s="53" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18019,10 +18024,10 @@
         <v>1001</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18030,10 +18035,10 @@
         <v>1002</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D4" s="59" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18041,10 +18046,10 @@
         <v>1004</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D5" s="62" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18052,10 +18057,10 @@
         <v>1005</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18063,10 +18068,10 @@
         <v>1006</v>
       </c>
       <c r="C7" s="61" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D7" s="62" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18074,10 +18079,10 @@
         <v>1007</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D8" s="59" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18085,10 +18090,10 @@
         <v>1017</v>
       </c>
       <c r="C9" s="61" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D9" s="62" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18096,10 +18101,10 @@
         <v>1018</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D10" s="59" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18107,10 +18112,10 @@
         <v>2003</v>
       </c>
       <c r="C11" s="61" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D11" s="62" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18118,10 +18123,10 @@
         <v>2005</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D12" s="59" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18129,10 +18134,10 @@
         <v>2008</v>
       </c>
       <c r="C13" s="61" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D13" s="62" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18140,10 +18145,10 @@
         <v>2009</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18151,10 +18156,10 @@
         <v>2011</v>
       </c>
       <c r="C15" s="61" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D15" s="62" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18162,10 +18167,10 @@
         <v>2014</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18173,10 +18178,10 @@
         <v>2016</v>
       </c>
       <c r="C17" s="61" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D17" s="62" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18184,10 +18189,10 @@
         <v>2018</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D18" s="59" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18195,10 +18200,10 @@
         <v>2022</v>
       </c>
       <c r="C19" s="61" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D19" s="62" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18206,10 +18211,10 @@
         <v>2025</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D20" s="59" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18217,10 +18222,10 @@
         <v>2032</v>
       </c>
       <c r="C21" s="61" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D21" s="62" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18228,10 +18233,10 @@
         <v>2034</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D22" s="59" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18239,10 +18244,10 @@
         <v>2037</v>
       </c>
       <c r="C23" s="61" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D23" s="62" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18250,10 +18255,10 @@
         <v>4010</v>
       </c>
       <c r="C24" s="58" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D24" s="59" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18261,10 +18266,10 @@
         <v>4017</v>
       </c>
       <c r="C25" s="61" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D25" s="62" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18272,10 +18277,10 @@
         <v>5006</v>
       </c>
       <c r="C26" s="58" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D26" s="59" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18283,10 +18288,10 @@
         <v>5007</v>
       </c>
       <c r="C27" s="61" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D27" s="62" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -18294,10 +18299,10 @@
         <v>5011</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D28" s="65" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/api/templates/device_and_site_summary_report/fr.xlsx
+++ b/api/templates/device_and_site_summary_report/fr.xlsx
@@ -916,7 +916,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1598,7 +1598,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" ht="15.75" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
       <c r="D12" s="22"/>
@@ -1613,7 +1613,7 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J13" s="2"/>
       <c r="K13" s="3"/>
       <c r="L13" s="2"/>
@@ -1624,7 +1624,7 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J14" s="2"/>
       <c r="K14" s="3"/>
       <c r="L14" s="2"/>
@@ -1635,7 +1635,7 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J15" s="2"/>
       <c r="K15" s="3"/>
       <c r="L15" s="2"/>
@@ -1646,7 +1646,7 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J16" s="2"/>
       <c r="K16" s="3"/>
       <c r="L16" s="2"/>
@@ -1657,7 +1657,7 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="3"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J17" s="2"/>
       <c r="K17" s="3"/>
       <c r="L17" s="2"/>
@@ -1668,7 +1668,7 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="3"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J18" s="2"/>
       <c r="K18" s="3"/>
       <c r="L18" s="2"/>
@@ -1679,7 +1679,7 @@
       <c r="Q18" s="2"/>
       <c r="R18" s="3"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J19" s="2"/>
       <c r="K19" s="3"/>
       <c r="L19" s="2"/>
@@ -1690,7 +1690,7 @@
       <c r="Q19" s="2"/>
       <c r="R19" s="3"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J20" s="2"/>
       <c r="K20" s="3"/>
       <c r="L20" s="2"/>
@@ -1701,7 +1701,7 @@
       <c r="Q20" s="2"/>
       <c r="R20" s="3"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J21" s="2"/>
       <c r="K21" s="3"/>
       <c r="L21" s="2"/>
@@ -1712,7 +1712,7 @@
       <c r="Q21" s="2"/>
       <c r="R21" s="3"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J22" s="2"/>
       <c r="K22" s="3"/>
       <c r="L22" s="2"/>
@@ -1723,7 +1723,7 @@
       <c r="Q22" s="2"/>
       <c r="R22" s="3"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J23" s="2"/>
       <c r="K23" s="3"/>
       <c r="L23" s="2"/>
@@ -1734,7 +1734,7 @@
       <c r="Q23" s="2"/>
       <c r="R23" s="3"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J24" s="2"/>
       <c r="K24" s="3"/>
       <c r="L24" s="2"/>
@@ -1745,7 +1745,7 @@
       <c r="Q24" s="2"/>
       <c r="R24" s="3"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J25" s="2"/>
       <c r="K25" s="3"/>
       <c r="L25" s="2"/>
@@ -1756,7 +1756,7 @@
       <c r="Q25" s="2"/>
       <c r="R25" s="3"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J26" s="2"/>
       <c r="K26" s="3"/>
       <c r="L26" s="2"/>
@@ -1767,7 +1767,7 @@
       <c r="Q26" s="2"/>
       <c r="R26" s="3"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J27" s="2"/>
       <c r="K27" s="3"/>
       <c r="L27" s="2"/>
@@ -1778,7 +1778,7 @@
       <c r="Q27" s="2"/>
       <c r="R27" s="3"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J28" s="2"/>
       <c r="K28" s="3"/>
       <c r="L28" s="2"/>
@@ -1789,7 +1789,7 @@
       <c r="Q28" s="2"/>
       <c r="R28" s="3"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J29" s="2"/>
       <c r="K29" s="3"/>
       <c r="L29" s="2"/>
@@ -1800,7 +1800,7 @@
       <c r="Q29" s="2"/>
       <c r="R29" s="3"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J30" s="2"/>
       <c r="K30" s="3"/>
       <c r="L30" s="2"/>
@@ -1811,7 +1811,7 @@
       <c r="Q30" s="2"/>
       <c r="R30" s="3"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J31" s="2"/>
       <c r="K31" s="3"/>
       <c r="L31" s="2"/>
@@ -1822,7 +1822,7 @@
       <c r="Q31" s="2"/>
       <c r="R31" s="3"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J32" s="2"/>
       <c r="K32" s="3"/>
       <c r="L32" s="2"/>
@@ -1833,7 +1833,7 @@
       <c r="Q32" s="2"/>
       <c r="R32" s="3"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J33" s="2"/>
       <c r="K33" s="3"/>
       <c r="L33" s="2"/>
@@ -1844,7 +1844,7 @@
       <c r="Q33" s="2"/>
       <c r="R33" s="3"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J34" s="2"/>
       <c r="K34" s="3"/>
       <c r="L34" s="2"/>
@@ -1855,7 +1855,7 @@
       <c r="Q34" s="2"/>
       <c r="R34" s="3"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J35" s="2"/>
       <c r="K35" s="3"/>
       <c r="L35" s="2"/>
@@ -1866,7 +1866,7 @@
       <c r="Q35" s="2"/>
       <c r="R35" s="3"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J36" s="2"/>
       <c r="K36" s="3"/>
       <c r="L36" s="2"/>
@@ -1877,7 +1877,7 @@
       <c r="Q36" s="2"/>
       <c r="R36" s="3"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J37" s="2"/>
       <c r="K37" s="3"/>
       <c r="L37" s="2"/>
@@ -1888,7 +1888,7 @@
       <c r="Q37" s="2"/>
       <c r="R37" s="3"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J38" s="2"/>
       <c r="K38" s="3"/>
       <c r="L38" s="2"/>
@@ -1899,7 +1899,7 @@
       <c r="Q38" s="2"/>
       <c r="R38" s="3"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J39" s="2"/>
       <c r="K39" s="3"/>
       <c r="L39" s="2"/>
@@ -1910,7 +1910,7 @@
       <c r="Q39" s="2"/>
       <c r="R39" s="3"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J40" s="2"/>
       <c r="K40" s="3"/>
       <c r="L40" s="2"/>
@@ -1921,7 +1921,7 @@
       <c r="Q40" s="2"/>
       <c r="R40" s="3"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J41" s="2"/>
       <c r="K41" s="3"/>
       <c r="L41" s="2"/>
@@ -1932,7 +1932,7 @@
       <c r="Q41" s="2"/>
       <c r="R41" s="3"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J42" s="2"/>
       <c r="K42" s="3"/>
       <c r="L42" s="2"/>
@@ -1943,7 +1943,7 @@
       <c r="Q42" s="2"/>
       <c r="R42" s="3"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J43" s="2"/>
       <c r="K43" s="3"/>
       <c r="L43" s="2"/>
@@ -1954,7 +1954,7 @@
       <c r="Q43" s="2"/>
       <c r="R43" s="3"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J44" s="2"/>
       <c r="K44" s="3"/>
       <c r="L44" s="2"/>
@@ -1965,7 +1965,7 @@
       <c r="Q44" s="2"/>
       <c r="R44" s="3"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J45" s="2"/>
       <c r="K45" s="3"/>
       <c r="L45" s="2"/>
@@ -1976,7 +1976,7 @@
       <c r="Q45" s="2"/>
       <c r="R45" s="3"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J46" s="2"/>
       <c r="K46" s="3"/>
       <c r="L46" s="2"/>
@@ -1987,7 +1987,7 @@
       <c r="Q46" s="2"/>
       <c r="R46" s="3"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J47" s="2"/>
       <c r="K47" s="3"/>
       <c r="L47" s="2"/>
@@ -1998,7 +1998,7 @@
       <c r="Q47" s="2"/>
       <c r="R47" s="3"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J48" s="2"/>
       <c r="K48" s="3"/>
       <c r="L48" s="2"/>
@@ -2009,7 +2009,7 @@
       <c r="Q48" s="2"/>
       <c r="R48" s="3"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J49" s="2"/>
       <c r="K49" s="3"/>
       <c r="L49" s="2"/>
@@ -2020,7 +2020,7 @@
       <c r="Q49" s="2"/>
       <c r="R49" s="3"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J50" s="2"/>
       <c r="K50" s="3"/>
       <c r="L50" s="2"/>
@@ -2031,7 +2031,7 @@
       <c r="Q50" s="2"/>
       <c r="R50" s="3"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J51" s="2"/>
       <c r="K51" s="3"/>
       <c r="L51" s="2"/>
@@ -2042,7 +2042,7 @@
       <c r="Q51" s="2"/>
       <c r="R51" s="3"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J52" s="2"/>
       <c r="K52" s="3"/>
       <c r="L52" s="2"/>
@@ -2053,7 +2053,7 @@
       <c r="Q52" s="2"/>
       <c r="R52" s="3"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J53" s="2"/>
       <c r="K53" s="3"/>
       <c r="L53" s="2"/>
@@ -2064,7 +2064,7 @@
       <c r="Q53" s="2"/>
       <c r="R53" s="3"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J54" s="2"/>
       <c r="K54" s="3"/>
       <c r="L54" s="2"/>
@@ -2075,7 +2075,7 @@
       <c r="Q54" s="2"/>
       <c r="R54" s="3"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J55" s="2"/>
       <c r="K55" s="3"/>
       <c r="L55" s="2"/>
@@ -2086,7 +2086,7 @@
       <c r="Q55" s="2"/>
       <c r="R55" s="3"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J56" s="2"/>
       <c r="K56" s="3"/>
       <c r="L56" s="2"/>
@@ -2097,7 +2097,7 @@
       <c r="Q56" s="2"/>
       <c r="R56" s="3"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J57" s="2"/>
       <c r="K57" s="3"/>
       <c r="L57" s="2"/>
@@ -2108,7 +2108,7 @@
       <c r="Q57" s="2"/>
       <c r="R57" s="3"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J58" s="2"/>
       <c r="K58" s="3"/>
       <c r="L58" s="2"/>
@@ -2119,7 +2119,7 @@
       <c r="Q58" s="2"/>
       <c r="R58" s="3"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J59" s="2"/>
       <c r="K59" s="3"/>
       <c r="L59" s="2"/>
@@ -2130,7 +2130,7 @@
       <c r="Q59" s="2"/>
       <c r="R59" s="3"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J60" s="2"/>
       <c r="K60" s="3"/>
       <c r="L60" s="2"/>
@@ -2141,7 +2141,7 @@
       <c r="Q60" s="2"/>
       <c r="R60" s="3"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J61" s="2"/>
       <c r="K61" s="3"/>
       <c r="L61" s="2"/>
@@ -2152,7 +2152,7 @@
       <c r="Q61" s="2"/>
       <c r="R61" s="3"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J62" s="2"/>
       <c r="K62" s="3"/>
       <c r="L62" s="2"/>
@@ -2163,7 +2163,7 @@
       <c r="Q62" s="2"/>
       <c r="R62" s="3"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J63" s="2"/>
       <c r="K63" s="3"/>
       <c r="L63" s="2"/>
@@ -2174,7 +2174,7 @@
       <c r="Q63" s="2"/>
       <c r="R63" s="3"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J64" s="2"/>
       <c r="K64" s="3"/>
       <c r="L64" s="2"/>
@@ -2185,7 +2185,7 @@
       <c r="Q64" s="2"/>
       <c r="R64" s="3"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J65" s="2"/>
       <c r="K65" s="3"/>
       <c r="L65" s="2"/>
@@ -2196,7 +2196,7 @@
       <c r="Q65" s="2"/>
       <c r="R65" s="3"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J66" s="2"/>
       <c r="K66" s="3"/>
       <c r="L66" s="2"/>
@@ -2207,7 +2207,7 @@
       <c r="Q66" s="2"/>
       <c r="R66" s="3"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J67" s="2"/>
       <c r="K67" s="3"/>
       <c r="L67" s="2"/>
@@ -2218,7 +2218,7 @@
       <c r="Q67" s="2"/>
       <c r="R67" s="3"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J68" s="2"/>
       <c r="K68" s="3"/>
       <c r="L68" s="2"/>
@@ -2229,7 +2229,7 @@
       <c r="Q68" s="2"/>
       <c r="R68" s="3"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J69" s="2"/>
       <c r="K69" s="3"/>
       <c r="L69" s="2"/>
@@ -2240,7 +2240,7 @@
       <c r="Q69" s="2"/>
       <c r="R69" s="3"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J70" s="2"/>
       <c r="K70" s="3"/>
       <c r="L70" s="2"/>
@@ -2251,7 +2251,7 @@
       <c r="Q70" s="2"/>
       <c r="R70" s="3"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J71" s="2"/>
       <c r="K71" s="3"/>
       <c r="L71" s="2"/>
@@ -2262,7 +2262,7 @@
       <c r="Q71" s="2"/>
       <c r="R71" s="3"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J72" s="2"/>
       <c r="K72" s="3"/>
       <c r="L72" s="2"/>
@@ -2273,7 +2273,7 @@
       <c r="Q72" s="2"/>
       <c r="R72" s="3"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J73" s="2"/>
       <c r="K73" s="3"/>
       <c r="L73" s="2"/>
@@ -2284,7 +2284,7 @@
       <c r="Q73" s="2"/>
       <c r="R73" s="3"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J74" s="2"/>
       <c r="K74" s="3"/>
       <c r="L74" s="2"/>
@@ -2295,7 +2295,7 @@
       <c r="Q74" s="2"/>
       <c r="R74" s="3"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J75" s="2"/>
       <c r="K75" s="3"/>
       <c r="L75" s="2"/>
@@ -2306,7 +2306,7 @@
       <c r="Q75" s="2"/>
       <c r="R75" s="3"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J76" s="2"/>
       <c r="K76" s="3"/>
       <c r="L76" s="2"/>
@@ -2317,7 +2317,7 @@
       <c r="Q76" s="2"/>
       <c r="R76" s="3"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J77" s="2"/>
       <c r="K77" s="3"/>
       <c r="L77" s="2"/>
@@ -2328,7 +2328,7 @@
       <c r="Q77" s="2"/>
       <c r="R77" s="3"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J78" s="2"/>
       <c r="K78" s="3"/>
       <c r="L78" s="2"/>
@@ -2339,7 +2339,7 @@
       <c r="Q78" s="2"/>
       <c r="R78" s="3"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J79" s="2"/>
       <c r="K79" s="3"/>
       <c r="L79" s="2"/>
@@ -2350,7 +2350,7 @@
       <c r="Q79" s="2"/>
       <c r="R79" s="3"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J80" s="2"/>
       <c r="K80" s="3"/>
       <c r="L80" s="2"/>
@@ -2361,7 +2361,7 @@
       <c r="Q80" s="2"/>
       <c r="R80" s="3"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J81" s="2"/>
       <c r="K81" s="3"/>
       <c r="L81" s="2"/>
@@ -2372,7 +2372,7 @@
       <c r="Q81" s="2"/>
       <c r="R81" s="3"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J82" s="2"/>
       <c r="K82" s="3"/>
       <c r="L82" s="2"/>
@@ -2383,7 +2383,7 @@
       <c r="Q82" s="2"/>
       <c r="R82" s="3"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J83" s="2"/>
       <c r="K83" s="3"/>
       <c r="L83" s="2"/>
@@ -2394,7 +2394,7 @@
       <c r="Q83" s="2"/>
       <c r="R83" s="3"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J84" s="2"/>
       <c r="K84" s="3"/>
       <c r="L84" s="2"/>
@@ -2405,7 +2405,7 @@
       <c r="Q84" s="2"/>
       <c r="R84" s="3"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J85" s="2"/>
       <c r="K85" s="3"/>
       <c r="L85" s="2"/>
@@ -2416,7 +2416,7 @@
       <c r="Q85" s="2"/>
       <c r="R85" s="3"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J86" s="2"/>
       <c r="K86" s="3"/>
       <c r="L86" s="2"/>
@@ -2427,7 +2427,7 @@
       <c r="Q86" s="2"/>
       <c r="R86" s="3"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J87" s="2"/>
       <c r="K87" s="3"/>
       <c r="L87" s="2"/>
@@ -2438,7 +2438,7 @@
       <c r="Q87" s="2"/>
       <c r="R87" s="3"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J88" s="2"/>
       <c r="K88" s="3"/>
       <c r="L88" s="2"/>
@@ -2449,7 +2449,7 @@
       <c r="Q88" s="2"/>
       <c r="R88" s="3"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J89" s="2"/>
       <c r="K89" s="3"/>
       <c r="L89" s="2"/>
@@ -2460,7 +2460,7 @@
       <c r="Q89" s="2"/>
       <c r="R89" s="3"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J90" s="2"/>
       <c r="K90" s="3"/>
       <c r="L90" s="2"/>
@@ -2471,7 +2471,7 @@
       <c r="Q90" s="2"/>
       <c r="R90" s="3"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J91" s="2"/>
       <c r="K91" s="3"/>
       <c r="L91" s="2"/>
@@ -2482,7 +2482,7 @@
       <c r="Q91" s="2"/>
       <c r="R91" s="3"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J92" s="2"/>
       <c r="K92" s="3"/>
       <c r="L92" s="2"/>
@@ -2493,7 +2493,7 @@
       <c r="Q92" s="2"/>
       <c r="R92" s="3"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J93" s="2"/>
       <c r="K93" s="3"/>
       <c r="L93" s="2"/>
@@ -2504,7 +2504,7 @@
       <c r="Q93" s="2"/>
       <c r="R93" s="3"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J94" s="2"/>
       <c r="K94" s="3"/>
       <c r="L94" s="2"/>
@@ -2515,7 +2515,7 @@
       <c r="Q94" s="2"/>
       <c r="R94" s="3"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J95" s="2"/>
       <c r="K95" s="3"/>
       <c r="L95" s="2"/>
@@ -2526,7 +2526,7 @@
       <c r="Q95" s="2"/>
       <c r="R95" s="3"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J96" s="2"/>
       <c r="K96" s="3"/>
       <c r="L96" s="2"/>
@@ -2537,7 +2537,7 @@
       <c r="Q96" s="2"/>
       <c r="R96" s="3"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J97" s="2"/>
       <c r="K97" s="3"/>
       <c r="L97" s="2"/>
@@ -2548,7 +2548,7 @@
       <c r="Q97" s="2"/>
       <c r="R97" s="3"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J98" s="2"/>
       <c r="K98" s="3"/>
       <c r="L98" s="2"/>
@@ -2559,7 +2559,7 @@
       <c r="Q98" s="2"/>
       <c r="R98" s="3"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J99" s="2"/>
       <c r="K99" s="3"/>
       <c r="L99" s="2"/>
@@ -2570,7 +2570,7 @@
       <c r="Q99" s="2"/>
       <c r="R99" s="3"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J100" s="2"/>
       <c r="K100" s="3"/>
       <c r="L100" s="2"/>
@@ -2581,7 +2581,7 @@
       <c r="Q100" s="2"/>
       <c r="R100" s="3"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J101" s="2"/>
       <c r="K101" s="3"/>
       <c r="L101" s="2"/>
@@ -2592,7 +2592,7 @@
       <c r="Q101" s="2"/>
       <c r="R101" s="3"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J102" s="2"/>
       <c r="K102" s="3"/>
       <c r="L102" s="2"/>
@@ -2603,7 +2603,7 @@
       <c r="Q102" s="2"/>
       <c r="R102" s="3"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J103" s="2"/>
       <c r="K103" s="3"/>
       <c r="L103" s="2"/>
@@ -2614,7 +2614,7 @@
       <c r="Q103" s="2"/>
       <c r="R103" s="3"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J104" s="2"/>
       <c r="K104" s="3"/>
       <c r="L104" s="2"/>
@@ -2625,7 +2625,7 @@
       <c r="Q104" s="2"/>
       <c r="R104" s="3"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J105" s="2"/>
       <c r="K105" s="3"/>
       <c r="L105" s="2"/>
@@ -2636,7 +2636,7 @@
       <c r="Q105" s="2"/>
       <c r="R105" s="3"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J106" s="2"/>
       <c r="K106" s="3"/>
       <c r="L106" s="2"/>
@@ -2647,7 +2647,7 @@
       <c r="Q106" s="2"/>
       <c r="R106" s="3"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J107" s="2"/>
       <c r="K107" s="3"/>
       <c r="L107" s="2"/>
@@ -2658,7 +2658,7 @@
       <c r="Q107" s="2"/>
       <c r="R107" s="3"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J108" s="2"/>
       <c r="K108" s="3"/>
       <c r="L108" s="2"/>
@@ -2669,7 +2669,7 @@
       <c r="Q108" s="2"/>
       <c r="R108" s="3"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J109" s="2"/>
       <c r="K109" s="3"/>
       <c r="L109" s="2"/>
@@ -2680,7 +2680,7 @@
       <c r="Q109" s="2"/>
       <c r="R109" s="3"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J110" s="2"/>
       <c r="K110" s="3"/>
       <c r="L110" s="2"/>
@@ -2691,7 +2691,7 @@
       <c r="Q110" s="2"/>
       <c r="R110" s="3"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J111" s="2"/>
       <c r="K111" s="3"/>
       <c r="L111" s="2"/>
@@ -2702,7 +2702,7 @@
       <c r="Q111" s="2"/>
       <c r="R111" s="3"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J112" s="2"/>
       <c r="K112" s="3"/>
       <c r="L112" s="2"/>
@@ -2713,7 +2713,7 @@
       <c r="Q112" s="2"/>
       <c r="R112" s="3"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="113" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J113" s="2"/>
       <c r="K113" s="3"/>
       <c r="L113" s="2"/>
@@ -2724,7 +2724,7 @@
       <c r="Q113" s="2"/>
       <c r="R113" s="3"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J114" s="2"/>
       <c r="K114" s="3"/>
       <c r="L114" s="2"/>
@@ -2735,7 +2735,7 @@
       <c r="Q114" s="2"/>
       <c r="R114" s="3"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="115" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J115" s="2"/>
       <c r="K115" s="3"/>
       <c r="L115" s="2"/>
@@ -2746,7 +2746,7 @@
       <c r="Q115" s="2"/>
       <c r="R115" s="3"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="116" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J116" s="2"/>
       <c r="K116" s="3"/>
       <c r="L116" s="2"/>
@@ -2757,7 +2757,7 @@
       <c r="Q116" s="2"/>
       <c r="R116" s="3"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="117" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J117" s="2"/>
       <c r="K117" s="3"/>
       <c r="L117" s="2"/>
@@ -2768,7 +2768,7 @@
       <c r="Q117" s="2"/>
       <c r="R117" s="3"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="118" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J118" s="2"/>
       <c r="K118" s="3"/>
       <c r="L118" s="2"/>
@@ -2779,7 +2779,7 @@
       <c r="Q118" s="2"/>
       <c r="R118" s="3"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="119" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J119" s="2"/>
       <c r="K119" s="3"/>
       <c r="L119" s="2"/>
@@ -2790,7 +2790,7 @@
       <c r="Q119" s="2"/>
       <c r="R119" s="3"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="120" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J120" s="2"/>
       <c r="K120" s="3"/>
       <c r="L120" s="2"/>
@@ -2801,7 +2801,7 @@
       <c r="Q120" s="2"/>
       <c r="R120" s="3"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="121" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J121" s="2"/>
       <c r="K121" s="3"/>
       <c r="L121" s="2"/>
@@ -2812,7 +2812,7 @@
       <c r="Q121" s="2"/>
       <c r="R121" s="3"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="122" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J122" s="2"/>
       <c r="K122" s="3"/>
       <c r="L122" s="2"/>
@@ -2823,7 +2823,7 @@
       <c r="Q122" s="2"/>
       <c r="R122" s="3"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J123" s="2"/>
       <c r="K123" s="3"/>
       <c r="L123" s="2"/>
@@ -2834,7 +2834,7 @@
       <c r="Q123" s="2"/>
       <c r="R123" s="3"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="124" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J124" s="2"/>
       <c r="K124" s="3"/>
       <c r="L124" s="2"/>
@@ -2845,7 +2845,7 @@
       <c r="Q124" s="2"/>
       <c r="R124" s="3"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="125" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J125" s="2"/>
       <c r="K125" s="3"/>
       <c r="L125" s="2"/>
@@ -2856,7 +2856,7 @@
       <c r="Q125" s="2"/>
       <c r="R125" s="3"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="126" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J126" s="2"/>
       <c r="K126" s="3"/>
       <c r="L126" s="2"/>
@@ -2867,7 +2867,7 @@
       <c r="Q126" s="2"/>
       <c r="R126" s="3"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="127" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J127" s="2"/>
       <c r="K127" s="3"/>
       <c r="L127" s="2"/>
@@ -2878,7 +2878,7 @@
       <c r="Q127" s="2"/>
       <c r="R127" s="3"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="128" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J128" s="2"/>
       <c r="K128" s="3"/>
       <c r="L128" s="2"/>
@@ -2889,7 +2889,7 @@
       <c r="Q128" s="2"/>
       <c r="R128" s="3"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="129" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J129" s="2"/>
       <c r="K129" s="3"/>
       <c r="L129" s="2"/>
@@ -2900,7 +2900,7 @@
       <c r="Q129" s="2"/>
       <c r="R129" s="3"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J130" s="2"/>
       <c r="K130" s="3"/>
       <c r="L130" s="2"/>
@@ -2911,7 +2911,7 @@
       <c r="Q130" s="2"/>
       <c r="R130" s="3"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J131" s="2"/>
       <c r="K131" s="3"/>
       <c r="L131" s="2"/>
@@ -2922,7 +2922,7 @@
       <c r="Q131" s="2"/>
       <c r="R131" s="3"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J132" s="2"/>
       <c r="K132" s="3"/>
       <c r="L132" s="2"/>
@@ -2933,7 +2933,7 @@
       <c r="Q132" s="2"/>
       <c r="R132" s="3"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="133" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J133" s="2"/>
       <c r="K133" s="3"/>
       <c r="L133" s="2"/>
@@ -2944,7 +2944,7 @@
       <c r="Q133" s="2"/>
       <c r="R133" s="3"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J134" s="2"/>
       <c r="K134" s="3"/>
       <c r="L134" s="2"/>
@@ -2955,7 +2955,7 @@
       <c r="Q134" s="2"/>
       <c r="R134" s="3"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="135" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J135" s="2"/>
       <c r="K135" s="3"/>
       <c r="L135" s="2"/>
@@ -2966,7 +2966,7 @@
       <c r="Q135" s="2"/>
       <c r="R135" s="3"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="136" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J136" s="2"/>
       <c r="K136" s="3"/>
       <c r="L136" s="2"/>
@@ -2977,7 +2977,7 @@
       <c r="Q136" s="2"/>
       <c r="R136" s="3"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="137" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J137" s="2"/>
       <c r="K137" s="3"/>
       <c r="L137" s="2"/>
@@ -2988,7 +2988,7 @@
       <c r="Q137" s="2"/>
       <c r="R137" s="3"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="138" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J138" s="2"/>
       <c r="K138" s="3"/>
       <c r="L138" s="2"/>
@@ -2999,7 +2999,7 @@
       <c r="Q138" s="2"/>
       <c r="R138" s="3"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J139" s="2"/>
       <c r="K139" s="3"/>
       <c r="L139" s="2"/>
@@ -3010,7 +3010,7 @@
       <c r="Q139" s="2"/>
       <c r="R139" s="3"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J140" s="2"/>
       <c r="K140" s="3"/>
       <c r="L140" s="2"/>
@@ -3021,7 +3021,7 @@
       <c r="Q140" s="2"/>
       <c r="R140" s="3"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="141" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J141" s="2"/>
       <c r="K141" s="3"/>
       <c r="L141" s="2"/>
@@ -3032,7 +3032,7 @@
       <c r="Q141" s="2"/>
       <c r="R141" s="3"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="142" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J142" s="2"/>
       <c r="K142" s="3"/>
       <c r="L142" s="2"/>
@@ -3043,7 +3043,7 @@
       <c r="Q142" s="2"/>
       <c r="R142" s="3"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="143" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J143" s="2"/>
       <c r="K143" s="3"/>
       <c r="L143" s="2"/>
@@ -3054,7 +3054,7 @@
       <c r="Q143" s="2"/>
       <c r="R143" s="3"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="144" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J144" s="2"/>
       <c r="K144" s="3"/>
       <c r="L144" s="2"/>
@@ -3065,7 +3065,7 @@
       <c r="Q144" s="2"/>
       <c r="R144" s="3"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="145" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J145" s="2"/>
       <c r="K145" s="3"/>
       <c r="L145" s="2"/>
@@ -3076,7 +3076,7 @@
       <c r="Q145" s="2"/>
       <c r="R145" s="3"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="146" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J146" s="2"/>
       <c r="K146" s="3"/>
       <c r="L146" s="2"/>
@@ -3087,7 +3087,7 @@
       <c r="Q146" s="2"/>
       <c r="R146" s="3"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="147" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J147" s="2"/>
       <c r="K147" s="3"/>
       <c r="L147" s="2"/>
@@ -3098,7 +3098,7 @@
       <c r="Q147" s="2"/>
       <c r="R147" s="3"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J148" s="2"/>
       <c r="K148" s="3"/>
       <c r="L148" s="2"/>
@@ -3109,7 +3109,7 @@
       <c r="Q148" s="2"/>
       <c r="R148" s="3"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J149" s="2"/>
       <c r="K149" s="3"/>
       <c r="L149" s="2"/>
@@ -3120,7 +3120,7 @@
       <c r="Q149" s="2"/>
       <c r="R149" s="3"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J150" s="2"/>
       <c r="K150" s="3"/>
       <c r="L150" s="2"/>
@@ -3131,7 +3131,7 @@
       <c r="Q150" s="2"/>
       <c r="R150" s="3"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="151" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J151" s="2"/>
       <c r="K151" s="3"/>
       <c r="L151" s="2"/>
@@ -3142,7 +3142,7 @@
       <c r="Q151" s="2"/>
       <c r="R151" s="3"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="152" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J152" s="2"/>
       <c r="K152" s="3"/>
       <c r="L152" s="2"/>
@@ -3153,7 +3153,7 @@
       <c r="Q152" s="2"/>
       <c r="R152" s="3"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="153" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J153" s="2"/>
       <c r="K153" s="3"/>
       <c r="L153" s="2"/>
@@ -3164,7 +3164,7 @@
       <c r="Q153" s="2"/>
       <c r="R153" s="3"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="154" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J154" s="2"/>
       <c r="K154" s="3"/>
       <c r="L154" s="2"/>
@@ -3175,7 +3175,7 @@
       <c r="Q154" s="2"/>
       <c r="R154" s="3"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="155" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J155" s="2"/>
       <c r="K155" s="3"/>
       <c r="L155" s="2"/>
@@ -3186,7 +3186,7 @@
       <c r="Q155" s="2"/>
       <c r="R155" s="3"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="156" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J156" s="2"/>
       <c r="K156" s="3"/>
       <c r="L156" s="2"/>
@@ -3197,7 +3197,7 @@
       <c r="Q156" s="2"/>
       <c r="R156" s="3"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="157" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J157" s="2"/>
       <c r="K157" s="3"/>
       <c r="L157" s="2"/>
@@ -3208,7 +3208,7 @@
       <c r="Q157" s="2"/>
       <c r="R157" s="3"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="158" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J158" s="2"/>
       <c r="K158" s="3"/>
       <c r="L158" s="2"/>
@@ -3219,7 +3219,7 @@
       <c r="Q158" s="2"/>
       <c r="R158" s="3"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="159" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J159" s="2"/>
       <c r="K159" s="3"/>
       <c r="L159" s="2"/>
@@ -3230,7 +3230,7 @@
       <c r="Q159" s="2"/>
       <c r="R159" s="3"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="160" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J160" s="2"/>
       <c r="K160" s="3"/>
       <c r="L160" s="2"/>
@@ -3241,7 +3241,7 @@
       <c r="Q160" s="2"/>
       <c r="R160" s="3"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="161" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J161" s="2"/>
       <c r="K161" s="3"/>
       <c r="L161" s="2"/>
@@ -3252,7 +3252,7 @@
       <c r="Q161" s="2"/>
       <c r="R161" s="3"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="162" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J162" s="2"/>
       <c r="K162" s="3"/>
       <c r="L162" s="2"/>
@@ -3263,7 +3263,7 @@
       <c r="Q162" s="2"/>
       <c r="R162" s="3"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="163" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J163" s="2"/>
       <c r="K163" s="3"/>
       <c r="L163" s="2"/>
@@ -3274,7 +3274,7 @@
       <c r="Q163" s="2"/>
       <c r="R163" s="3"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="164" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J164" s="2"/>
       <c r="K164" s="3"/>
       <c r="L164" s="2"/>
@@ -3285,7 +3285,7 @@
       <c r="Q164" s="2"/>
       <c r="R164" s="3"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="165" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J165" s="2"/>
       <c r="K165" s="3"/>
       <c r="L165" s="2"/>
@@ -3296,7 +3296,7 @@
       <c r="Q165" s="2"/>
       <c r="R165" s="3"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="166" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J166" s="2"/>
       <c r="K166" s="3"/>
       <c r="L166" s="2"/>
@@ -3307,7 +3307,7 @@
       <c r="Q166" s="2"/>
       <c r="R166" s="3"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="167" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J167" s="2"/>
       <c r="K167" s="3"/>
       <c r="L167" s="2"/>
@@ -3318,7 +3318,7 @@
       <c r="Q167" s="2"/>
       <c r="R167" s="3"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="168" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J168" s="2"/>
       <c r="K168" s="3"/>
       <c r="L168" s="2"/>
@@ -3329,7 +3329,7 @@
       <c r="Q168" s="2"/>
       <c r="R168" s="3"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="169" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J169" s="2"/>
       <c r="K169" s="3"/>
       <c r="L169" s="2"/>
@@ -3340,7 +3340,7 @@
       <c r="Q169" s="2"/>
       <c r="R169" s="3"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="170" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J170" s="2"/>
       <c r="K170" s="3"/>
       <c r="L170" s="2"/>
@@ -3351,7 +3351,7 @@
       <c r="Q170" s="2"/>
       <c r="R170" s="3"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="171" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J171" s="2"/>
       <c r="K171" s="3"/>
       <c r="L171" s="2"/>
@@ -3362,7 +3362,7 @@
       <c r="Q171" s="2"/>
       <c r="R171" s="3"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="172" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J172" s="2"/>
       <c r="K172" s="3"/>
       <c r="L172" s="2"/>
@@ -3373,7 +3373,7 @@
       <c r="Q172" s="2"/>
       <c r="R172" s="3"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="173" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J173" s="2"/>
       <c r="K173" s="3"/>
       <c r="L173" s="2"/>
@@ -3384,7 +3384,7 @@
       <c r="Q173" s="2"/>
       <c r="R173" s="3"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="174" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J174" s="2"/>
       <c r="K174" s="3"/>
       <c r="L174" s="2"/>
@@ -3395,7 +3395,7 @@
       <c r="Q174" s="2"/>
       <c r="R174" s="3"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="175" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J175" s="2"/>
       <c r="K175" s="3"/>
       <c r="L175" s="2"/>
@@ -3406,7 +3406,7 @@
       <c r="Q175" s="2"/>
       <c r="R175" s="3"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="176" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J176" s="2"/>
       <c r="K176" s="3"/>
       <c r="L176" s="2"/>
@@ -3417,7 +3417,7 @@
       <c r="Q176" s="2"/>
       <c r="R176" s="3"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="177" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J177" s="2"/>
       <c r="K177" s="3"/>
       <c r="L177" s="2"/>
@@ -3428,7 +3428,7 @@
       <c r="Q177" s="2"/>
       <c r="R177" s="3"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="178" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J178" s="2"/>
       <c r="K178" s="3"/>
       <c r="L178" s="2"/>
@@ -3439,7 +3439,7 @@
       <c r="Q178" s="2"/>
       <c r="R178" s="3"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="179" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J179" s="2"/>
       <c r="K179" s="3"/>
       <c r="L179" s="2"/>
@@ -3450,7 +3450,7 @@
       <c r="Q179" s="2"/>
       <c r="R179" s="3"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="180" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J180" s="2"/>
       <c r="K180" s="3"/>
       <c r="L180" s="2"/>
@@ -3461,7 +3461,7 @@
       <c r="Q180" s="2"/>
       <c r="R180" s="3"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="181" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J181" s="2"/>
       <c r="K181" s="3"/>
       <c r="L181" s="2"/>
@@ -3472,7 +3472,7 @@
       <c r="Q181" s="2"/>
       <c r="R181" s="3"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="182" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J182" s="2"/>
       <c r="K182" s="3"/>
       <c r="L182" s="2"/>
@@ -3483,7 +3483,7 @@
       <c r="Q182" s="2"/>
       <c r="R182" s="3"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="183" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J183" s="2"/>
       <c r="K183" s="3"/>
       <c r="L183" s="2"/>
@@ -3494,7 +3494,7 @@
       <c r="Q183" s="2"/>
       <c r="R183" s="3"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="184" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J184" s="2"/>
       <c r="K184" s="3"/>
       <c r="L184" s="2"/>
@@ -3505,7 +3505,7 @@
       <c r="Q184" s="2"/>
       <c r="R184" s="3"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="185" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J185" s="2"/>
       <c r="K185" s="3"/>
       <c r="L185" s="2"/>
@@ -3516,7 +3516,7 @@
       <c r="Q185" s="2"/>
       <c r="R185" s="3"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="186" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J186" s="2"/>
       <c r="K186" s="3"/>
       <c r="L186" s="2"/>
@@ -3527,7 +3527,7 @@
       <c r="Q186" s="2"/>
       <c r="R186" s="3"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="187" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J187" s="2"/>
       <c r="K187" s="3"/>
       <c r="L187" s="2"/>
@@ -3538,7 +3538,7 @@
       <c r="Q187" s="2"/>
       <c r="R187" s="3"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="188" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J188" s="2"/>
       <c r="K188" s="3"/>
       <c r="L188" s="2"/>
@@ -3549,7 +3549,7 @@
       <c r="Q188" s="2"/>
       <c r="R188" s="3"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="189" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J189" s="2"/>
       <c r="K189" s="3"/>
       <c r="L189" s="2"/>
@@ -3560,7 +3560,7 @@
       <c r="Q189" s="2"/>
       <c r="R189" s="3"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="190" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J190" s="2"/>
       <c r="K190" s="3"/>
       <c r="L190" s="2"/>
@@ -3571,7 +3571,7 @@
       <c r="Q190" s="2"/>
       <c r="R190" s="3"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="191" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J191" s="2"/>
       <c r="K191" s="3"/>
       <c r="L191" s="2"/>
@@ -3582,7 +3582,7 @@
       <c r="Q191" s="2"/>
       <c r="R191" s="3"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="192" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J192" s="2"/>
       <c r="K192" s="3"/>
       <c r="L192" s="2"/>
@@ -3593,7 +3593,7 @@
       <c r="Q192" s="2"/>
       <c r="R192" s="3"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="193" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J193" s="2"/>
       <c r="K193" s="3"/>
       <c r="L193" s="2"/>
@@ -3604,7 +3604,7 @@
       <c r="Q193" s="2"/>
       <c r="R193" s="3"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="194" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J194" s="2"/>
       <c r="K194" s="3"/>
       <c r="L194" s="2"/>
@@ -3615,7 +3615,7 @@
       <c r="Q194" s="2"/>
       <c r="R194" s="3"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="195" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J195" s="2"/>
       <c r="K195" s="3"/>
       <c r="L195" s="2"/>
@@ -3626,7 +3626,7 @@
       <c r="Q195" s="2"/>
       <c r="R195" s="3"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="196" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J196" s="2"/>
       <c r="K196" s="3"/>
       <c r="L196" s="2"/>
@@ -3637,7 +3637,7 @@
       <c r="Q196" s="2"/>
       <c r="R196" s="3"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="197" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J197" s="2"/>
       <c r="K197" s="3"/>
       <c r="L197" s="2"/>
@@ -3648,7 +3648,7 @@
       <c r="Q197" s="2"/>
       <c r="R197" s="3"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="198" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J198" s="2"/>
       <c r="K198" s="3"/>
       <c r="L198" s="2"/>
@@ -3659,7 +3659,7 @@
       <c r="Q198" s="2"/>
       <c r="R198" s="3"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="199" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J199" s="2"/>
       <c r="K199" s="3"/>
       <c r="L199" s="2"/>
@@ -3670,7 +3670,7 @@
       <c r="Q199" s="2"/>
       <c r="R199" s="3"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="200" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J200" s="2"/>
       <c r="K200" s="3"/>
       <c r="L200" s="2"/>
@@ -3681,7 +3681,7 @@
       <c r="Q200" s="2"/>
       <c r="R200" s="3"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="201" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J201" s="2"/>
       <c r="K201" s="3"/>
       <c r="L201" s="2"/>
@@ -3692,7 +3692,7 @@
       <c r="Q201" s="2"/>
       <c r="R201" s="3"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="202" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J202" s="2"/>
       <c r="K202" s="3"/>
       <c r="L202" s="2"/>
@@ -3703,7 +3703,7 @@
       <c r="Q202" s="2"/>
       <c r="R202" s="3"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="203" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J203" s="2"/>
       <c r="K203" s="3"/>
       <c r="L203" s="2"/>
@@ -3714,7 +3714,7 @@
       <c r="Q203" s="2"/>
       <c r="R203" s="3"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="204" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J204" s="2"/>
       <c r="K204" s="3"/>
       <c r="L204" s="2"/>
@@ -3725,7 +3725,7 @@
       <c r="Q204" s="2"/>
       <c r="R204" s="3"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="205" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J205" s="2"/>
       <c r="K205" s="3"/>
       <c r="L205" s="2"/>
@@ -3736,7 +3736,7 @@
       <c r="Q205" s="2"/>
       <c r="R205" s="3"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="206" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J206" s="2"/>
       <c r="K206" s="3"/>
       <c r="L206" s="2"/>
@@ -3747,7 +3747,7 @@
       <c r="Q206" s="2"/>
       <c r="R206" s="3"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="207" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J207" s="2"/>
       <c r="K207" s="3"/>
       <c r="L207" s="2"/>
@@ -3758,7 +3758,7 @@
       <c r="Q207" s="2"/>
       <c r="R207" s="3"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="208" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J208" s="2"/>
       <c r="K208" s="3"/>
       <c r="L208" s="2"/>
@@ -3769,7 +3769,7 @@
       <c r="Q208" s="2"/>
       <c r="R208" s="3"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="209" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J209" s="2"/>
       <c r="K209" s="3"/>
       <c r="L209" s="2"/>
@@ -3780,7 +3780,7 @@
       <c r="Q209" s="2"/>
       <c r="R209" s="3"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="210" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J210" s="2"/>
       <c r="K210" s="3"/>
       <c r="L210" s="2"/>
@@ -3791,7 +3791,7 @@
       <c r="Q210" s="2"/>
       <c r="R210" s="3"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="211" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J211" s="2"/>
       <c r="K211" s="3"/>
       <c r="L211" s="2"/>
@@ -3802,7 +3802,7 @@
       <c r="Q211" s="2"/>
       <c r="R211" s="3"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="212" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J212" s="2"/>
       <c r="K212" s="3"/>
       <c r="L212" s="2"/>
@@ -3813,7 +3813,7 @@
       <c r="Q212" s="2"/>
       <c r="R212" s="3"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="213" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J213" s="2"/>
       <c r="K213" s="3"/>
       <c r="L213" s="2"/>
@@ -3824,7 +3824,7 @@
       <c r="Q213" s="2"/>
       <c r="R213" s="3"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="214" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J214" s="2"/>
       <c r="K214" s="3"/>
       <c r="L214" s="2"/>
@@ -3835,7 +3835,7 @@
       <c r="Q214" s="2"/>
       <c r="R214" s="3"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="215" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J215" s="2"/>
       <c r="K215" s="3"/>
       <c r="L215" s="2"/>
@@ -3846,7 +3846,7 @@
       <c r="Q215" s="2"/>
       <c r="R215" s="3"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="216" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J216" s="2"/>
       <c r="K216" s="3"/>
       <c r="L216" s="2"/>
@@ -3857,7 +3857,7 @@
       <c r="Q216" s="2"/>
       <c r="R216" s="3"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="217" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J217" s="2"/>
       <c r="K217" s="3"/>
       <c r="L217" s="2"/>
@@ -3868,7 +3868,7 @@
       <c r="Q217" s="2"/>
       <c r="R217" s="3"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="218" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J218" s="2"/>
       <c r="K218" s="3"/>
       <c r="L218" s="2"/>
@@ -3879,7 +3879,7 @@
       <c r="Q218" s="2"/>
       <c r="R218" s="3"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="219" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J219" s="2"/>
       <c r="K219" s="3"/>
       <c r="L219" s="2"/>
@@ -3890,7 +3890,7 @@
       <c r="Q219" s="2"/>
       <c r="R219" s="3"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="220" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J220" s="2"/>
       <c r="K220" s="3"/>
       <c r="L220" s="2"/>
@@ -3901,7 +3901,7 @@
       <c r="Q220" s="2"/>
       <c r="R220" s="3"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="221" ht="15.75" customHeight="1" spans="10:18" x14ac:dyDescent="0.25">
       <c r="J221" s="2"/>
       <c r="K221" s="3"/>
       <c r="L221" s="2"/>
@@ -14482,7 +14482,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -14495,7 +14495,7 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -14508,7 +14508,7 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -14521,7 +14521,7 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -14534,7 +14534,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -14547,7 +14547,7 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -14560,7 +14560,7 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -14573,7 +14573,7 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -14586,7 +14586,7 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -14599,7 +14599,7 @@
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -14612,7 +14612,7 @@
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -14625,7 +14625,7 @@
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -14638,7 +14638,7 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -14651,7 +14651,7 @@
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -14664,7 +14664,7 @@
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -14677,7 +14677,7 @@
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -14690,7 +14690,7 @@
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -14703,7 +14703,7 @@
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -14716,7 +14716,7 @@
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -14729,7 +14729,7 @@
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -14742,7 +14742,7 @@
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -14755,7 +14755,7 @@
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -14768,7 +14768,7 @@
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -14781,7 +14781,7 @@
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -14794,7 +14794,7 @@
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -14807,7 +14807,7 @@
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -14820,7 +14820,7 @@
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -14833,7 +14833,7 @@
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -14846,7 +14846,7 @@
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -14859,7 +14859,7 @@
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -14872,7 +14872,7 @@
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -14885,7 +14885,7 @@
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
@@ -14898,7 +14898,7 @@
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -14911,7 +14911,7 @@
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -14924,7 +14924,7 @@
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -14937,7 +14937,7 @@
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -14950,7 +14950,7 @@
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -14963,7 +14963,7 @@
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -14976,7 +14976,7 @@
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
@@ -14989,7 +14989,7 @@
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -15002,7 +15002,7 @@
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -15015,7 +15015,7 @@
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -15028,7 +15028,7 @@
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -15041,7 +15041,7 @@
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
@@ -15054,7 +15054,7 @@
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -15067,7 +15067,7 @@
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
@@ -15080,7 +15080,7 @@
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -15093,7 +15093,7 @@
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
@@ -15106,7 +15106,7 @@
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
@@ -15119,7 +15119,7 @@
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -15132,7 +15132,7 @@
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -15145,7 +15145,7 @@
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -15158,7 +15158,7 @@
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -15171,7 +15171,7 @@
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
@@ -15184,7 +15184,7 @@
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -15197,7 +15197,7 @@
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
@@ -15210,7 +15210,7 @@
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -15223,7 +15223,7 @@
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
@@ -15236,7 +15236,7 @@
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -15249,7 +15249,7 @@
       <c r="K71" s="2"/>
       <c r="L71" s="2"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
@@ -15262,7 +15262,7 @@
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
@@ -15275,7 +15275,7 @@
       <c r="K73" s="2"/>
       <c r="L73" s="2"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
@@ -15288,7 +15288,7 @@
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
@@ -15301,7 +15301,7 @@
       <c r="K75" s="2"/>
       <c r="L75" s="2"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
@@ -15314,7 +15314,7 @@
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
@@ -15327,7 +15327,7 @@
       <c r="K77" s="2"/>
       <c r="L77" s="2"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
@@ -15340,7 +15340,7 @@
       <c r="K78" s="2"/>
       <c r="L78" s="2"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
@@ -15353,7 +15353,7 @@
       <c r="K79" s="2"/>
       <c r="L79" s="2"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
@@ -15366,7 +15366,7 @@
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
@@ -15379,7 +15379,7 @@
       <c r="K81" s="2"/>
       <c r="L81" s="2"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
@@ -15392,7 +15392,7 @@
       <c r="K82" s="2"/>
       <c r="L82" s="2"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
@@ -15405,7 +15405,7 @@
       <c r="K83" s="2"/>
       <c r="L83" s="2"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
@@ -15418,7 +15418,7 @@
       <c r="K84" s="2"/>
       <c r="L84" s="2"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
@@ -15431,7 +15431,7 @@
       <c r="K85" s="2"/>
       <c r="L85" s="2"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
@@ -15444,7 +15444,7 @@
       <c r="K86" s="2"/>
       <c r="L86" s="2"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
@@ -15457,7 +15457,7 @@
       <c r="K87" s="2"/>
       <c r="L87" s="2"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
@@ -15470,7 +15470,7 @@
       <c r="K88" s="2"/>
       <c r="L88" s="2"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
@@ -15483,7 +15483,7 @@
       <c r="K89" s="2"/>
       <c r="L89" s="2"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
@@ -15496,7 +15496,7 @@
       <c r="K90" s="2"/>
       <c r="L90" s="2"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
@@ -15509,7 +15509,7 @@
       <c r="K91" s="2"/>
       <c r="L91" s="2"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
@@ -15522,7 +15522,7 @@
       <c r="K92" s="2"/>
       <c r="L92" s="2"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
@@ -15535,7 +15535,7 @@
       <c r="K93" s="2"/>
       <c r="L93" s="2"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
@@ -15548,7 +15548,7 @@
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
@@ -15561,7 +15561,7 @@
       <c r="K95" s="2"/>
       <c r="L95" s="2"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
@@ -15574,7 +15574,7 @@
       <c r="K96" s="2"/>
       <c r="L96" s="2"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
@@ -15587,7 +15587,7 @@
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
@@ -15600,7 +15600,7 @@
       <c r="K98" s="2"/>
       <c r="L98" s="2"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
@@ -15613,7 +15613,7 @@
       <c r="K99" s="2"/>
       <c r="L99" s="2"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
@@ -15626,7 +15626,7 @@
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
@@ -15639,7 +15639,7 @@
       <c r="K101" s="2"/>
       <c r="L101" s="2"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
@@ -15652,7 +15652,7 @@
       <c r="K102" s="2"/>
       <c r="L102" s="2"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
@@ -15665,7 +15665,7 @@
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
@@ -15678,7 +15678,7 @@
       <c r="K104" s="2"/>
       <c r="L104" s="2"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
@@ -15691,7 +15691,7 @@
       <c r="K105" s="2"/>
       <c r="L105" s="2"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
@@ -15704,7 +15704,7 @@
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
@@ -15717,7 +15717,7 @@
       <c r="K107" s="2"/>
       <c r="L107" s="2"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
@@ -15730,7 +15730,7 @@
       <c r="K108" s="2"/>
       <c r="L108" s="2"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
@@ -15743,7 +15743,7 @@
       <c r="K109" s="2"/>
       <c r="L109" s="2"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
@@ -15756,7 +15756,7 @@
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
@@ -15769,7 +15769,7 @@
       <c r="K111" s="2"/>
       <c r="L111" s="2"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
@@ -15782,7 +15782,7 @@
       <c r="K112" s="2"/>
       <c r="L112" s="2"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
@@ -15795,7 +15795,7 @@
       <c r="K113" s="2"/>
       <c r="L113" s="2"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
@@ -15808,7 +15808,7 @@
       <c r="K114" s="2"/>
       <c r="L114" s="2"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
@@ -15821,7 +15821,7 @@
       <c r="K115" s="2"/>
       <c r="L115" s="2"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
@@ -15834,7 +15834,7 @@
       <c r="K116" s="2"/>
       <c r="L116" s="2"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
@@ -15847,7 +15847,7 @@
       <c r="K117" s="2"/>
       <c r="L117" s="2"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
@@ -15860,7 +15860,7 @@
       <c r="K118" s="2"/>
       <c r="L118" s="2"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
@@ -15873,7 +15873,7 @@
       <c r="K119" s="2"/>
       <c r="L119" s="2"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
@@ -15886,7 +15886,7 @@
       <c r="K120" s="2"/>
       <c r="L120" s="2"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
@@ -15899,7 +15899,7 @@
       <c r="K121" s="2"/>
       <c r="L121" s="2"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
@@ -15912,7 +15912,7 @@
       <c r="K122" s="2"/>
       <c r="L122" s="2"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
@@ -15925,7 +15925,7 @@
       <c r="K123" s="2"/>
       <c r="L123" s="2"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
@@ -15938,7 +15938,7 @@
       <c r="K124" s="2"/>
       <c r="L124" s="2"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
@@ -15951,7 +15951,7 @@
       <c r="K125" s="2"/>
       <c r="L125" s="2"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
@@ -15964,7 +15964,7 @@
       <c r="K126" s="2"/>
       <c r="L126" s="2"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
@@ -15977,7 +15977,7 @@
       <c r="K127" s="2"/>
       <c r="L127" s="2"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
@@ -15990,7 +15990,7 @@
       <c r="K128" s="2"/>
       <c r="L128" s="2"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
@@ -16003,7 +16003,7 @@
       <c r="K129" s="2"/>
       <c r="L129" s="2"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
@@ -16016,7 +16016,7 @@
       <c r="K130" s="2"/>
       <c r="L130" s="2"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
@@ -16029,7 +16029,7 @@
       <c r="K131" s="2"/>
       <c r="L131" s="2"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
@@ -16042,7 +16042,7 @@
       <c r="K132" s="2"/>
       <c r="L132" s="2"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
@@ -16055,7 +16055,7 @@
       <c r="K133" s="2"/>
       <c r="L133" s="2"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
@@ -16068,7 +16068,7 @@
       <c r="K134" s="2"/>
       <c r="L134" s="2"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
@@ -16081,7 +16081,7 @@
       <c r="K135" s="2"/>
       <c r="L135" s="2"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
@@ -16094,7 +16094,7 @@
       <c r="K136" s="2"/>
       <c r="L136" s="2"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
       <c r="D137" s="2"/>
@@ -16107,7 +16107,7 @@
       <c r="K137" s="2"/>
       <c r="L137" s="2"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
@@ -16120,7 +16120,7 @@
       <c r="K138" s="2"/>
       <c r="L138" s="2"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
@@ -16133,7 +16133,7 @@
       <c r="K139" s="2"/>
       <c r="L139" s="2"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
@@ -16146,7 +16146,7 @@
       <c r="K140" s="2"/>
       <c r="L140" s="2"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
@@ -16159,7 +16159,7 @@
       <c r="K141" s="2"/>
       <c r="L141" s="2"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
@@ -16172,7 +16172,7 @@
       <c r="K142" s="2"/>
       <c r="L142" s="2"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
@@ -16185,7 +16185,7 @@
       <c r="K143" s="2"/>
       <c r="L143" s="2"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
@@ -16198,7 +16198,7 @@
       <c r="K144" s="2"/>
       <c r="L144" s="2"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
@@ -16211,7 +16211,7 @@
       <c r="K145" s="2"/>
       <c r="L145" s="2"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
@@ -16224,7 +16224,7 @@
       <c r="K146" s="2"/>
       <c r="L146" s="2"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
@@ -16237,7 +16237,7 @@
       <c r="K147" s="2"/>
       <c r="L147" s="2"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
@@ -16250,7 +16250,7 @@
       <c r="K148" s="2"/>
       <c r="L148" s="2"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
       <c r="D149" s="2"/>
@@ -16263,7 +16263,7 @@
       <c r="K149" s="2"/>
       <c r="L149" s="2"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
@@ -16276,7 +16276,7 @@
       <c r="K150" s="2"/>
       <c r="L150" s="2"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
@@ -16289,7 +16289,7 @@
       <c r="K151" s="2"/>
       <c r="L151" s="2"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
@@ -16302,7 +16302,7 @@
       <c r="K152" s="2"/>
       <c r="L152" s="2"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
       <c r="D153" s="2"/>
@@ -16315,7 +16315,7 @@
       <c r="K153" s="2"/>
       <c r="L153" s="2"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
       <c r="D154" s="2"/>
@@ -16328,7 +16328,7 @@
       <c r="K154" s="2"/>
       <c r="L154" s="2"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
       <c r="D155" s="2"/>
@@ -16341,7 +16341,7 @@
       <c r="K155" s="2"/>
       <c r="L155" s="2"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
@@ -16354,7 +16354,7 @@
       <c r="K156" s="2"/>
       <c r="L156" s="2"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
@@ -16367,7 +16367,7 @@
       <c r="K157" s="2"/>
       <c r="L157" s="2"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
       <c r="D158" s="2"/>
@@ -16380,7 +16380,7 @@
       <c r="K158" s="2"/>
       <c r="L158" s="2"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
       <c r="D159" s="2"/>
@@ -16393,7 +16393,7 @@
       <c r="K159" s="2"/>
       <c r="L159" s="2"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
       <c r="D160" s="2"/>
@@ -16406,7 +16406,7 @@
       <c r="K160" s="2"/>
       <c r="L160" s="2"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
@@ -16419,7 +16419,7 @@
       <c r="K161" s="2"/>
       <c r="L161" s="2"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
       <c r="D162" s="2"/>
@@ -16432,7 +16432,7 @@
       <c r="K162" s="2"/>
       <c r="L162" s="2"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
       <c r="D163" s="2"/>
@@ -16445,7 +16445,7 @@
       <c r="K163" s="2"/>
       <c r="L163" s="2"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
@@ -16458,7 +16458,7 @@
       <c r="K164" s="2"/>
       <c r="L164" s="2"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
@@ -16471,7 +16471,7 @@
       <c r="K165" s="2"/>
       <c r="L165" s="2"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
       <c r="D166" s="2"/>
@@ -16484,7 +16484,7 @@
       <c r="K166" s="2"/>
       <c r="L166" s="2"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
       <c r="D167" s="2"/>
@@ -16497,7 +16497,7 @@
       <c r="K167" s="2"/>
       <c r="L167" s="2"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
@@ -16510,7 +16510,7 @@
       <c r="K168" s="2"/>
       <c r="L168" s="2"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
       <c r="D169" s="2"/>
@@ -16523,7 +16523,7 @@
       <c r="K169" s="2"/>
       <c r="L169" s="2"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
       <c r="D170" s="2"/>
@@ -16536,7 +16536,7 @@
       <c r="K170" s="2"/>
       <c r="L170" s="2"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
@@ -16549,7 +16549,7 @@
       <c r="K171" s="2"/>
       <c r="L171" s="2"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
@@ -16562,7 +16562,7 @@
       <c r="K172" s="2"/>
       <c r="L172" s="2"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
@@ -16575,7 +16575,7 @@
       <c r="K173" s="2"/>
       <c r="L173" s="2"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
@@ -16588,7 +16588,7 @@
       <c r="K174" s="2"/>
       <c r="L174" s="2"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
@@ -16601,7 +16601,7 @@
       <c r="K175" s="2"/>
       <c r="L175" s="2"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
@@ -16614,7 +16614,7 @@
       <c r="K176" s="2"/>
       <c r="L176" s="2"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
@@ -16627,7 +16627,7 @@
       <c r="K177" s="2"/>
       <c r="L177" s="2"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
@@ -16640,7 +16640,7 @@
       <c r="K178" s="2"/>
       <c r="L178" s="2"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
@@ -16653,7 +16653,7 @@
       <c r="K179" s="2"/>
       <c r="L179" s="2"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
@@ -16666,7 +16666,7 @@
       <c r="K180" s="2"/>
       <c r="L180" s="2"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
@@ -16679,7 +16679,7 @@
       <c r="K181" s="2"/>
       <c r="L181" s="2"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
       <c r="D182" s="2"/>
@@ -16692,7 +16692,7 @@
       <c r="K182" s="2"/>
       <c r="L182" s="2"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
       <c r="D183" s="2"/>
@@ -16705,7 +16705,7 @@
       <c r="K183" s="2"/>
       <c r="L183" s="2"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
@@ -16718,7 +16718,7 @@
       <c r="K184" s="2"/>
       <c r="L184" s="2"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
@@ -16731,7 +16731,7 @@
       <c r="K185" s="2"/>
       <c r="L185" s="2"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
@@ -16744,7 +16744,7 @@
       <c r="K186" s="2"/>
       <c r="L186" s="2"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
@@ -16757,7 +16757,7 @@
       <c r="K187" s="2"/>
       <c r="L187" s="2"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
@@ -16770,7 +16770,7 @@
       <c r="K188" s="2"/>
       <c r="L188" s="2"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
@@ -16783,7 +16783,7 @@
       <c r="K189" s="2"/>
       <c r="L189" s="2"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
       <c r="D190" s="2"/>
@@ -16796,7 +16796,7 @@
       <c r="K190" s="2"/>
       <c r="L190" s="2"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
       <c r="D191" s="2"/>
@@ -16809,7 +16809,7 @@
       <c r="K191" s="2"/>
       <c r="L191" s="2"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
@@ -16822,7 +16822,7 @@
       <c r="K192" s="2"/>
       <c r="L192" s="2"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
@@ -16835,7 +16835,7 @@
       <c r="K193" s="2"/>
       <c r="L193" s="2"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
@@ -16848,7 +16848,7 @@
       <c r="K194" s="2"/>
       <c r="L194" s="2"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
       <c r="D195" s="2"/>
@@ -16861,7 +16861,7 @@
       <c r="K195" s="2"/>
       <c r="L195" s="2"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
@@ -16874,7 +16874,7 @@
       <c r="K196" s="2"/>
       <c r="L196" s="2"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
       <c r="D197" s="2"/>
@@ -16887,7 +16887,7 @@
       <c r="K197" s="2"/>
       <c r="L197" s="2"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
@@ -16900,7 +16900,7 @@
       <c r="K198" s="2"/>
       <c r="L198" s="2"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
@@ -16913,7 +16913,7 @@
       <c r="K199" s="2"/>
       <c r="L199" s="2"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
@@ -16926,7 +16926,7 @@
       <c r="K200" s="2"/>
       <c r="L200" s="2"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
@@ -16939,7 +16939,7 @@
       <c r="K201" s="2"/>
       <c r="L201" s="2"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
@@ -16952,7 +16952,7 @@
       <c r="K202" s="2"/>
       <c r="L202" s="2"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
@@ -16965,7 +16965,7 @@
       <c r="K203" s="2"/>
       <c r="L203" s="2"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
@@ -16978,7 +16978,7 @@
       <c r="K204" s="2"/>
       <c r="L204" s="2"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
@@ -16991,7 +16991,7 @@
       <c r="K205" s="2"/>
       <c r="L205" s="2"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
@@ -17004,7 +17004,7 @@
       <c r="K206" s="2"/>
       <c r="L206" s="2"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
       <c r="D207" s="2"/>
@@ -17017,7 +17017,7 @@
       <c r="K207" s="2"/>
       <c r="L207" s="2"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
       <c r="D208" s="2"/>
@@ -17030,7 +17030,7 @@
       <c r="K208" s="2"/>
       <c r="L208" s="2"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
@@ -17043,7 +17043,7 @@
       <c r="K209" s="2"/>
       <c r="L209" s="2"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
       <c r="D210" s="2"/>
@@ -17056,7 +17056,7 @@
       <c r="K210" s="2"/>
       <c r="L210" s="2"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
       <c r="D211" s="2"/>
@@ -17069,7 +17069,7 @@
       <c r="K211" s="2"/>
       <c r="L211" s="2"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
@@ -17082,7 +17082,7 @@
       <c r="K212" s="2"/>
       <c r="L212" s="2"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
       <c r="D213" s="2"/>
@@ -17095,7 +17095,7 @@
       <c r="K213" s="2"/>
       <c r="L213" s="2"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>
@@ -17108,7 +17108,7 @@
       <c r="K214" s="2"/>
       <c r="L214" s="2"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
       <c r="D215" s="2"/>
@@ -17121,7 +17121,7 @@
       <c r="K215" s="2"/>
       <c r="L215" s="2"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
       <c r="D216" s="2"/>
@@ -17134,7 +17134,7 @@
       <c r="K216" s="2"/>
       <c r="L216" s="2"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
       <c r="D217" s="2"/>
@@ -17147,7 +17147,7 @@
       <c r="K217" s="2"/>
       <c r="L217" s="2"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
       <c r="D218" s="2"/>
@@ -17160,7 +17160,7 @@
       <c r="K218" s="2"/>
       <c r="L218" s="2"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
       <c r="D219" s="2"/>
@@ -17173,7 +17173,7 @@
       <c r="K219" s="2"/>
       <c r="L219" s="2"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
       <c r="D220" s="2"/>
@@ -17186,7 +17186,7 @@
       <c r="K220" s="2"/>
       <c r="L220" s="2"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" ht="15.75" customHeight="1" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
       <c r="D221" s="2"/>

--- a/api/templates/device_and_site_summary_report/fr.xlsx
+++ b/api/templates/device_and_site_summary_report/fr.xlsx
@@ -38,7 +38,7 @@
     <t>&lt;AssaysLabel&gt;: &lt;Assays&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Dispositifs déclassés: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -916,7 +916,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
